--- a/liberation_war_articles.xlsx
+++ b/liberation_war_articles.xlsx
@@ -13,9 +13,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Articles'!$A$1:$F$145</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Needs review'!$A$1:$G$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Other sections'!$A$1:$G$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Articles'!$A$1:$F$158</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Needs review'!$A$1:$G$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Other sections'!$A$1:$G$50</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F145"/>
+  <dimension ref="A1:F158"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -492,21 +492,21 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>42469</v>
+        <v>43085</v>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>Naeem Mohaiemen</t>
+          <t>Anthony Mascarenhas</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>Muktijuddho: Polyphony of the Ocean</t>
+          <t>GENOCIDE</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/in-focus/muktijuddho-polyphony-the-ocean-1206313</t>
+          <t>https://www.thedailystar.net/slow-reads/focus/news/genocide-1505440</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -520,21 +520,21 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>42700</v>
+        <v>42084</v>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>ASIF MUNIER</t>
+          <t>Md Shahnawaz Khan Chandan</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>Munier Chowdhury: Personal Glimpses</t>
+          <t>Their Lips are Sealed</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/in-focus/munier-chowdhury-personal-glimpses-1320649</t>
+          <t>https://www.thedailystar.net/in-focus/their-lips-are-sealed-72792</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -548,21 +548,21 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>42721</v>
+        <v>42091</v>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Serajul Islam Choudhury</t>
+          <t>Kaberi Gayen</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>THE UNFINISHED STRUGGLE</t>
+          <t>Why women freedom fighters are missing from Bangladesh's Liberation War films</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/in-focus/the-unfinished-struggle-1331104</t>
+          <t>https://www.thedailystar.net/in-focus/women-not-portrayed-freedom-fighters-screen-74241</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -576,7 +576,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>42770</v>
+        <v>42098</v>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
@@ -585,12 +585,12 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>We shall overcome</t>
+          <t>In conversation with Professor Rehman Sobhan</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/in-focus/we-shall-overcome-1355557</t>
+          <t>https://www.thedailystar.net/in-focus/the-economist-and-the-patriot-75436</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -604,26 +604,26 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>42798</v>
+        <v>42231</v>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Md. Golam Kibria</t>
+          <t>Tarashankar Bandyopadhyay</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>A Quiet Courage</t>
+          <t>On the Eve of the Emergence of Bangladesh</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/slow-reads/focus/news/quiet-courage-1370599</t>
+          <t>https://www.thedailystar.net/in-focus/the-eve-the-emergence-bangladesh-127051</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Borderline</t>
+          <t>Core</t>
         </is>
       </c>
     </row>
@@ -632,26 +632,26 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>42819</v>
+        <v>42259</v>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Mashruk Ahmed</t>
+          <t>The Daily Star</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>“The war is not over yet”</t>
+          <t>A Purist's Struggle</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/in-focus/the-war-not-over-yet-1380949</t>
+          <t>https://www.thedailystar.net/in-focus/purists-struggle-141622</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Borderline</t>
         </is>
       </c>
     </row>
@@ -660,26 +660,26 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>42933</v>
+        <v>42357</v>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Nahela Nowshin</t>
+          <t>The Daily Star</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>Justice After Nuremberg</t>
+          <t>Thinkers Will Lead The Way</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/in-focus/justice-after-nuremberg-1434352</t>
+          <t>https://www.thedailystar.net/slow-reads/focus/news/thinkers-will-lead-the-way-189340</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Borderline</t>
+          <t>Core</t>
         </is>
       </c>
     </row>
@@ -688,26 +688,26 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>42961</v>
+        <v>42392</v>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Catherine Masud</t>
+          <t>Naznin Tithi</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Tareque and Munier: You are always with us</t>
+          <t>GANO ADALOT</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/in-focus/tareque-and-munier-you-are-always-us-1448296</t>
+          <t>https://www.thedailystar.net/in-focus/gano-adalot-205765</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Borderline</t>
+          <t>Core</t>
         </is>
       </c>
     </row>
@@ -716,26 +716,26 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>42996</v>
+        <v>42420</v>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>Sushmita S Preetha</t>
+          <t>The Daily Star</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Ethical challenges of documenting Birangonas</t>
+          <t>The Origins of the Language Movement</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/slow-reads/focus/news/ethical-challenges-documenting-birangonas-1463638</t>
+          <t>https://www.thedailystar.net/in-focus/the-origins-the-language-movement-574846</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Borderline</t>
         </is>
       </c>
     </row>
@@ -744,21 +744,21 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>43045</v>
+        <v>42455</v>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>The Daily Star</t>
+          <t>Kajalie Shehreen Islam</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>In loving memory of a Crack Platoon warrior</t>
+          <t>The Burden of Dis/honour</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/in-focus/loving-memory-crack-platoon-warrior-1487017</t>
+          <t>https://www.thedailystar.net/in-focus/the-burden-dishonour-1199632</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -772,26 +772,26 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>43073</v>
+        <v>42469</v>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>Waqar A Khan</t>
+          <t>Naeem Mohaiemen</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>From the labyrinth of memory</t>
+          <t>Muktijuddho: Polyphony of the Ocean</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/in-focus/the-labyrinth-memory-1499692</t>
+          <t>https://www.thedailystar.net/in-focus/muktijuddho-polyphony-the-ocean-1206313</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Borderline</t>
+          <t>Core</t>
         </is>
       </c>
     </row>
@@ -800,26 +800,26 @@
         <v>12</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>43085</v>
+        <v>42700</v>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Anthony Mascarenhas</t>
+          <t>ASIF MUNIER</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>GENOCIDE</t>
+          <t>Munier Chowdhury: Personal Glimpses</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/slow-reads/focus/news/genocide-1505440</t>
+          <t>https://www.thedailystar.net/in-focus/munier-chowdhury-personal-glimpses-1320649</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Borderline</t>
         </is>
       </c>
     </row>
@@ -828,21 +828,21 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>43087</v>
+        <v>42721</v>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>Col Towficur Rahman (Retd)</t>
+          <t>Serajul Islam Choudhury</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>The journey to Liberation War by a fifteen year old boy</t>
+          <t>THE UNFINISHED STRUGGLE</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/slow-reads/focus/news/the-journey-liberation-war-fifteen-year-old-boy-1506442</t>
+          <t>https://www.thedailystar.net/in-focus/the-unfinished-struggle-1331104</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -856,26 +856,26 @@
         <v>14</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>43549</v>
+        <v>42770</v>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Interview by Ananta Yusuf</t>
+          <t>Amitava Kar</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>Raghu Rai: The man behind the lens</t>
+          <t>We shall overcome</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/slow-reads/focus/news/raghu-rai-the-man-behind-the-lens-1720066</t>
+          <t>https://www.thedailystar.net/in-focus/we-shall-overcome-1355557</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Borderline</t>
         </is>
       </c>
     </row>
@@ -884,26 +884,26 @@
         <v>15</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>43710</v>
+        <v>42798</v>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>The Daily Star</t>
+          <t>Md. Golam Kibria</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>"I am only making a modest contribution to the struggle of my people"</t>
+          <t>A Quiet Courage</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/in-focus/news/i-am-only-making-modest-contribution-the-struggle-my-people-1794181</t>
+          <t>https://www.thedailystar.net/slow-reads/focus/news/quiet-courage-1370599</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Borderline</t>
         </is>
       </c>
     </row>
@@ -912,21 +912,21 @@
         <v>16</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>43787</v>
+        <v>42819</v>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Emran Mahfuz</t>
+          <t>Mashruk Ahmed</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>Eid in 1971: A forgotten chapter of the Liberation War</t>
+          <t>“The war is not over yet”</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/slow-reads/focus/news/eid-1971-forgotten-chapter-the-liberation-war-1828372</t>
+          <t>https://www.thedailystar.net/in-focus/the-war-not-over-yet-1380949</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -940,21 +940,21 @@
         <v>17</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>44033</v>
+        <v>42933</v>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>Tonny Nowshin</t>
+          <t>Nahela Nowshin</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>Shirin Banu Mitil: A person out of a fairy-tale</t>
+          <t>Justice After Nuremberg</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/slow-reads/focus/news/shirin-banu-mitil-person-out-fairy-tale-1933769</t>
+          <t>https://www.thedailystar.net/in-focus/justice-after-nuremberg-1434352</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -968,21 +968,21 @@
         <v>18</v>
       </c>
       <c r="B19" s="2" t="n">
-        <v>44081</v>
+        <v>42961</v>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Tariq Karim</t>
+          <t>Catherine Masud</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>Bangabandhu: the architect of Bangladesh's foreign policy</t>
+          <t>Tareque and Munier: You are always with us</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/in-focus/news/bangabandhu-the-architect-bangladeshs-foreign-policy-1956905</t>
+          <t>https://www.thedailystar.net/in-focus/tareque-and-munier-you-are-always-us-1448296</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -996,21 +996,21 @@
         <v>19</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>44179</v>
+        <v>42996</v>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>Shashoti Haque</t>
+          <t>Sushmita S Preetha</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>The Brave Doctor</t>
+          <t>Ethical challenges of documenting Birangonas</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/in-focus/news/the-brave-doctor-shaheed-dr-azharul-haque-2010921</t>
+          <t>https://www.thedailystar.net/slow-reads/focus/news/ethical-challenges-documenting-birangonas-1463638</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1024,26 +1024,26 @@
         <v>20</v>
       </c>
       <c r="B21" s="2" t="n">
-        <v>44221</v>
+        <v>43045</v>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Samantha Christiansen</t>
+          <t>The Daily Star</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>The Angry Young World</t>
+          <t>In loving memory of a Crack Platoon warrior</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/in-focus/news/the-angry-young-world-2033213</t>
+          <t>https://www.thedailystar.net/in-focus/loving-memory-crack-platoon-warrior-1487017</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Borderline</t>
+          <t>Core</t>
         </is>
       </c>
     </row>
@@ -1052,26 +1052,26 @@
         <v>21</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>44263</v>
+        <v>43073</v>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>Mayabee Arannya and Tasnim Odrika</t>
+          <t>Waqar A Khan</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>50 years later, the fight goes on</t>
+          <t>From the labyrinth of memory</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/in-focus/news/50-years-later-the-fight-goes-2056797</t>
+          <t>https://www.thedailystar.net/in-focus/the-labyrinth-memory-1499692</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Borderline</t>
         </is>
       </c>
     </row>
@@ -1080,21 +1080,21 @@
         <v>22</v>
       </c>
       <c r="B23" s="2" t="n">
-        <v>44264</v>
+        <v>43087</v>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Shamsuddoza Sajen</t>
+          <t>Col Towficur Rahman (Retd)</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>Bhashani’s support for non-cooperation movement</t>
+          <t>The journey to Liberation War by a fifteen year old boy</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/slow-reads/focus/news/bhashanis-support-non-cooperation-movement-2057441</t>
+          <t>https://www.thedailystar.net/slow-reads/focus/news/the-journey-liberation-war-fifteen-year-old-boy-1506442</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1108,21 +1108,21 @@
         <v>23</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>44277</v>
+        <v>43549</v>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>Subho Basu</t>
+          <t>Interview by Ananta Yusuf</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>The birth of Bangladesh and nationality question in South Asia</t>
+          <t>Raghu Rai: The man behind the lens</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/slow-reads/focus/news/the-birth-bangladesh-and-nationality-question-south-asia-2064513</t>
+          <t>https://www.thedailystar.net/slow-reads/focus/news/raghu-rai-the-man-behind-the-lens-1720066</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1136,21 +1136,21 @@
         <v>24</v>
       </c>
       <c r="B25" s="2" t="n">
-        <v>44283</v>
+        <v>43569</v>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Sadia Mahmood</t>
+          <t>Mannan Mashhur Zarif</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>The 1971 war, caste, citizenship and a war memorial in Tharparkar</t>
+          <t>Quamrul’s Bengal</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/slow-reads/focus/news/the-1971-war-caste-citizenship-and-war-memorial-tharparkar-2067765</t>
+          <t>https://www.thedailystar.net/slow-reads/slow-reads-special/news/quamruls-bengal-1729789</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1164,21 +1164,21 @@
         <v>25</v>
       </c>
       <c r="B26" s="2" t="n">
-        <v>44284</v>
+        <v>43710</v>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>Thomas Newbold</t>
+          <t>The Daily Star</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>The Historian and the Riflemen</t>
+          <t>"I am only making a modest contribution to the struggle of my people"</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/in-focus/news/the-historian-and-the-riflemen-2068577</t>
+          <t>https://www.thedailystar.net/in-focus/news/i-am-only-making-modest-contribution-the-struggle-my-people-1794181</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1192,26 +1192,26 @@
         <v>26</v>
       </c>
       <c r="B27" s="2" t="n">
-        <v>44305</v>
+        <v>43787</v>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>Waqar A Khan</t>
+          <t>Emran Mahfuz</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>The myth of martial race: Seared into a schoolboy's memory!</t>
+          <t>Eid in 1971: A forgotten chapter of the Liberation War</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/in-focus/news/the-myth-martial-race-seared-schoolboys-memory-2079653</t>
+          <t>https://www.thedailystar.net/slow-reads/focus/news/eid-1971-forgotten-chapter-the-liberation-war-1828372</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Borderline</t>
+          <t>Core</t>
         </is>
       </c>
     </row>
@@ -1220,26 +1220,26 @@
         <v>27</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>44340</v>
+        <v>44033</v>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>Brig R P Singh, VSM (retired)</t>
+          <t>Tonny Nowshin</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>How the Mukti Bahini was trained</t>
+          <t>Shirin Banu Mitil: A person out of a fairy-tale</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/in-focus/news/how-the-mukti-bahini-was-trained-2097481</t>
+          <t>https://www.thedailystar.net/slow-reads/focus/news/shirin-banu-mitil-person-out-fairy-tale-1933769</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Borderline</t>
         </is>
       </c>
     </row>
@@ -1248,26 +1248,26 @@
         <v>28</v>
       </c>
       <c r="B29" s="2" t="n">
-        <v>44361</v>
+        <v>44081</v>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>Mahbub Uddin Ahmed Bir Bikram</t>
+          <t>Tariq Karim</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>Remembering the Battle of Bhomra</t>
+          <t>Bangabandhu: the architect of Bangladesh's foreign policy</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/in-focus/news/remembering-the-battle-bhomra-2110329</t>
+          <t>https://www.thedailystar.net/in-focus/news/bangabandhu-the-architect-bangladeshs-foreign-policy-1956905</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Borderline</t>
         </is>
       </c>
     </row>
@@ -1276,21 +1276,21 @@
         <v>29</v>
       </c>
       <c r="B30" s="2" t="n">
-        <v>44368</v>
+        <v>44179</v>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>Nayanika Mookherjee</t>
+          <t>Shashoti Haque</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>History and the Birangona</t>
+          <t>The Brave Doctor</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/in-focus/news/history-and-the-birangona-2114681</t>
+          <t>https://www.thedailystar.net/in-focus/news/the-brave-doctor-shaheed-dr-azharul-haque-2010921</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1304,21 +1304,21 @@
         <v>30</v>
       </c>
       <c r="B31" s="2" t="n">
-        <v>44389</v>
+        <v>44221</v>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>Waqar A Khan</t>
+          <t>Samantha Christiansen</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>The Incorrigible Zulfikar Ali Bhutto</t>
+          <t>The Angry Young World</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/slow-reads/focus/news/the-incorrigible-zulfikar-ali-bhutto-2127616</t>
+          <t>https://www.thedailystar.net/in-focus/news/the-angry-young-world-2033213</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1332,21 +1332,21 @@
         <v>31</v>
       </c>
       <c r="B32" s="2" t="n">
-        <v>44410</v>
+        <v>44263</v>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>Hendrick von der Heifden</t>
+          <t>Mayabee Arannya and Tasnim Odrika</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>'It was like the morning after a nuclear attack'</t>
+          <t>50 years later, the fight goes on</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/slow-reads/focus/news/it-was-the-morning-after-nuclear-attack-2142386</t>
+          <t>https://www.thedailystar.net/in-focus/news/50-years-later-the-fight-goes-2056797</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1360,26 +1360,26 @@
         <v>32</v>
       </c>
       <c r="B33" s="2" t="n">
-        <v>44424</v>
+        <v>44264</v>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>Meghna Guhathakurta</t>
+          <t>Shamsuddoza Sajen</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>Two women, one family, and divided nations</t>
+          <t>Bhashani’s support for non-cooperation movement</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/slow-reads/focus/news/two-women-one-family-and-divided-nations-2152926</t>
+          <t>https://www.thedailystar.net/slow-reads/focus/news/bhashanis-support-non-cooperation-movement-2057441</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Borderline</t>
+          <t>Core</t>
         </is>
       </c>
     </row>
@@ -1388,26 +1388,26 @@
         <v>33</v>
       </c>
       <c r="B34" s="2" t="n">
-        <v>44459</v>
+        <v>44277</v>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>Dr M M Akash</t>
+          <t>Subho Basu</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>Bangabandhu and his unrealised dreams</t>
+          <t>The birth of Bangladesh and nationality question in South Asia</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/slow-reads/focus/news/bangabandhu-and-his-unrealised-dreams-2179521</t>
+          <t>https://www.thedailystar.net/slow-reads/focus/news/the-birth-bangladesh-and-nationality-question-south-asia-2064513</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Borderline</t>
+          <t>Core</t>
         </is>
       </c>
     </row>
@@ -1416,26 +1416,26 @@
         <v>34</v>
       </c>
       <c r="B35" s="2" t="n">
-        <v>44494</v>
+        <v>44283</v>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>Mahbub Uddin Ahmed Bir Bikram</t>
+          <t>Sadia Mahmood</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>Battle Ground Baliadanga- A milestone in our liberation war</t>
+          <t>The 1971 war, caste, citizenship and a war memorial in Tharparkar</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/slow-reads/focus/news/battle-ground-baliadanga-milestone-our-liberation-war-2205411</t>
+          <t>https://www.thedailystar.net/slow-reads/focus/news/the-1971-war-caste-citizenship-and-war-memorial-tharparkar-2067765</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Borderline</t>
         </is>
       </c>
     </row>
@@ -1444,26 +1444,26 @@
         <v>35</v>
       </c>
       <c r="B36" s="2" t="n">
-        <v>44501</v>
+        <v>44284</v>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>Waqar A Khan</t>
+          <t>Thomas Newbold</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>Maj. Gen. Ishfakul Majid: Soldier &amp; Gentleman</t>
+          <t>The Historian and the Riflemen</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/slow-reads/focus/news/maj-gen-ishfakul-majid-soldier-gentleman-2210766</t>
+          <t>https://www.thedailystar.net/in-focus/news/the-historian-and-the-riflemen-2068577</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Borderline</t>
+          <t>Core</t>
         </is>
       </c>
     </row>
@@ -1472,21 +1472,21 @@
         <v>36</v>
       </c>
       <c r="B37" s="2" t="n">
-        <v>44508</v>
+        <v>44305</v>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>Mohammad Afzalur Rahman</t>
+          <t>Waqar A Khan</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>Dhirendranath Dutta: Portrait of a patriot</t>
+          <t>The myth of martial race: Seared into a schoolboy's memory!</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/slow-reads/focus/news/dhirendranath-dutta-portrait-patriot-2224291</t>
+          <t>https://www.thedailystar.net/in-focus/news/the-myth-martial-race-seared-schoolboys-memory-2079653</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1500,26 +1500,26 @@
         <v>37</v>
       </c>
       <c r="B38" s="2" t="n">
-        <v>44529</v>
+        <v>44340</v>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>Salimullah Khan</t>
+          <t>Brig R P Singh, VSM (retired)</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>Mary Frances Dunham: In memoriam</t>
+          <t>How the Mukti Bahini was trained</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/slow-reads/focus/news/mary-frances-dunham-memoriam-2905086</t>
+          <t>https://www.thedailystar.net/in-focus/news/how-the-mukti-bahini-was-trained-2097481</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Borderline</t>
+          <t>Core</t>
         </is>
       </c>
     </row>
@@ -1528,21 +1528,21 @@
         <v>38</v>
       </c>
       <c r="B39" s="2" t="n">
-        <v>44543</v>
+        <v>44361</v>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>V. G. Kiernan</t>
+          <t>Mahbub Uddin Ahmed Bir Bikram</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>The Great Powers Wash Their Hands</t>
+          <t>Remembering the Battle of Bhomra</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/slow-reads/focus/news/the-great-powers-wash-their-hands-2915911</t>
+          <t>https://www.thedailystar.net/in-focus/news/remembering-the-battle-bhomra-2110329</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1556,21 +1556,21 @@
         <v>39</v>
       </c>
       <c r="B40" s="2" t="n">
-        <v>44544</v>
+        <v>44368</v>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>Tanvir Haider Chaudhury</t>
+          <t>Nayanika Mookherjee</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>The country my father wanted</t>
+          <t>History and the Birangona</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/slow-reads/focus/news/the-country-my-father-wanted-2916781</t>
+          <t>https://www.thedailystar.net/in-focus/news/history-and-the-birangona-2114681</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1584,26 +1584,26 @@
         <v>40</v>
       </c>
       <c r="B41" s="2" t="n">
-        <v>44546</v>
+        <v>44389</v>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>Priyam Pritim Paul</t>
+          <t>Waqar A Khan</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>‘I regret that Pakistan has still not formally apologised’</t>
+          <t>The Incorrigible Zulfikar Ali Bhutto</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/slow-reads/focus/news/i-regret-pakistan-has-still-not-formally-apologised-2918031</t>
+          <t>https://www.thedailystar.net/slow-reads/focus/news/the-incorrigible-zulfikar-ali-bhutto-2127616</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Borderline</t>
         </is>
       </c>
     </row>
@@ -1612,26 +1612,26 @@
         <v>41</v>
       </c>
       <c r="B42" s="2" t="n">
-        <v>44585</v>
+        <v>44410</v>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>Subho Basu</t>
+          <t>Hendrick von der Heifden</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>Global Sixties in Bangladesh: Praetorian Guards and Subaltern Resistance</t>
+          <t>'It was like the morning after a nuclear attack'</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/views/in-focus/news/global-sixties-bangladesh-praetorian-guards-and-subaltern-resistance-2945626</t>
+          <t>https://www.thedailystar.net/slow-reads/focus/news/it-was-the-morning-after-nuclear-attack-2142386</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Borderline</t>
+          <t>Core</t>
         </is>
       </c>
     </row>
@@ -1640,26 +1640,26 @@
         <v>42</v>
       </c>
       <c r="B43" s="2" t="n">
-        <v>44592</v>
+        <v>44424</v>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>Mahbub Uddin Ahmed Bir Bikram</t>
+          <t>Meghna Guhathakurta</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>Bangladesh liberation war memories: An Untold Story</t>
+          <t>Two women, one family, and divided nations</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/views/in-focus/news/bangladesh-liberation-war-memories-untold-story-2950696</t>
+          <t>https://www.thedailystar.net/slow-reads/focus/news/two-women-one-family-and-divided-nations-2152926</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Borderline</t>
         </is>
       </c>
     </row>
@@ -1668,21 +1668,21 @@
         <v>43</v>
       </c>
       <c r="B44" s="2" t="n">
-        <v>44599</v>
+        <v>44459</v>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>Mostafa Kamal</t>
+          <t>Dr M M Akash</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>The origin of the Language Movement</t>
+          <t>Bangabandhu and his unrealised dreams</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/slow-reads/focus/news/the-origin-the-language-movement-2955811</t>
+          <t>https://www.thedailystar.net/slow-reads/focus/news/bangabandhu-and-his-unrealised-dreams-2179521</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1696,26 +1696,26 @@
         <v>44</v>
       </c>
       <c r="B45" s="2" t="n">
-        <v>44613</v>
+        <v>44494</v>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>Abul Mansur Ahmad</t>
+          <t>Mahbub Uddin Ahmed Bir Bikram</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>Only Bangla will be our state language</t>
+          <t>Battle Ground Baliadanga- A milestone in our liberation war</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/slow-reads/focus/news/only-bangla-will-be-our-state-language-2966726</t>
+          <t>https://www.thedailystar.net/slow-reads/focus/news/battle-ground-baliadanga-milestone-our-liberation-war-2205411</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Borderline</t>
+          <t>Core</t>
         </is>
       </c>
     </row>
@@ -1724,21 +1724,21 @@
         <v>45</v>
       </c>
       <c r="B46" s="2" t="n">
-        <v>44613</v>
+        <v>44501</v>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>Qazi Motahar Hossain</t>
+          <t>Waqar A Khan</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>State language and East Pakistan’s language issue</t>
+          <t>Maj. Gen. Ishfakul Majid: Soldier &amp; Gentleman</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/slow-reads/focus/news/state-language-and-east-pakistans-language-issue-2966736</t>
+          <t>https://www.thedailystar.net/slow-reads/focus/news/maj-gen-ishfakul-majid-soldier-gentleman-2210766</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -1752,21 +1752,21 @@
         <v>46</v>
       </c>
       <c r="B47" s="2" t="n">
-        <v>44613</v>
+        <v>44508</v>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>Priyam Paul and Shamsuddoza Sajen</t>
+          <t>Mohammad Afzalur Rahman</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>“Most of the commentators are unaware of the importance of the events between 1948 and 1952.”</t>
+          <t>Dhirendranath Dutta: Portrait of a patriot</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/slow-reads/focus/news/most-the-commentators-are-unaware-the-importance-the-events-between-1948-and-1952-2966776</t>
+          <t>https://www.thedailystar.net/slow-reads/focus/news/dhirendranath-dutta-portrait-patriot-2224291</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -1780,21 +1780,21 @@
         <v>47</v>
       </c>
       <c r="B48" s="2" t="n">
-        <v>44620</v>
+        <v>44529</v>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>Waqar A Khan</t>
+          <t>Salimullah Khan</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>The day we made a tryst with destiny!</t>
+          <t>Mary Frances Dunham: In memoriam</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/slow-reads/focus/news/the-day-we-made-tryst-destiny-2972141</t>
+          <t>https://www.thedailystar.net/slow-reads/focus/news/mary-frances-dunham-memoriam-2905086</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -1808,21 +1808,21 @@
         <v>48</v>
       </c>
       <c r="B49" s="2" t="n">
-        <v>44627</v>
+        <v>44543</v>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>Translated by Mumtaz Iqbal</t>
+          <t>V. G. Kiernan</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>Guerrilla operations</t>
+          <t>The Great Powers Wash Their Hands</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/slow-reads/focus/news/guerrilla-operations-2977046</t>
+          <t>https://www.thedailystar.net/slow-reads/focus/news/the-great-powers-wash-their-hands-2915911</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -1836,21 +1836,21 @@
         <v>49</v>
       </c>
       <c r="B50" s="2" t="n">
-        <v>44634</v>
+        <v>44544</v>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>Chaity Das</t>
+          <t>Tanvir Haider Chaudhury</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>Between fiction and testimony: Revisiting the inheritances Liberation War</t>
+          <t>The country my father wanted</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/views/in-focus/news/revisiting-the-inheritances-bangladesh-liberation-war-2982286</t>
+          <t>https://www.thedailystar.net/slow-reads/focus/news/the-country-my-father-wanted-2916781</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -1864,21 +1864,21 @@
         <v>50</v>
       </c>
       <c r="B51" s="2" t="n">
-        <v>44641</v>
+        <v>44546</v>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>Ali Usman Qasmi</t>
+          <t>Priyam Pritim Paul</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>Sorry for what?</t>
+          <t>‘I regret that Pakistan has still not formally apologised’</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/slow-reads/focus/news/sorry-what-2986911</t>
+          <t>https://www.thedailystar.net/slow-reads/focus/news/i-regret-pakistan-has-still-not-formally-apologised-2918031</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -1892,21 +1892,21 @@
         <v>51</v>
       </c>
       <c r="B52" s="2" t="n">
-        <v>44648</v>
+        <v>44571</v>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>Samuel Jaffe</t>
+          <t>Shams Rahman</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>America, Grassroots Activism and the Creation of Bangladesh</t>
+          <t>Bangabandhu’s strategy and our independence</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/views/in-focus/news/america-grassroots-activism-and-the-creation-bangladesh-2992001</t>
+          <t>https://www.thedailystar.net/slow-reads/slow-reads-classics/news/bangabandhus-strategy-and-our-independence-2936171</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -1920,26 +1920,26 @@
         <v>52</v>
       </c>
       <c r="B53" s="2" t="n">
-        <v>44816</v>
+        <v>44585</v>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>Neeti Nair</t>
+          <t>Subho Basu</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>1971 and the case for secularism in Bangladesh and India</t>
+          <t>Global Sixties in Bangladesh: Praetorian Guards and Subaltern Resistance</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/slow-reads/focus/news/1971-and-the-case-secularism-bangladesh-and-india-3117261</t>
+          <t>https://www.thedailystar.net/views/in-focus/news/global-sixties-bangladesh-praetorian-guards-and-subaltern-resistance-2945626</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Borderline</t>
         </is>
       </c>
     </row>
@@ -1948,21 +1948,21 @@
         <v>53</v>
       </c>
       <c r="B54" s="2" t="n">
-        <v>44858</v>
+        <v>44592</v>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>Elora Halim Chowdhury</t>
+          <t>Mahbub Uddin Ahmed Bir Bikram</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>Ethical encounters: A look into women, war, and cinema in Bangladesh</t>
+          <t>Bangladesh liberation war memories: An Untold Story</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/slow-reads/focus/news/ethical-encounters-look-women-war-and-cinema-bangladesh-3150546</t>
+          <t>https://www.thedailystar.net/views/in-focus/news/bangladesh-liberation-war-memories-untold-story-2950696</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -1976,26 +1976,26 @@
         <v>54</v>
       </c>
       <c r="B55" s="2" t="n">
-        <v>44865</v>
+        <v>44599</v>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>Amirul Rajiv</t>
+          <t>Mostafa Kamal</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>Marc Riboud’s Bangladesh 1971: Mourning and Morning</t>
+          <t>The origin of the Language Movement</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/slow-reads/focus/news/marc-ribouds-bangladesh-1971-mourning-and-morning-3156566</t>
+          <t>https://www.thedailystar.net/slow-reads/focus/news/the-origin-the-language-movement-2955811</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Borderline</t>
         </is>
       </c>
     </row>
@@ -2004,26 +2004,26 @@
         <v>55</v>
       </c>
       <c r="B56" s="2" t="n">
-        <v>44900</v>
+        <v>44613</v>
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>Jason Miklian and Scott Carney</t>
+          <t>Abul Mansur Ahmad</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>After the storm</t>
+          <t>Only Bangla will be our state language</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/slow-reads/focus/news/after-the-storm-3187796</t>
+          <t>https://www.thedailystar.net/slow-reads/focus/news/only-bangla-will-be-our-state-language-2966726</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Borderline</t>
         </is>
       </c>
     </row>
@@ -2032,26 +2032,26 @@
         <v>56</v>
       </c>
       <c r="B57" s="2" t="n">
-        <v>44911</v>
+        <v>44613</v>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>Muhammad Mozammel Hussain</t>
+          <t>Qazi Motahar Hossain</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>Instructions to genocide</t>
+          <t>State language and East Pakistan’s language issue</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/slow-reads/focus/news/instructions-genocide-3197291</t>
+          <t>https://www.thedailystar.net/slow-reads/focus/news/state-language-and-east-pakistans-language-issue-2966736</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Borderline</t>
         </is>
       </c>
     </row>
@@ -2060,26 +2060,26 @@
         <v>57</v>
       </c>
       <c r="B58" s="2" t="n">
-        <v>44911</v>
+        <v>44613</v>
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>Amirul Rajiv</t>
+          <t>Priyam Paul and Shamsuddoza Sajen</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>Women photographers of the Bangladesh Liberation War</t>
+          <t>“Most of the commentators are unaware of the importance of the events between 1948 and 1952.”</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/slow-reads/focus/news/women-photographers-the-bangladesh-liberation-war-3197181</t>
+          <t>https://www.thedailystar.net/slow-reads/focus/news/most-the-commentators-are-unaware-the-importance-the-events-between-1948-and-1952-2966776</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Borderline</t>
         </is>
       </c>
     </row>
@@ -2088,26 +2088,26 @@
         <v>58</v>
       </c>
       <c r="B59" s="2" t="n">
-        <v>44914</v>
+        <v>44620</v>
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>Anam Zakaria</t>
+          <t>Waqar A Khan</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>Guarding the silences</t>
+          <t>The day we made a tryst with destiny!</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/slow-reads/focus/news/guarding-the-silences-3199446</t>
+          <t>https://www.thedailystar.net/slow-reads/focus/news/the-day-we-made-tryst-destiny-2972141</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Borderline</t>
         </is>
       </c>
     </row>
@@ -2116,26 +2116,26 @@
         <v>59</v>
       </c>
       <c r="B60" s="2" t="n">
-        <v>44977</v>
+        <v>44627</v>
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>Syed Jamil Ahmed</t>
+          <t>Translated by Mumtaz Iqbal</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>Kabar at 70</t>
+          <t>Guerrilla operations</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/slow-reads/focus/news/kabar-70-3252606</t>
+          <t>https://www.thedailystar.net/slow-reads/focus/news/guerrilla-operations-2977046</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Borderline</t>
+          <t>Core</t>
         </is>
       </c>
     </row>
@@ -2144,21 +2144,21 @@
         <v>60</v>
       </c>
       <c r="B61" s="2" t="n">
-        <v>45005</v>
+        <v>44634</v>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>Debali Mookerjea-Leonard</t>
+          <t>Chaity Das</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>Writing the Good Fight: Women, War, and Jahanara Imam’s Ekattorer Dinguli</t>
+          <t>Between fiction and testimony: Revisiting the inheritances Liberation War</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/slow-reads/focus/news/writing-the-good-fight-women-war-and-jahanara-imams-ekattorer-dinguli-3275561</t>
+          <t>https://www.thedailystar.net/views/in-focus/news/revisiting-the-inheritances-bangladesh-liberation-war-2982286</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2172,21 +2172,21 @@
         <v>61</v>
       </c>
       <c r="B62" s="2" t="n">
-        <v>45012</v>
+        <v>44641</v>
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>Madhurima Sen</t>
+          <t>Ali Usman Qasmi</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>The Liberation War Museum narrating collective trauma</t>
+          <t>Sorry for what?</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/slow-reads/focus/news/the-liberation-war-museum-narrating-collective-trauma-3281601</t>
+          <t>https://www.thedailystar.net/slow-reads/focus/news/sorry-what-2986911</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2200,21 +2200,21 @@
         <v>62</v>
       </c>
       <c r="B63" s="2" t="n">
-        <v>45026</v>
+        <v>44648</v>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>Mahmud Shah Qureshi</t>
+          <t>Samuel Jaffe</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>Honouring André Malraux’s Legacy</t>
+          <t>America, Grassroots Activism and the Creation of Bangladesh</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/slow-reads/focus/news/honouring-andre-malrauxs-legacy-3293296</t>
+          <t>https://www.thedailystar.net/views/in-focus/news/america-grassroots-activism-and-the-creation-bangladesh-2992001</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2228,26 +2228,26 @@
         <v>63</v>
       </c>
       <c r="B64" s="2" t="n">
-        <v>45236</v>
+        <v>44816</v>
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>Mahbub Uddin Ahmed Bir Bikram</t>
+          <t>Neeti Nair</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>The night of unspeakable horror: A survivor’s account</t>
+          <t>1971 and the case for secularism in Bangladesh and India</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/slow-reads/focus/news/the-night-unspeakable-horror-survivors-account-3462816</t>
+          <t>https://www.thedailystar.net/slow-reads/focus/news/1971-and-the-case-secularism-bangladesh-and-india-3117261</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Borderline</t>
+          <t>Core</t>
         </is>
       </c>
     </row>
@@ -2256,21 +2256,21 @@
         <v>64</v>
       </c>
       <c r="B65" s="2" t="n">
-        <v>45276</v>
+        <v>44858</v>
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>Saudia Afrin</t>
+          <t>Elora Halim Chowdhury</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>The Courageous Journey of three sisters</t>
+          <t>Ethical encounters: A look into women, war, and cinema in Bangladesh</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/slow-reads/focus/news/the-courageous-journey-three-sisters-3495476</t>
+          <t>https://www.thedailystar.net/slow-reads/focus/news/ethical-encounters-look-women-war-and-cinema-bangladesh-3150546</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2284,21 +2284,21 @@
         <v>65</v>
       </c>
       <c r="B66" s="2" t="n">
-        <v>45292</v>
+        <v>44865</v>
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>Salimullah Khan</t>
+          <t>Amirul Rajiv</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t>Jasim Uddin’s 1971</t>
+          <t>Marc Riboud’s Bangladesh 1971: Mourning and Morning</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/slow-reads/focus/news/jasim-uddins-1971-3507586</t>
+          <t>https://www.thedailystar.net/slow-reads/focus/news/marc-ribouds-bangladesh-1971-mourning-and-morning-3156566</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2312,26 +2312,26 @@
         <v>66</v>
       </c>
       <c r="B67" s="2" t="n">
-        <v>45343</v>
+        <v>44900</v>
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>Mohammad Afzalur Rahman</t>
+          <t>Jason Miklian and Scott Carney</t>
         </is>
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>How Ekushey was commemorated during the Pakistan period</t>
+          <t>After the storm</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/slow-reads/focus/news/how-ekushey-was-commemorated-during-the-pakistan-period-3549101</t>
+          <t>https://www.thedailystar.net/slow-reads/focus/news/after-the-storm-3187796</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Borderline</t>
+          <t>Core</t>
         </is>
       </c>
     </row>
@@ -2340,21 +2340,21 @@
         <v>67</v>
       </c>
       <c r="B68" s="2" t="n">
-        <v>45355</v>
+        <v>44911</v>
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>Debjani Sengupta</t>
+          <t>Muhammad Mozammel Hussain</t>
         </is>
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>Bangladesh and 1971</t>
+          <t>Instructions to genocide</t>
         </is>
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/slow-reads/focus/news/bangladesh-and-1971-3558381</t>
+          <t>https://www.thedailystar.net/slow-reads/focus/news/instructions-genocide-3197291</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2368,21 +2368,21 @@
         <v>68</v>
       </c>
       <c r="B69" s="2" t="n">
-        <v>45376</v>
+        <v>44911</v>
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>Azizul Rasel</t>
+          <t>Amirul Rajiv</t>
         </is>
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>Silencing the subaltern voice</t>
+          <t>Women photographers of the Bangladesh Liberation War</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/slow-reads/focus/news/silencing-the-subaltern-voice-3574441</t>
+          <t>https://www.thedailystar.net/slow-reads/focus/news/women-photographers-the-bangladesh-liberation-war-3197181</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2396,21 +2396,21 @@
         <v>69</v>
       </c>
       <c r="B70" s="2" t="n">
-        <v>45495</v>
+        <v>44914</v>
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>Rachel Stevens</t>
+          <t>Anam Zakaria</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>Australian involvement in the Bangladesh Liberation War</t>
+          <t>Guarding the silences</t>
         </is>
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/slow-reads/focus/news/australian-involvement-the-bangladesh-liberation-war-3663391</t>
+          <t>https://www.thedailystar.net/slow-reads/focus/news/guarding-the-silences-3199446</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2424,26 +2424,26 @@
         <v>70</v>
       </c>
       <c r="B71" s="2" t="n">
-        <v>45512</v>
+        <v>44977</v>
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>Jason Miklian and Scott Carney</t>
+          <t>Syed Jamil Ahmed</t>
         </is>
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>Concert for Bangladesh</t>
+          <t>Kabar at 70</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/slow-reads/focus/news/concert-bangladesh-3672136</t>
+          <t>https://www.thedailystar.net/slow-reads/focus/news/kabar-70-3252606</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Borderline</t>
         </is>
       </c>
     </row>
@@ -2452,26 +2452,26 @@
         <v>71</v>
       </c>
       <c r="B72" s="2" t="n">
-        <v>45599</v>
+        <v>45005</v>
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>Priyam Pritim Paul</t>
+          <t>Debali Mookerjea-Leonard</t>
         </is>
       </c>
       <c r="D72" s="3" t="inlineStr">
         <is>
-          <t>Blood on the Barred Walls: The 1975 Jail Killing Revisited</t>
+          <t>Writing the Good Fight: Women, War, and Jahanara Imam’s Ekattorer Dinguli</t>
         </is>
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/slow-reads/focus/news/blood-the-barred-walls-the-1975-jail-killing-revisited-3743131</t>
+          <t>https://www.thedailystar.net/slow-reads/focus/news/writing-the-good-fight-women-war-and-jahanara-imams-ekattorer-dinguli-3275561</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Borderline</t>
+          <t>Core</t>
         </is>
       </c>
     </row>
@@ -2480,21 +2480,21 @@
         <v>72</v>
       </c>
       <c r="B73" s="2" t="n">
-        <v>45636</v>
+        <v>45012</v>
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>Azra Rashid</t>
+          <t>Madhurima Sen</t>
         </is>
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>Gender and Genocide in Bangladesh</t>
+          <t>The Liberation War Museum narrating collective trauma</t>
         </is>
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/slow-reads/focus/news/gender-and-genocide-bangladesh-3772441</t>
+          <t>https://www.thedailystar.net/slow-reads/focus/news/the-liberation-war-museum-narrating-collective-trauma-3281601</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2508,21 +2508,21 @@
         <v>73</v>
       </c>
       <c r="B74" s="2" t="n">
-        <v>45640</v>
+        <v>45026</v>
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>Tanvir Haider Chaudhury</t>
+          <t>Mahmud Shah Qureshi</t>
         </is>
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
-          <t>Of 1971, 2024, Rabindranath Tagore and Martyred Intellectuals Day</t>
+          <t>Honouring André Malraux’s Legacy</t>
         </is>
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/slow-reads/focus/news/1971-2024-rabindranath-tagore-and-martyred-intellectuals-day-3775526</t>
+          <t>https://www.thedailystar.net/slow-reads/focus/news/honouring-andre-malrauxs-legacy-3293296</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -2536,26 +2536,26 @@
         <v>74</v>
       </c>
       <c r="B75" s="2" t="n">
-        <v>45640</v>
+        <v>45236</v>
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>Meghna Guhathakurta</t>
+          <t>Mahbub Uddin Ahmed Bir Bikram</t>
         </is>
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>Shilalipi: A Legend Carved in Stone</t>
+          <t>The night of unspeakable horror: A survivor’s account</t>
         </is>
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/slow-reads/focus/news/shilalipi-legend-carved-stone-3775521</t>
+          <t>https://www.thedailystar.net/slow-reads/focus/news/the-night-unspeakable-horror-survivors-account-3462816</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Borderline</t>
         </is>
       </c>
     </row>
@@ -2564,21 +2564,21 @@
         <v>75</v>
       </c>
       <c r="B76" s="2" t="n">
-        <v>45642</v>
+        <v>45276</v>
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>Salimullah Khan</t>
+          <t>Saudia Afrin</t>
         </is>
       </c>
       <c r="D76" s="3" t="inlineStr">
         <is>
-          <t>Intellectuals of Bangladesh in and after 1971</t>
+          <t>The Courageous Journey of three sisters</t>
         </is>
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/slow-reads/focus/news/intellectuals-bangladesh-and-after-1971-3777186</t>
+          <t>https://www.thedailystar.net/slow-reads/focus/news/the-courageous-journey-three-sisters-3495476</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -2592,21 +2592,21 @@
         <v>76</v>
       </c>
       <c r="B77" s="2" t="n">
-        <v>45642</v>
+        <v>45292</v>
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>Ahmad Istiak</t>
+          <t>Salimullah Khan</t>
         </is>
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>Wartime treatment: The heroes who saved lives, silently</t>
+          <t>Jasim Uddin’s 1971</t>
         </is>
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/slow-reads/focus/news/wartime-treatment-the-heroes-who-saved-lives-silently-3777526</t>
+          <t>https://www.thedailystar.net/slow-reads/focus/news/jasim-uddins-1971-3507586</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -2620,21 +2620,21 @@
         <v>77</v>
       </c>
       <c r="B78" s="2" t="n">
-        <v>45705</v>
+        <v>45343</v>
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>Iqra L Qamari</t>
+          <t>Mohammad Afzalur Rahman</t>
         </is>
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>Kamruddin Ahmad: A visionary political thinker we must remember</t>
+          <t>How Ekushey was commemorated during the Pakistan period</t>
         </is>
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/slow-reads/focus/news/kamruddin-ahmad-visionary-political-thinker-we-must-remember-3825991</t>
+          <t>https://www.thedailystar.net/slow-reads/focus/news/how-ekushey-was-commemorated-during-the-pakistan-period-3549101</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -2648,26 +2648,26 @@
         <v>78</v>
       </c>
       <c r="B79" s="2" t="n">
-        <v>45726</v>
+        <v>45355</v>
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>Rehman Sobhan</t>
+          <t>Debjani Sengupta</t>
         </is>
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>Anisur Rahman: Farewell to a fellow traveler</t>
+          <t>Bangladesh and 1971</t>
         </is>
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/slow-reads/focus/news/anisur-rahman-farewell-fellow-traveler-3843641</t>
+          <t>https://www.thedailystar.net/slow-reads/focus/news/bangladesh-and-1971-3558381</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Borderline</t>
+          <t>Core</t>
         </is>
       </c>
     </row>
@@ -2676,21 +2676,21 @@
         <v>79</v>
       </c>
       <c r="B80" s="2" t="n">
-        <v>45740</v>
+        <v>45376</v>
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>Rachel Stevens</t>
+          <t>Azizul Rasel</t>
         </is>
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
-          <t>How Bangladesh gained global legitimacy</t>
+          <t>Silencing the subaltern voice</t>
         </is>
       </c>
       <c r="E80" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/slow-reads/focus/news/how-bangladesh-gained-global-legitimacy-3856236</t>
+          <t>https://www.thedailystar.net/slow-reads/focus/news/silencing-the-subaltern-voice-3574441</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -2704,21 +2704,21 @@
         <v>80</v>
       </c>
       <c r="B81" s="2" t="n">
-        <v>45742</v>
+        <v>45377</v>
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>Leesa Gazi</t>
+          <t>Saudia Afrin</t>
         </is>
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>Birangona Women of Bangladesh</t>
+          <t>March 1971 as witnessed by women</t>
         </is>
       </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/slow-reads/focus/news/birangona-women-bangladesh-3857816</t>
+          <t>https://www.thedailystar.net/slow-reads/slow-reads-special/news/march-1971-witnessed-women-3575141</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -2732,21 +2732,21 @@
         <v>81</v>
       </c>
       <c r="B82" s="2" t="n">
-        <v>45742</v>
+        <v>45495</v>
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>Navine Murshid</t>
+          <t>Rachel Stevens</t>
         </is>
       </c>
       <c r="D82" s="3" t="inlineStr">
         <is>
-          <t>Echoes of exile: Remembering 1971, confronting the Rohingya crisis</t>
+          <t>Australian involvement in the Bangladesh Liberation War</t>
         </is>
       </c>
       <c r="E82" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/slow-reads/slow-reads-special/news/echoes-exile-remembering-1971-confronting-the-rohingya-crisis-3857851</t>
+          <t>https://www.thedailystar.net/slow-reads/focus/news/australian-involvement-the-bangladesh-liberation-war-3663391</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -2760,21 +2760,21 @@
         <v>82</v>
       </c>
       <c r="B83" s="2" t="n">
-        <v>45742</v>
+        <v>45512</v>
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>Azizul Rasel</t>
+          <t>Jason Miklian and Scott Carney</t>
         </is>
       </c>
       <c r="D83" s="3" t="inlineStr">
         <is>
-          <t>‘A huge gulf separates Mujib from Bhutto’</t>
+          <t>Concert for Bangladesh</t>
         </is>
       </c>
       <c r="E83" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/slow-reads/focus/news/huge-gulf-separates-mujib-bhutto-3857841</t>
+          <t>https://www.thedailystar.net/slow-reads/focus/news/concert-bangladesh-3672136</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -2788,26 +2788,26 @@
         <v>83</v>
       </c>
       <c r="B84" s="2" t="n">
-        <v>45859</v>
+        <v>45599</v>
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>Ilyas Chattha</t>
+          <t>Priyam Pritim Paul</t>
         </is>
       </c>
       <c r="D84" s="3" t="inlineStr">
         <is>
-          <t>The crime of being Bengali: The untold story of Bengali internment in Pakistan</t>
+          <t>Blood on the Barred Walls: The 1975 Jail Killing Revisited</t>
         </is>
       </c>
       <c r="E84" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/slow-reads/focus/news/the-crime-being-bengali-the-untold-story-bengali-internment-pakistan-3944131</t>
+          <t>https://www.thedailystar.net/slow-reads/focus/news/blood-the-barred-walls-the-1975-jail-killing-revisited-3743131</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Borderline</t>
         </is>
       </c>
     </row>
@@ -2816,21 +2816,21 @@
         <v>84</v>
       </c>
       <c r="B85" s="2" t="n">
-        <v>45861</v>
+        <v>45636</v>
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>Shuvo Kibria</t>
+          <t>Azra Rashid</t>
         </is>
       </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
-          <t>A man hard to find</t>
+          <t>Gender and Genocide in Bangladesh</t>
         </is>
       </c>
       <c r="E85" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/slow-reads/focus/news/man-hard-find-3945766</t>
+          <t>https://www.thedailystar.net/slow-reads/focus/news/gender-and-genocide-bangladesh-3772441</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -2844,21 +2844,21 @@
         <v>85</v>
       </c>
       <c r="B86" s="2" t="n">
-        <v>45861</v>
+        <v>45640</v>
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>Ahrar Ahmad</t>
+          <t>Tanvir Haider Chaudhury</t>
         </is>
       </c>
       <c r="D86" s="3" t="inlineStr">
         <is>
-          <t>An atypical leader</t>
+          <t>Of 1971, 2024, Rabindranath Tagore and Martyred Intellectuals Day</t>
         </is>
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/slow-reads/focus/news/atypical-leader-3945751</t>
+          <t>https://www.thedailystar.net/slow-reads/focus/news/1971-2024-rabindranath-tagore-and-martyred-intellectuals-day-3775526</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -2872,21 +2872,21 @@
         <v>86</v>
       </c>
       <c r="B87" s="2" t="n">
-        <v>45861</v>
+        <v>45640</v>
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t>Subho Basu</t>
+          <t>Meghna Guhathakurta</t>
         </is>
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
-          <t>An unsung hero: Tajuddin Ahmad and the Bangladesh revolution</t>
+          <t>Shilalipi: A Legend Carved in Stone</t>
         </is>
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/slow-reads/focus/news/unsung-hero-tajuddin-ahmad-and-the-bangladesh-revolution-3945786</t>
+          <t>https://www.thedailystar.net/slow-reads/focus/news/shilalipi-legend-carved-stone-3775521</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -2900,21 +2900,21 @@
         <v>87</v>
       </c>
       <c r="B88" s="2" t="n">
-        <v>45861</v>
+        <v>45642</v>
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>Syeda Zohra Tajuddin</t>
+          <t>Salimullah Khan</t>
         </is>
       </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
-          <t>On the path of dawn</t>
+          <t>Intellectuals of Bangladesh in and after 1971</t>
         </is>
       </c>
       <c r="E88" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/slow-reads/focus/news/the-path-dawn-3945556</t>
+          <t>https://www.thedailystar.net/slow-reads/focus/news/intellectuals-bangladesh-and-after-1971-3777186</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -2928,21 +2928,21 @@
         <v>88</v>
       </c>
       <c r="B89" s="2" t="n">
-        <v>45861</v>
+        <v>45642</v>
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t>Serajul Islam Choudhury</t>
+          <t>Ahmad Istiak</t>
         </is>
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t>Our finest representative of liberal politics</t>
+          <t>Wartime treatment: The heroes who saved lives, silently</t>
         </is>
       </c>
       <c r="E89" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/slow-reads/focus/news/our-finest-representative-liberal-politics-3945816</t>
+          <t>https://www.thedailystar.net/slow-reads/focus/news/wartime-treatment-the-heroes-who-saved-lives-silently-3777526</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -2956,21 +2956,21 @@
         <v>89</v>
       </c>
       <c r="B90" s="2" t="n">
-        <v>45861</v>
+        <v>45705</v>
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t>Taj Iman Ahmad Ibn Munir</t>
+          <t>Iqra L Qamari</t>
         </is>
       </c>
       <c r="D90" s="3" t="inlineStr">
         <is>
-          <t>Our moral inheritance Tajuddin Ahmad’s call to national conscience</t>
+          <t>Kamruddin Ahmad: A visionary political thinker we must remember</t>
         </is>
       </c>
       <c r="E90" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/slow-reads/focus/news/our-moral-inheritance-tajuddin-ahmads-call-national-conscience-3945771</t>
+          <t>https://www.thedailystar.net/slow-reads/focus/news/kamruddin-ahmad-visionary-political-thinker-we-must-remember-3825991</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -2984,21 +2984,21 @@
         <v>90</v>
       </c>
       <c r="B91" s="2" t="n">
-        <v>45861</v>
+        <v>45726</v>
       </c>
       <c r="C91" s="3" t="inlineStr">
         <is>
-          <t>Selim Jahan</t>
+          <t>Rehman Sobhan</t>
         </is>
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
-          <t>Reading his diaries and understanding the man</t>
+          <t>Anisur Rahman: Farewell to a fellow traveler</t>
         </is>
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/slow-reads/focus/news/reading-his-diaries-and-understanding-the-man-3945776</t>
+          <t>https://www.thedailystar.net/slow-reads/focus/news/anisur-rahman-farewell-fellow-traveler-3843641</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3012,21 +3012,21 @@
         <v>91</v>
       </c>
       <c r="B92" s="2" t="n">
-        <v>45861</v>
+        <v>45740</v>
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t>Dr Kamal Hossain</t>
+          <t>Rachel Stevens</t>
         </is>
       </c>
       <c r="D92" s="3" t="inlineStr">
         <is>
-          <t>Remembering Tajuddin Bhai</t>
+          <t>How Bangladesh gained global legitimacy</t>
         </is>
       </c>
       <c r="E92" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/slow-reads/focus/news/remembering-tajuddin-bhai-3945836</t>
+          <t>https://www.thedailystar.net/slow-reads/focus/news/how-bangladesh-gained-global-legitimacy-3856236</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3040,26 +3040,26 @@
         <v>92</v>
       </c>
       <c r="B93" s="2" t="n">
-        <v>45861</v>
+        <v>45742</v>
       </c>
       <c r="C93" s="3" t="inlineStr">
         <is>
-          <t>Priyam Paul</t>
+          <t>Leesa Gazi</t>
         </is>
       </c>
       <c r="D93" s="3" t="inlineStr">
         <is>
-          <t>Self and Society: Tajuddin’s formative years</t>
+          <t>Birangona Women of Bangladesh</t>
         </is>
       </c>
       <c r="E93" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/slow-reads/focus/news/self-and-society-tajuddins-formative-years-3945571</t>
+          <t>https://www.thedailystar.net/slow-reads/focus/news/birangona-women-bangladesh-3857816</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Borderline</t>
+          <t>Core</t>
         </is>
       </c>
     </row>
@@ -3068,21 +3068,21 @@
         <v>93</v>
       </c>
       <c r="B94" s="2" t="n">
-        <v>45861</v>
+        <v>45742</v>
       </c>
       <c r="C94" s="3" t="inlineStr">
         <is>
-          <t>Mofidul Hoque</t>
+          <t>Navine Murshid</t>
         </is>
       </c>
       <c r="D94" s="3" t="inlineStr">
         <is>
-          <t>Tajuddin Ahmad man who shaped history</t>
+          <t>Echoes of exile: Remembering 1971, confronting the Rohingya crisis</t>
         </is>
       </c>
       <c r="E94" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/slow-reads/focus/news/tajuddin-ahmad-man-who-shaped-history-3945746</t>
+          <t>https://www.thedailystar.net/slow-reads/slow-reads-special/news/echoes-exile-remembering-1971-confronting-the-rohingya-crisis-3857851</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3096,21 +3096,21 @@
         <v>94</v>
       </c>
       <c r="B95" s="2" t="n">
-        <v>45861</v>
+        <v>45742</v>
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t>Morshed Shafiul Hasan</t>
+          <t>Azizul Rasel</t>
         </is>
       </c>
       <c r="D95" s="3" t="inlineStr">
         <is>
-          <t>Tajuddin’s unfinished revolution</t>
+          <t>‘A huge gulf separates Mujib from Bhutto’</t>
         </is>
       </c>
       <c r="E95" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/slow-reads/focus/news/tajuddins-unfinished-revolution-3945566</t>
+          <t>https://www.thedailystar.net/slow-reads/focus/news/huge-gulf-separates-mujib-bhutto-3857841</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3124,21 +3124,21 @@
         <v>95</v>
       </c>
       <c r="B96" s="2" t="n">
-        <v>45861</v>
+        <v>45859</v>
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t>K A S Murshid</t>
+          <t>Ilyas Chattha</t>
         </is>
       </c>
       <c r="D96" s="3" t="inlineStr">
         <is>
-          <t>The forgotten luminary of Bangladesh’s liberation war</t>
+          <t>The crime of being Bengali: The untold story of Bengali internment in Pakistan</t>
         </is>
       </c>
       <c r="E96" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/slow-reads/focus/news/the-forgotten-luminary-bangladeshs-liberation-war-3945801</t>
+          <t>https://www.thedailystar.net/slow-reads/focus/news/the-crime-being-bengali-the-untold-story-bengali-internment-pakistan-3944131</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3156,17 +3156,17 @@
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t>Priyam Paul</t>
+          <t>Shuvo Kibria</t>
         </is>
       </c>
       <c r="D97" s="3" t="inlineStr">
         <is>
-          <t>‘Tajuddin Ahmad seems like a Greek tragic hero who had all the great qualities but destiny was against him’</t>
+          <t>A man hard to find</t>
         </is>
       </c>
       <c r="E97" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/slow-reads/focus/news/tajuddin-ahmad-seems-greek-tragic-hero-who-had-all-the-great-qualities-destiny-was-against-him-3945761</t>
+          <t>https://www.thedailystar.net/slow-reads/focus/news/man-hard-find-3945766</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3184,17 +3184,17 @@
       </c>
       <c r="C98" s="3" t="inlineStr">
         <is>
-          <t>Priyam Paul</t>
+          <t>Ahrar Ahmad</t>
         </is>
       </c>
       <c r="D98" s="3" t="inlineStr">
         <is>
-          <t>‘Tajuddin was objective, fact-based — quite unlike many other Awami League leaders’: Muyeedul Hasan</t>
+          <t>An atypical leader</t>
         </is>
       </c>
       <c r="E98" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/slow-reads/focus/news/tajuddin-was-objective-fact-based-quite-unlike-many-other-awami-league-leaders-muyeedul-hasan-3945811</t>
+          <t>https://www.thedailystar.net/slow-reads/focus/news/atypical-leader-3945751</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3212,17 +3212,17 @@
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t>Priyam Paul</t>
+          <t>Subho Basu</t>
         </is>
       </c>
       <c r="D99" s="3" t="inlineStr">
         <is>
-          <t>‘Tajuddin’s place in history should be seen in terms of his wartime leadership’</t>
+          <t>An unsung hero: Tajuddin Ahmad and the Bangladesh revolution</t>
         </is>
       </c>
       <c r="E99" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/slow-reads/focus/news/tajuddins-place-history-should-be-seen-terms-his-wartime-leadership-3945551</t>
+          <t>https://www.thedailystar.net/slow-reads/focus/news/unsung-hero-tajuddin-ahmad-and-the-bangladesh-revolution-3945786</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3240,17 +3240,17 @@
       </c>
       <c r="C100" s="3" t="inlineStr">
         <is>
-          <t>Miftahul Jannat and Priyam Paul</t>
+          <t>Syeda Zohra Tajuddin</t>
         </is>
       </c>
       <c r="D100" s="3" t="inlineStr">
         <is>
-          <t>‘The trial of the jail killing case should be reopened’</t>
+          <t>On the path of dawn</t>
         </is>
       </c>
       <c r="E100" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/slow-reads/focus/news/the-trial-the-jail-killing-case-should-be-reopened-3945756</t>
+          <t>https://www.thedailystar.net/slow-reads/focus/news/the-path-dawn-3945556</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3264,26 +3264,26 @@
         <v>100</v>
       </c>
       <c r="B101" s="2" t="n">
-        <v>45915</v>
+        <v>45861</v>
       </c>
       <c r="C101" s="3" t="inlineStr">
         <is>
-          <t>Bidhan Rebeiro</t>
+          <t>Serajul Islam Choudhury</t>
         </is>
       </c>
       <c r="D101" s="3" t="inlineStr">
         <is>
-          <t>Why Zahir Raihan matters more than ever after the August uprising</t>
+          <t>Our finest representative of liberal politics</t>
         </is>
       </c>
       <c r="E101" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/slow-reads/focus/news/why-zahir-raihan-matters-more-ever-after-the-august-uprising-3986446</t>
+          <t>https://www.thedailystar.net/slow-reads/focus/news/our-finest-representative-liberal-politics-3945816</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Borderline</t>
+          <t>Core</t>
         </is>
       </c>
     </row>
@@ -3292,26 +3292,26 @@
         <v>101</v>
       </c>
       <c r="B102" s="2" t="n">
-        <v>45964</v>
+        <v>45861</v>
       </c>
       <c r="C102" s="3" t="inlineStr">
         <is>
-          <t>Cynthia Farid</t>
+          <t>Taj Iman Ahmad Ibn Munir</t>
         </is>
       </c>
       <c r="D102" s="3" t="inlineStr">
         <is>
-          <t>The Last Republican</t>
+          <t>Our moral inheritance Tajuddin Ahmad’s call to national conscience</t>
         </is>
       </c>
       <c r="E102" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/slow-reads/focus/news/the-last-republican-4026026</t>
+          <t>https://www.thedailystar.net/slow-reads/focus/news/our-moral-inheritance-tajuddin-ahmads-call-national-conscience-3945771</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Borderline</t>
         </is>
       </c>
     </row>
@@ -3320,26 +3320,26 @@
         <v>102</v>
       </c>
       <c r="B103" s="2" t="n">
-        <v>45971</v>
+        <v>45861</v>
       </c>
       <c r="C103" s="3" t="inlineStr">
         <is>
-          <t>Sultan Mehmood and Ahmed Mushfiq Mobarak</t>
+          <t>Selim Jahan</t>
         </is>
       </c>
       <c r="D103" s="3" t="inlineStr">
         <is>
-          <t>The Bhola Cyclone and the making of Bangladesh</t>
+          <t>Reading his diaries and understanding the man</t>
         </is>
       </c>
       <c r="E103" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/slow-reads/focus/news/the-bhola-cyclone-and-the-making-bangladesh-4031136</t>
+          <t>https://www.thedailystar.net/slow-reads/focus/news/reading-his-diaries-and-understanding-the-man-3945776</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Borderline</t>
         </is>
       </c>
     </row>
@@ -3348,26 +3348,26 @@
         <v>103</v>
       </c>
       <c r="B104" s="2" t="n">
-        <v>45978</v>
+        <v>45861</v>
       </c>
       <c r="C104" s="3" t="inlineStr">
         <is>
-          <t>Shahadat Parvez</t>
+          <t>Dr Kamal Hossain</t>
         </is>
       </c>
       <c r="D104" s="3" t="inlineStr">
         <is>
-          <t>Bhashani and the gayebi janazah of 1968: A photographic history</t>
+          <t>Remembering Tajuddin Bhai</t>
         </is>
       </c>
       <c r="E104" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/slow-reads/focus/news/bhashani-and-the-gayebi-janazah-1968-photographic-history-4036841</t>
+          <t>https://www.thedailystar.net/slow-reads/focus/news/remembering-tajuddin-bhai-3945836</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Borderline</t>
+          <t>Core</t>
         </is>
       </c>
     </row>
@@ -3376,21 +3376,21 @@
         <v>104</v>
       </c>
       <c r="B105" s="2" t="n">
-        <v>45985</v>
+        <v>45861</v>
       </c>
       <c r="C105" s="3" t="inlineStr">
         <is>
-          <t>Serajul Islam Choudhury</t>
+          <t>Priyam Paul</t>
         </is>
       </c>
       <c r="D105" s="3" t="inlineStr">
         <is>
-          <t>Remembering Munier Bhai</t>
+          <t>Self and Society: Tajuddin’s formative years</t>
         </is>
       </c>
       <c r="E105" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/slow-reads/focus/news/remembering-munier-bhai-4042036</t>
+          <t>https://www.thedailystar.net/slow-reads/focus/news/self-and-society-tajuddins-formative-years-3945571</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -3404,21 +3404,21 @@
         <v>105</v>
       </c>
       <c r="B106" s="2" t="n">
-        <v>45992</v>
+        <v>45861</v>
       </c>
       <c r="C106" s="3" t="inlineStr">
         <is>
-          <t>Ansar Ahmed Ullah</t>
+          <t>Mofidul Hoque</t>
         </is>
       </c>
       <c r="D106" s="3" t="inlineStr">
         <is>
-          <t>A British witness to Bangladesh genocide: Val Harding’s 1971 story</t>
+          <t>Tajuddin Ahmad man who shaped history</t>
         </is>
       </c>
       <c r="E106" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/slow-reads/focus/news/british-witness-bangladesh-genocide-val-hardings-1971-story-4047561</t>
+          <t>https://www.thedailystar.net/slow-reads/focus/news/tajuddin-ahmad-man-who-shaped-history-3945746</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -3432,21 +3432,21 @@
         <v>106</v>
       </c>
       <c r="B107" s="2" t="n">
-        <v>46003</v>
+        <v>45861</v>
       </c>
       <c r="C107" s="3" t="inlineStr">
         <is>
-          <t>Shahadat Parvez</t>
+          <t>Morshed Shafiul Hasan</t>
         </is>
       </c>
       <c r="D107" s="3" t="inlineStr">
         <is>
-          <t>The untold story behind 1971’s two most haunting photographs</t>
+          <t>Tajuddin’s unfinished revolution</t>
         </is>
       </c>
       <c r="E107" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/slow-reads/focus/news/the-untold-story-behind-1971s-two-most-haunting-photographs-4056081</t>
+          <t>https://www.thedailystar.net/slow-reads/focus/news/tajuddins-unfinished-revolution-3945566</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -3460,21 +3460,21 @@
         <v>107</v>
       </c>
       <c r="B108" s="2" t="n">
-        <v>46007</v>
+        <v>45861</v>
       </c>
       <c r="C108" s="3" t="inlineStr">
         <is>
-          <t>Minhazul Islam</t>
+          <t>K A S Murshid</t>
         </is>
       </c>
       <c r="D108" s="3" t="inlineStr">
         <is>
-          <t>American doctors who exposed the Nixon-Kissinger lies</t>
+          <t>The forgotten luminary of Bangladesh’s liberation war</t>
         </is>
       </c>
       <c r="E108" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/slow-reads/focus/news/american-doctors-who-exposed-the-nixon-kissinger-lies-4059096</t>
+          <t>https://www.thedailystar.net/slow-reads/focus/news/the-forgotten-luminary-bangladeshs-liberation-war-3945801</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -3488,21 +3488,21 @@
         <v>108</v>
       </c>
       <c r="B109" s="2" t="n">
-        <v>46007</v>
+        <v>45861</v>
       </c>
       <c r="C109" s="3" t="inlineStr">
         <is>
-          <t>Miftahul Jannat</t>
+          <t>Priyam Paul</t>
         </is>
       </c>
       <c r="D109" s="3" t="inlineStr">
         <is>
-          <t>How music carried Bangladesh’s struggle to the world</t>
+          <t>‘Tajuddin Ahmad seems like a Greek tragic hero who had all the great qualities but destiny was against him’</t>
         </is>
       </c>
       <c r="E109" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/slow-reads/focus/news/how-music-carried-bangladeshs-struggle-the-world-4059121</t>
+          <t>https://www.thedailystar.net/slow-reads/focus/news/tajuddin-ahmad-seems-greek-tragic-hero-who-had-all-the-great-qualities-destiny-was-against-him-3945761</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -3516,21 +3516,21 @@
         <v>109</v>
       </c>
       <c r="B110" s="2" t="n">
-        <v>46007</v>
+        <v>45861</v>
       </c>
       <c r="C110" s="3" t="inlineStr">
         <is>
-          <t>Ahmad Istiak</t>
+          <t>Priyam Paul</t>
         </is>
       </c>
       <c r="D110" s="3" t="inlineStr">
         <is>
-          <t>The art lover who stole The Love Letter for Bangladesh’s freedom</t>
+          <t>‘Tajuddin was objective, fact-based — quite unlike many other Awami League leaders’: Muyeedul Hasan</t>
         </is>
       </c>
       <c r="E110" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/slow-reads/focus/news/the-art-lover-who-stole-the-love-letter-bangladeshs-freedom-4059101</t>
+          <t>https://www.thedailystar.net/slow-reads/focus/news/tajuddin-was-objective-fact-based-quite-unlike-many-other-awami-league-leaders-muyeedul-hasan-3945811</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -3544,26 +3544,26 @@
         <v>110</v>
       </c>
       <c r="B111" s="2" t="n">
-        <v>46016</v>
+        <v>45861</v>
       </c>
       <c r="C111" s="3" t="inlineStr">
         <is>
-          <t>AKM Zakaria, Manoj Dey</t>
+          <t>Priyam Paul</t>
         </is>
       </c>
       <c r="D111" s="3" t="inlineStr">
         <is>
-          <t>Anti-Liberation War forces have taken advantage of the failure of democracy</t>
+          <t>‘Tajuddin’s place in history should be seen in terms of his wartime leadership’</t>
         </is>
       </c>
       <c r="E111" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/slow-reads/focus/news/anti-liberation-war-forces-have-taken-advantage-the-failure-democracy-4065701</t>
+          <t>https://www.thedailystar.net/slow-reads/focus/news/tajuddins-place-history-should-be-seen-terms-his-wartime-leadership-3945551</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Borderline</t>
+          <t>Core</t>
         </is>
       </c>
     </row>
@@ -3572,26 +3572,26 @@
         <v>111</v>
       </c>
       <c r="B112" s="2" t="n">
-        <v>46033</v>
+        <v>45861</v>
       </c>
       <c r="C112" s="3" t="inlineStr">
         <is>
-          <t>Shahadat Parvez</t>
+          <t>Miftahul Jannat and Priyam Paul</t>
         </is>
       </c>
       <c r="D112" s="3" t="inlineStr">
         <is>
-          <t>Amanul Huq: The romantic documentarian</t>
+          <t>‘The trial of the jail killing case should be reopened’</t>
         </is>
       </c>
       <c r="E112" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/slow-reads/focus/news/amanul-huq-the-romantic-documentarian-4078731</t>
+          <t>https://www.thedailystar.net/slow-reads/focus/news/the-trial-the-jail-killing-case-should-be-reopened-3945756</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Borderline</t>
+          <t>Core</t>
         </is>
       </c>
     </row>
@@ -3600,21 +3600,21 @@
         <v>112</v>
       </c>
       <c r="B113" s="2" t="n">
-        <v>46054</v>
+        <v>45915</v>
       </c>
       <c r="C113" s="3" t="inlineStr">
         <is>
-          <t>Naeem Mohaiemen</t>
+          <t>Bidhan Rebeiro</t>
         </is>
       </c>
       <c r="D113" s="3" t="inlineStr">
         <is>
-          <t>Raihan-Ghatak-Tarkovsky: We shall search, we shall find</t>
+          <t>Why Zahir Raihan matters more than ever after the August uprising</t>
         </is>
       </c>
       <c r="E113" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/slow-reads/focus/news/raihan-ghatak-tarkovsky-we-shall-search-we-shall-find-4096101</t>
+          <t>https://www.thedailystar.net/slow-reads/focus/news/why-zahir-raihan-matters-more-ever-after-the-august-uprising-3986446</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -3628,26 +3628,26 @@
         <v>113</v>
       </c>
       <c r="B114" s="2" t="n">
-        <v>46055</v>
+        <v>45964</v>
       </c>
       <c r="C114" s="3" t="inlineStr">
         <is>
-          <t>Bulbul Hasan</t>
+          <t>Cynthia Farid</t>
         </is>
       </c>
       <c r="D114" s="3" t="inlineStr">
         <is>
-          <t>Between memory and truth: Mark Tully and the Bangladesh he witnessed</t>
+          <t>The Last Republican</t>
         </is>
       </c>
       <c r="E114" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/slow-reads/focus/news/between-memory-and-truth-mark-tully-and-the-bangladesh-he-witnessed-4096631</t>
+          <t>https://www.thedailystar.net/slow-reads/focus/news/the-last-republican-4026026</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Borderline</t>
+          <t>Core</t>
         </is>
       </c>
     </row>
@@ -3656,26 +3656,26 @@
         <v>114</v>
       </c>
       <c r="B115" s="2" t="n">
-        <v>46070</v>
+        <v>45971</v>
       </c>
       <c r="C115" s="3" t="inlineStr">
         <is>
-          <t>Samia Huda</t>
+          <t>Sultan Mehmood and Ahmed Mushfiq Mobarak</t>
         </is>
       </c>
       <c r="D115" s="3" t="inlineStr">
         <is>
-          <t>Amar Ekushey: Before Bangla became a demand</t>
+          <t>The Bhola Cyclone and the making of Bangladesh</t>
         </is>
       </c>
       <c r="E115" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/slow-reads/focus/news/amar-ekushey-bangla-became-demand-4108021</t>
+          <t>https://www.thedailystar.net/slow-reads/focus/news/the-bhola-cyclone-and-the-making-bangladesh-4031136</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Borderline</t>
+          <t>Core</t>
         </is>
       </c>
     </row>
@@ -3684,21 +3684,21 @@
         <v>115</v>
       </c>
       <c r="B116" s="2" t="n">
-        <v>46074</v>
+        <v>45978</v>
       </c>
       <c r="C116" s="3" t="inlineStr">
         <is>
-          <t>Rahat Minhaz</t>
+          <t>Shahadat Parvez</t>
         </is>
       </c>
       <c r="D116" s="3" t="inlineStr">
         <is>
-          <t>Ekushey in the Mirror of Azad</t>
+          <t>Bhashani and the gayebi janazah of 1968: A photographic history</t>
         </is>
       </c>
       <c r="E116" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/slow-reads/focus/news/ekushey-the-mirror-azad-4111286</t>
+          <t>https://www.thedailystar.net/slow-reads/focus/news/bhashani-and-the-gayebi-janazah-1968-photographic-history-4036841</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -3712,21 +3712,21 @@
         <v>116</v>
       </c>
       <c r="B117" s="2" t="n">
-        <v>46075</v>
+        <v>45985</v>
       </c>
       <c r="C117" s="3" t="inlineStr">
         <is>
-          <t>Shahadat Parvez</t>
+          <t>Serajul Islam Choudhury</t>
         </is>
       </c>
       <c r="D117" s="3" t="inlineStr">
         <is>
-          <t>Capturing the Language Movement: Rafiqul's rare archive</t>
+          <t>Remembering Munier Bhai</t>
         </is>
       </c>
       <c r="E117" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/slow-reads/focus/news/capturing-the-language-movement-rafiquls-rare-archive-4112011</t>
+          <t>https://www.thedailystar.net/slow-reads/focus/news/remembering-munier-bhai-4042036</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -3740,21 +3740,21 @@
         <v>117</v>
       </c>
       <c r="B118" s="2" t="n">
-        <v>46084</v>
+        <v>45992</v>
       </c>
       <c r="C118" s="3" t="inlineStr">
         <is>
-          <t>Sayem Bin Rafiq</t>
+          <t>Ansar Ahmed Ullah</t>
         </is>
       </c>
       <c r="D118" s="3" t="inlineStr">
         <is>
-          <t>The Australian doctor who witnessed what Bangladesh wanted to forget</t>
+          <t>A British witness to Bangladesh genocide: Val Harding’s 1971 story</t>
         </is>
       </c>
       <c r="E118" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/slow-reads/focus/news/the-australian-doctor-who-witnessed-what-bangladesh-wanted-forget-4118701</t>
+          <t>https://www.thedailystar.net/slow-reads/focus/news/british-witness-bangladesh-genocide-val-hardings-1971-story-4047561</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -3768,21 +3768,21 @@
         <v>118</v>
       </c>
       <c r="B119" s="2" t="n">
-        <v>46097</v>
+        <v>46003</v>
       </c>
       <c r="C119" s="3" t="inlineStr">
         <is>
-          <t>Sultana Kamal</t>
+          <t>Shahadat Parvez</t>
         </is>
       </c>
       <c r="D119" s="3" t="inlineStr">
         <is>
-          <t>My mother’s letter during the Liberation War</t>
+          <t>The untold story behind 1971’s two most haunting photographs</t>
         </is>
       </c>
       <c r="E119" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/slow-reads/focus/news/my-mothers-letter-during-the-liberation-war-4129891</t>
+          <t>https://www.thedailystar.net/slow-reads/focus/news/the-untold-story-behind-1971s-two-most-haunting-photographs-4056081</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -3796,26 +3796,26 @@
         <v>119</v>
       </c>
       <c r="B120" s="2" t="n">
-        <v>46098</v>
+        <v>46007</v>
       </c>
       <c r="C120" s="3" t="inlineStr">
         <is>
-          <t>Faruq Choudhury</t>
+          <t>Minhazul Islam</t>
         </is>
       </c>
       <c r="D120" s="3" t="inlineStr">
         <is>
-          <t>Bangabandhu and the world</t>
+          <t>American doctors who exposed the Nixon-Kissinger lies</t>
         </is>
       </c>
       <c r="E120" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/slow-reads/slow-reads-classics/news/bangabandhu-and-the-world-4131081</t>
+          <t>https://www.thedailystar.net/slow-reads/focus/news/american-doctors-who-exposed-the-nixon-kissinger-lies-4059096</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Borderline</t>
+          <t>Core</t>
         </is>
       </c>
     </row>
@@ -3824,21 +3824,21 @@
         <v>120</v>
       </c>
       <c r="B121" s="2" t="n">
-        <v>46098</v>
+        <v>46007</v>
       </c>
       <c r="C121" s="3" t="inlineStr">
         <is>
-          <t>Madhurima Sen</t>
+          <t>Miftahul Jannat</t>
         </is>
       </c>
       <c r="D121" s="3" t="inlineStr">
         <is>
-          <t>How does Pakistan write 1971?</t>
+          <t>How music carried Bangladesh’s struggle to the world</t>
         </is>
       </c>
       <c r="E121" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/slow-reads/focus/news/how-does-pakistan-write-1971-4130621</t>
+          <t>https://www.thedailystar.net/slow-reads/focus/news/how-music-carried-bangladeshs-struggle-the-world-4059121</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -3852,21 +3852,21 @@
         <v>121</v>
       </c>
       <c r="B122" s="2" t="n">
-        <v>46099</v>
+        <v>46007</v>
       </c>
       <c r="C122" s="3" t="inlineStr">
         <is>
-          <t>Rehman Sobhan</t>
+          <t>Ahmad Istiak</t>
         </is>
       </c>
       <c r="D122" s="3" t="inlineStr">
         <is>
-          <t>Prelude to an order for genocide</t>
+          <t>The art lover who stole The Love Letter for Bangladesh’s freedom</t>
         </is>
       </c>
       <c r="E122" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/slow-reads/slow-reads-classics/prelude-order-genocide-4554</t>
+          <t>https://www.thedailystar.net/slow-reads/focus/news/the-art-lover-who-stole-the-love-letter-bangladeshs-freedom-4059101</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -3880,26 +3880,26 @@
         <v>122</v>
       </c>
       <c r="B123" s="2" t="n">
-        <v>46106</v>
+        <v>46016</v>
       </c>
       <c r="C123" s="3" t="inlineStr">
         <is>
-          <t>Miftahul Jannat</t>
+          <t>AKM Zakaria, Manoj Dey</t>
         </is>
       </c>
       <c r="D123" s="3" t="inlineStr">
         <is>
-          <t>Echoes of Anne Frank in Swati’s war diary</t>
+          <t>Anti-Liberation War forces have taken advantage of the failure of democracy</t>
         </is>
       </c>
       <c r="E123" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/slow-reads/focus/news/echoes-anne-frank-swatis-war-diary-4135246</t>
+          <t>https://www.thedailystar.net/slow-reads/focus/news/anti-liberation-war-forces-have-taken-advantage-the-failure-democracy-4065701</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Borderline</t>
         </is>
       </c>
     </row>
@@ -3908,21 +3908,21 @@
         <v>123</v>
       </c>
       <c r="B124" s="2" t="n">
-        <v>46106</v>
+        <v>46028</v>
       </c>
       <c r="C124" s="3" t="inlineStr">
         <is>
-          <t>Rahat Minhaz</t>
+          <t>Sumaiya Ferdous</t>
         </is>
       </c>
       <c r="D124" s="3" t="inlineStr">
         <is>
-          <t>Genesis of a genocide report</t>
+          <t>Living in occupied Dhaka: Diaries from 1971</t>
         </is>
       </c>
       <c r="E124" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/slow-reads/focus/news/genesis-genocide-report-4134546</t>
+          <t>https://www.thedailystar.net/slow-reads/focus/news/living-occupied-dhaka-diaries-1971-4074711</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -3936,26 +3936,26 @@
         <v>124</v>
       </c>
       <c r="B125" s="2" t="n">
-        <v>46106</v>
+        <v>46033</v>
       </c>
       <c r="C125" s="3" t="inlineStr">
         <is>
-          <t>Ystiaque Ahmed</t>
+          <t>Shahadat Parvez</t>
         </is>
       </c>
       <c r="D125" s="3" t="inlineStr">
         <is>
-          <t>The naval hero who envisioned a nation</t>
+          <t>Amanul Huq: The romantic documentarian</t>
         </is>
       </c>
       <c r="E125" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/slow-reads/focus/news/the-naval-hero-who-envisioned-nation-4135206</t>
+          <t>https://www.thedailystar.net/slow-reads/focus/news/amanul-huq-the-romantic-documentarian-4078731</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Borderline</t>
         </is>
       </c>
     </row>
@@ -3964,26 +3964,26 @@
         <v>125</v>
       </c>
       <c r="B126" s="2" t="n">
-        <v>46107</v>
+        <v>46054</v>
       </c>
       <c r="C126" s="3" t="inlineStr">
         <is>
-          <t>SB Meraj</t>
+          <t>Naeem Mohaiemen</t>
         </is>
       </c>
       <c r="D126" s="3" t="inlineStr">
         <is>
-          <t>The black flag at Rajshahi and the officer who chose conscience</t>
+          <t>Raihan-Ghatak-Tarkovsky: We shall search, we shall find</t>
         </is>
       </c>
       <c r="E126" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/slow-reads/focus/news/the-black-flag-rajshahi-and-the-officer-who-chose-conscience-4135981</t>
+          <t>https://www.thedailystar.net/slow-reads/focus/news/raihan-ghatak-tarkovsky-we-shall-search-we-shall-find-4096101</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Borderline</t>
         </is>
       </c>
     </row>
@@ -3992,26 +3992,26 @@
         <v>126</v>
       </c>
       <c r="B127" s="2" t="n">
-        <v>46108</v>
+        <v>46055</v>
       </c>
       <c r="C127" s="3" t="inlineStr">
         <is>
-          <t>Shaila Shobnam</t>
+          <t>Bulbul Hasan</t>
         </is>
       </c>
       <c r="D127" s="3" t="inlineStr">
         <is>
-          <t>How Pakistan saw 1971: Inside the Hamoodur Rehman Commission Report</t>
+          <t>Between memory and truth: Mark Tully and the Bangladesh he witnessed</t>
         </is>
       </c>
       <c r="E127" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/slow-reads/big-picture/news/how-pakistan-saw-1971-inside-the-hamoodur-rehman-commission-report-4137001</t>
+          <t>https://www.thedailystar.net/slow-reads/focus/news/between-memory-and-truth-mark-tully-and-the-bangladesh-he-witnessed-4096631</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Borderline</t>
         </is>
       </c>
     </row>
@@ -4020,21 +4020,21 @@
         <v>127</v>
       </c>
       <c r="B128" s="2" t="n">
-        <v>46112</v>
+        <v>46070</v>
       </c>
       <c r="C128" s="3" t="inlineStr">
         <is>
-          <t>Priyam Pritim Paul</t>
+          <t>Samia Huda</t>
         </is>
       </c>
       <c r="D128" s="3" t="inlineStr">
         <is>
-          <t>Once again the debate over Bengali nationalism</t>
+          <t>Amar Ekushey: Before Bangla became a demand</t>
         </is>
       </c>
       <c r="E128" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/slow-reads/focus/news/once-again-the-debate-over-bengali-nationalism-4139921</t>
+          <t>https://www.thedailystar.net/slow-reads/focus/news/amar-ekushey-bangla-became-demand-4108021</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4048,26 +4048,26 @@
         <v>128</v>
       </c>
       <c r="B129" s="2" t="n">
-        <v>46114</v>
+        <v>46074</v>
       </c>
       <c r="C129" s="3" t="inlineStr">
         <is>
-          <t>Ashfaqur Rahman</t>
+          <t>Rahat Minhaz</t>
         </is>
       </c>
       <c r="D129" s="3" t="inlineStr">
         <is>
-          <t>Banglay Bidroho: A rare collection of Liberation War paintings</t>
+          <t>Ekushey in the Mirror of Azad</t>
         </is>
       </c>
       <c r="E129" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/slow-reads/focus/news/banglay-bidroho-rare-collection-liberation-war-paintings-4141771</t>
+          <t>https://www.thedailystar.net/slow-reads/focus/news/ekushey-the-mirror-azad-4111286</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Borderline</t>
         </is>
       </c>
     </row>
@@ -4076,26 +4076,26 @@
         <v>129</v>
       </c>
       <c r="B130" s="2" t="n">
-        <v>46122</v>
+        <v>46075</v>
       </c>
       <c r="C130" s="3" t="inlineStr">
         <is>
-          <t>Priyam Paul</t>
+          <t>Shahadat Parvez</t>
         </is>
       </c>
       <c r="D130" s="3" t="inlineStr">
         <is>
-          <t>The proclamation that gave Bangladesh its statehood</t>
+          <t>Capturing the Language Movement: Rafiqul's rare archive</t>
         </is>
       </c>
       <c r="E130" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/slow-reads/focus/news/the-proclamation-gave-bangladesh-its-statehood-4148281</t>
+          <t>https://www.thedailystar.net/slow-reads/focus/news/capturing-the-language-movement-rafiquls-rare-archive-4112011</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Borderline</t>
         </is>
       </c>
     </row>
@@ -4104,26 +4104,26 @@
         <v>130</v>
       </c>
       <c r="B131" s="2" t="n">
-        <v>46128</v>
+        <v>46084</v>
       </c>
       <c r="C131" s="3" t="inlineStr">
         <is>
-          <t>Mahdi Chowdhury</t>
+          <t>Sayem Bin Rafiq</t>
         </is>
       </c>
       <c r="D131" s="3" t="inlineStr">
         <is>
-          <t>The pain of water</t>
+          <t>The Australian doctor who witnessed what Bangladesh wanted to forget</t>
         </is>
       </c>
       <c r="E131" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/slow-reads/focus/news/the-pain-water-4026791</t>
+          <t>https://www.thedailystar.net/slow-reads/focus/news/the-australian-doctor-who-witnessed-what-bangladesh-wanted-forget-4118701</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Borderline</t>
+          <t>Core</t>
         </is>
       </c>
     </row>
@@ -4132,21 +4132,21 @@
         <v>131</v>
       </c>
       <c r="B132" s="2" t="n">
-        <v>46129</v>
+        <v>46097</v>
       </c>
       <c r="C132" s="3" t="inlineStr">
         <is>
-          <t>Tajuddin Ahmad</t>
+          <t>Sultana Kamal</t>
         </is>
       </c>
       <c r="D132" s="3" t="inlineStr">
         <is>
-          <t>Bangladesh speaks to the world</t>
+          <t>My mother’s letter during the Liberation War</t>
         </is>
       </c>
       <c r="E132" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/slow-reads/focus/news/bangladesh-speaks-the-world-4153116</t>
+          <t>https://www.thedailystar.net/slow-reads/focus/news/my-mothers-letter-during-the-liberation-war-4129891</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -4160,26 +4160,26 @@
         <v>132</v>
       </c>
       <c r="B133" s="2" t="n">
-        <v>46129</v>
+        <v>46098</v>
       </c>
       <c r="C133" s="3" t="inlineStr">
         <is>
-          <t>Rahat Minhaz</t>
+          <t>Faruq Choudhury</t>
         </is>
       </c>
       <c r="D133" s="3" t="inlineStr">
         <is>
-          <t>Witnessing a nation in the making: A journalist’s journey to Mujibnagar</t>
+          <t>Bangabandhu and the world</t>
         </is>
       </c>
       <c r="E133" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/slow-reads/focus/news/witnessing-nation-the-making-journalists-journey-mujibnagar-4153696</t>
+          <t>https://www.thedailystar.net/slow-reads/slow-reads-classics/news/bangabandhu-and-the-world-4131081</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Borderline</t>
         </is>
       </c>
     </row>
@@ -4188,26 +4188,26 @@
         <v>133</v>
       </c>
       <c r="B134" s="2" t="n">
-        <v>46131</v>
+        <v>46098</v>
       </c>
       <c r="C134" s="3" t="inlineStr">
         <is>
-          <t>Musrat Hossain Mithila</t>
+          <t>Madhurima Sen</t>
         </is>
       </c>
       <c r="D134" s="3" t="inlineStr">
         <is>
-          <t>Zobaida Khatun Chowdhury: A life carved in courage</t>
+          <t>How does Pakistan write 1971?</t>
         </is>
       </c>
       <c r="E134" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/slow-reads/focus/news/zobaida-khatun-chowdhury-life-carved-courage-4154851</t>
+          <t>https://www.thedailystar.net/slow-reads/focus/news/how-does-pakistan-write-1971-4130621</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Borderline</t>
+          <t>Core</t>
         </is>
       </c>
     </row>
@@ -4216,21 +4216,21 @@
         <v>134</v>
       </c>
       <c r="B135" s="2" t="n">
-        <v>46134</v>
+        <v>46099</v>
       </c>
       <c r="C135" s="3" t="inlineStr">
         <is>
-          <t>RBR</t>
+          <t>Rehman Sobhan</t>
         </is>
       </c>
       <c r="D135" s="3" t="inlineStr">
         <is>
-          <t>Maleka Khan: A guardian of memory</t>
+          <t>Prelude to an order for genocide</t>
         </is>
       </c>
       <c r="E135" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/slow-reads/focus/news/maleka-khan-guardian-memory-4157096</t>
+          <t>https://www.thedailystar.net/slow-reads/slow-reads-classics/prelude-order-genocide-4554</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -4244,26 +4244,26 @@
         <v>135</v>
       </c>
       <c r="B136" s="2" t="n">
-        <v>46176</v>
+        <v>46106</v>
       </c>
       <c r="C136" s="3" t="inlineStr">
         <is>
-          <t>Zaglul Haider</t>
+          <t>Miftahul Jannat</t>
         </is>
       </c>
       <c r="D136" s="3" t="inlineStr">
         <is>
-          <t>Are Bangladesh’s Biharis truly equal citizens?</t>
+          <t>Echoes of Anne Frank in Swati’s war diary</t>
         </is>
       </c>
       <c r="E136" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/slow-reads/big-picture/news/are-bangladeshs-biharis-truly-equal-citizens-4185176</t>
+          <t>https://www.thedailystar.net/slow-reads/focus/news/echoes-anne-frank-swatis-war-diary-4135246</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Borderline</t>
+          <t>Core</t>
         </is>
       </c>
     </row>
@@ -4272,26 +4272,26 @@
         <v>136</v>
       </c>
       <c r="B137" s="2" t="n">
-        <v>46177</v>
+        <v>46106</v>
       </c>
       <c r="C137" s="3" t="inlineStr">
         <is>
-          <t>A.I. Mahbub Uddin Ahmed</t>
+          <t>Rahat Minhaz</t>
         </is>
       </c>
       <c r="D137" s="3" t="inlineStr">
         <is>
-          <t>K.A.M. Saaduddin: Architect and activist of anti-imperialist sociology and social movements in Bangladesh</t>
+          <t>Genesis of a genocide report</t>
         </is>
       </c>
       <c r="E137" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/slow-reads/focus/news/kam-saaduddin-architect-and-activist-anti-imperialist-sociology-and-social-movements-bangladesh-4189861</t>
+          <t>https://www.thedailystar.net/slow-reads/focus/news/genesis-genocide-report-4134546</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Borderline</t>
+          <t>Core</t>
         </is>
       </c>
     </row>
@@ -4300,21 +4300,21 @@
         <v>137</v>
       </c>
       <c r="B138" s="2" t="n">
-        <v>46180</v>
+        <v>46106</v>
       </c>
       <c r="C138" s="3" t="inlineStr">
         <is>
-          <t>Shahadat Parvez</t>
+          <t>Ystiaque Ahmed</t>
         </is>
       </c>
       <c r="D138" s="3" t="inlineStr">
         <is>
-          <t>Historic Six-Point Movement: The photographs they suppressed</t>
+          <t>The naval hero who envisioned a nation</t>
         </is>
       </c>
       <c r="E138" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/slow-reads/focus/news/historic-six-point-movement-the-photographs-they-suppressed-4192071</t>
+          <t>https://www.thedailystar.net/slow-reads/focus/news/the-naval-hero-who-envisioned-nation-4135206</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -4328,26 +4328,26 @@
         <v>138</v>
       </c>
       <c r="B139" s="2" t="n">
-        <v>46206</v>
+        <v>46107</v>
       </c>
       <c r="C139" s="3" t="inlineStr">
         <is>
-          <t>Dhrubo Alam</t>
+          <t>SB Meraj</t>
         </is>
       </c>
       <c r="D139" s="3" t="inlineStr">
         <is>
-          <t>The forgotten history of football in Bangladesh</t>
+          <t>The black flag at Rajshahi and the officer who chose conscience</t>
         </is>
       </c>
       <c r="E139" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/slow-reads/focus/news/the-forgotten-history-football-bangladesh-4214576</t>
+          <t>https://www.thedailystar.net/slow-reads/focus/news/the-black-flag-rajshahi-and-the-officer-who-chose-conscience-4135981</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Borderline</t>
+          <t>Core</t>
         </is>
       </c>
     </row>
@@ -4356,26 +4356,26 @@
         <v>139</v>
       </c>
       <c r="B140" s="2" t="n">
-        <v>46220</v>
+        <v>46108</v>
       </c>
       <c r="C140" s="3" t="inlineStr">
         <is>
-          <t>Sahidul Hasan and Md. Hasaibur Rahman</t>
+          <t>Shaila Shobnam</t>
         </is>
       </c>
       <c r="D140" s="3" t="inlineStr">
         <is>
-          <t>Football as freedom: From colonial Bengal to Bangladesh</t>
+          <t>How Pakistan saw 1971: Inside the Hamoodur Rehman Commission Report</t>
         </is>
       </c>
       <c r="E140" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/slow-reads/focus/news/football-freedom-colonial-bengal-bangladesh-4225591</t>
+          <t>https://www.thedailystar.net/slow-reads/big-picture/news/how-pakistan-saw-1971-inside-the-hamoodur-rehman-commission-report-4137001</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Borderline</t>
+          <t>Core</t>
         </is>
       </c>
     </row>
@@ -4384,26 +4384,26 @@
         <v>140</v>
       </c>
       <c r="B141" s="2" t="n">
-        <v>46230</v>
+        <v>46112</v>
       </c>
       <c r="C141" s="3" t="inlineStr">
         <is>
-          <t>Tanvir Haider Chaudhury</t>
+          <t>Priyam Pritim Paul</t>
         </is>
       </c>
       <c r="D141" s="3" t="inlineStr">
         <is>
-          <t>Mufazzal Haider Chaudhury and the idea of Bangladesh</t>
+          <t>Once again the debate over Bengali nationalism</t>
         </is>
       </c>
       <c r="E141" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/slow-reads/focus/news/mufazzal-haider-chaudhury-and-the-idea-bangladesh-4232936</t>
+          <t>https://www.thedailystar.net/slow-reads/focus/news/once-again-the-debate-over-bengali-nationalism-4139921</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Borderline</t>
         </is>
       </c>
     </row>
@@ -4412,21 +4412,21 @@
         <v>141</v>
       </c>
       <c r="B142" s="2" t="n">
-        <v>46241</v>
+        <v>46114</v>
       </c>
       <c r="C142" s="3" t="inlineStr">
         <is>
-          <t>Members of the 2nd Bangladesh Liberation War Course</t>
+          <t>Ashfaqur Rahman</t>
         </is>
       </c>
       <c r="D142" s="3" t="inlineStr">
         <is>
-          <t>The enduring legacy of the 2nd Bangladesh Liberation War Course</t>
+          <t>Banglay Bidroho: A rare collection of Liberation War paintings</t>
         </is>
       </c>
       <c r="E142" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/slow-reads/focus/news/the-enduring-legacy-the-2nd-bangladesh-liberation-war-course-4241891</t>
+          <t>https://www.thedailystar.net/slow-reads/focus/news/banglay-bidroho-rare-collection-liberation-war-paintings-4141771</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -4440,26 +4440,26 @@
         <v>142</v>
       </c>
       <c r="B143" s="2" t="n">
-        <v>46249</v>
+        <v>46122</v>
       </c>
       <c r="C143" s="3" t="inlineStr">
         <is>
-          <t>Rahat Minhaz</t>
+          <t>Priyam Paul</t>
         </is>
       </c>
       <c r="D143" s="3" t="inlineStr">
         <is>
-          <t>Sheikh Mujib’s killing: What the newspapers told and what they omitted</t>
+          <t>The proclamation that gave Bangladesh its statehood</t>
         </is>
       </c>
       <c r="E143" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/slow-reads/focus/news/sheikh-mujibs-killing-what-the-newspapers-told-and-what-they-omitted-4248181</t>
+          <t>https://www.thedailystar.net/slow-reads/focus/news/the-proclamation-gave-bangladesh-its-statehood-4148281</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Borderline</t>
+          <t>Core</t>
         </is>
       </c>
     </row>
@@ -4468,26 +4468,26 @@
         <v>143</v>
       </c>
       <c r="B144" s="2" t="n">
-        <v>46254</v>
+        <v>46128</v>
       </c>
       <c r="C144" s="3" t="inlineStr">
         <is>
-          <t>Tasnim Odrika</t>
+          <t>Mahdi Chowdhury</t>
         </is>
       </c>
       <c r="D144" s="3" t="inlineStr">
         <is>
-          <t>Operation Jackpot: How Bangladesh’s naval commandos struck at Pakistan’s lifeline in 1971</t>
+          <t>The pain of water</t>
         </is>
       </c>
       <c r="E144" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/slow-reads/focus/news/operation-jackpot-how-bangladeshs-naval-commandos-struck-pakistans-lifeline-1971-4252981</t>
+          <t>https://www.thedailystar.net/slow-reads/focus/news/the-pain-water-4026791</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Borderline</t>
         </is>
       </c>
     </row>
@@ -4496,31 +4496,395 @@
         <v>144</v>
       </c>
       <c r="B145" s="2" t="n">
+        <v>46129</v>
+      </c>
+      <c r="C145" s="3" t="inlineStr">
+        <is>
+          <t>Tajuddin Ahmad</t>
+        </is>
+      </c>
+      <c r="D145" s="3" t="inlineStr">
+        <is>
+          <t>Bangladesh speaks to the world</t>
+        </is>
+      </c>
+      <c r="E145" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/slow-reads/focus/news/bangladesh-speaks-the-world-4153116</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>145</v>
+      </c>
+      <c r="B146" s="2" t="n">
+        <v>46129</v>
+      </c>
+      <c r="C146" s="3" t="inlineStr">
+        <is>
+          <t>Rahat Minhaz</t>
+        </is>
+      </c>
+      <c r="D146" s="3" t="inlineStr">
+        <is>
+          <t>Witnessing a nation in the making: A journalist’s journey to Mujibnagar</t>
+        </is>
+      </c>
+      <c r="E146" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/slow-reads/focus/news/witnessing-nation-the-making-journalists-journey-mujibnagar-4153696</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>146</v>
+      </c>
+      <c r="B147" s="2" t="n">
+        <v>46131</v>
+      </c>
+      <c r="C147" s="3" t="inlineStr">
+        <is>
+          <t>Musrat Hossain Mithila</t>
+        </is>
+      </c>
+      <c r="D147" s="3" t="inlineStr">
+        <is>
+          <t>Zobaida Khatun Chowdhury: A life carved in courage</t>
+        </is>
+      </c>
+      <c r="E147" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/slow-reads/focus/news/zobaida-khatun-chowdhury-life-carved-courage-4154851</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>Borderline</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>147</v>
+      </c>
+      <c r="B148" s="2" t="n">
+        <v>46134</v>
+      </c>
+      <c r="C148" s="3" t="inlineStr">
+        <is>
+          <t>RBR</t>
+        </is>
+      </c>
+      <c r="D148" s="3" t="inlineStr">
+        <is>
+          <t>Maleka Khan: A guardian of memory</t>
+        </is>
+      </c>
+      <c r="E148" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/slow-reads/focus/news/maleka-khan-guardian-memory-4157096</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>148</v>
+      </c>
+      <c r="B149" s="2" t="n">
+        <v>46176</v>
+      </c>
+      <c r="C149" s="3" t="inlineStr">
+        <is>
+          <t>Zaglul Haider</t>
+        </is>
+      </c>
+      <c r="D149" s="3" t="inlineStr">
+        <is>
+          <t>Are Bangladesh’s Biharis truly equal citizens?</t>
+        </is>
+      </c>
+      <c r="E149" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/slow-reads/big-picture/news/are-bangladeshs-biharis-truly-equal-citizens-4185176</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>Borderline</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>149</v>
+      </c>
+      <c r="B150" s="2" t="n">
+        <v>46177</v>
+      </c>
+      <c r="C150" s="3" t="inlineStr">
+        <is>
+          <t>A.I. Mahbub Uddin Ahmed</t>
+        </is>
+      </c>
+      <c r="D150" s="3" t="inlineStr">
+        <is>
+          <t>K.A.M. Saaduddin: Architect and activist of anti-imperialist sociology and social movements in Bangladesh</t>
+        </is>
+      </c>
+      <c r="E150" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/slow-reads/focus/news/kam-saaduddin-architect-and-activist-anti-imperialist-sociology-and-social-movements-bangladesh-4189861</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>Borderline</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>150</v>
+      </c>
+      <c r="B151" s="2" t="n">
+        <v>46180</v>
+      </c>
+      <c r="C151" s="3" t="inlineStr">
+        <is>
+          <t>Shahadat Parvez</t>
+        </is>
+      </c>
+      <c r="D151" s="3" t="inlineStr">
+        <is>
+          <t>Historic Six-Point Movement: The photographs they suppressed</t>
+        </is>
+      </c>
+      <c r="E151" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/slow-reads/focus/news/historic-six-point-movement-the-photographs-they-suppressed-4192071</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>151</v>
+      </c>
+      <c r="B152" s="2" t="n">
+        <v>46206</v>
+      </c>
+      <c r="C152" s="3" t="inlineStr">
+        <is>
+          <t>Dhrubo Alam</t>
+        </is>
+      </c>
+      <c r="D152" s="3" t="inlineStr">
+        <is>
+          <t>The forgotten history of football in Bangladesh</t>
+        </is>
+      </c>
+      <c r="E152" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/slow-reads/focus/news/the-forgotten-history-football-bangladesh-4214576</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>Borderline</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>152</v>
+      </c>
+      <c r="B153" s="2" t="n">
+        <v>46220</v>
+      </c>
+      <c r="C153" s="3" t="inlineStr">
+        <is>
+          <t>Sahidul Hasan and Md. Hasaibur Rahman</t>
+        </is>
+      </c>
+      <c r="D153" s="3" t="inlineStr">
+        <is>
+          <t>Football as freedom: From colonial Bengal to Bangladesh</t>
+        </is>
+      </c>
+      <c r="E153" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/slow-reads/focus/news/football-freedom-colonial-bengal-bangladesh-4225591</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>Borderline</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>153</v>
+      </c>
+      <c r="B154" s="2" t="n">
+        <v>46230</v>
+      </c>
+      <c r="C154" s="3" t="inlineStr">
+        <is>
+          <t>Tanvir Haider Chaudhury</t>
+        </is>
+      </c>
+      <c r="D154" s="3" t="inlineStr">
+        <is>
+          <t>Mufazzal Haider Chaudhury and the idea of Bangladesh</t>
+        </is>
+      </c>
+      <c r="E154" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/slow-reads/focus/news/mufazzal-haider-chaudhury-and-the-idea-bangladesh-4232936</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>154</v>
+      </c>
+      <c r="B155" s="2" t="n">
+        <v>46241</v>
+      </c>
+      <c r="C155" s="3" t="inlineStr">
+        <is>
+          <t>Members of the 2nd Bangladesh Liberation War Course</t>
+        </is>
+      </c>
+      <c r="D155" s="3" t="inlineStr">
+        <is>
+          <t>The enduring legacy of the 2nd Bangladesh Liberation War Course</t>
+        </is>
+      </c>
+      <c r="E155" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/slow-reads/focus/news/the-enduring-legacy-the-2nd-bangladesh-liberation-war-course-4241891</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>155</v>
+      </c>
+      <c r="B156" s="2" t="n">
+        <v>46249</v>
+      </c>
+      <c r="C156" s="3" t="inlineStr">
+        <is>
+          <t>Rahat Minhaz</t>
+        </is>
+      </c>
+      <c r="D156" s="3" t="inlineStr">
+        <is>
+          <t>Sheikh Mujib’s killing: What the newspapers told and what they omitted</t>
+        </is>
+      </c>
+      <c r="E156" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/slow-reads/focus/news/sheikh-mujibs-killing-what-the-newspapers-told-and-what-they-omitted-4248181</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>Borderline</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>156</v>
+      </c>
+      <c r="B157" s="2" t="n">
+        <v>46254</v>
+      </c>
+      <c r="C157" s="3" t="inlineStr">
+        <is>
+          <t>Tasnim Odrika</t>
+        </is>
+      </c>
+      <c r="D157" s="3" t="inlineStr">
+        <is>
+          <t>Operation Jackpot: How Bangladesh’s naval commandos struck at Pakistan’s lifeline in 1971</t>
+        </is>
+      </c>
+      <c r="E157" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/slow-reads/focus/news/operation-jackpot-how-bangladeshs-naval-commandos-struck-pakistans-lifeline-1971-4252981</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>157</v>
+      </c>
+      <c r="B158" s="2" t="n">
         <v>46272</v>
       </c>
-      <c r="C145" s="3" t="inlineStr">
+      <c r="C158" s="3" t="inlineStr">
         <is>
           <t>A.Z.M. Akhlaqur Rahman</t>
         </is>
       </c>
-      <c r="D145" s="3" t="inlineStr">
+      <c r="D158" s="3" t="inlineStr">
         <is>
           <t>Untold stories of 1971 through private letters</t>
         </is>
       </c>
-      <c r="E145" s="4" t="inlineStr">
+      <c r="E158" s="4" t="inlineStr">
         <is>
           <t>https://www.thedailystar.net/slow-reads/focus/news/untold-stories-1971-through-private-letters-4266326</t>
         </is>
       </c>
-      <c r="F145" t="inlineStr">
+      <c r="F158" t="inlineStr">
         <is>
           <t>Core</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F145"/>
+  <autoFilter ref="A1:F158"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId2"/>
@@ -4666,6 +5030,19 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E143" r:id="rId142"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E144" r:id="rId143"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E158" r:id="rId157"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4677,7 +5054,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4728,56 +5105,56 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>42700</v>
+        <v>41043</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ASIF MUNIER</t>
+          <t>Julfikar Ali Manik and Rizanuzzaman Laskar</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>Munier Chowdhury: Personal Glimpses</t>
+          <t>Anti-Bangladesh before &amp; after '71</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/in-focus/munier-chowdhury-personal-glimpses-1320649</t>
+          <t>https://www.thedailystar.net/news-detail-234068</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Borderline</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Articles</t>
+          <t>Other sections</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>relevance uncertain: Subject killed in 1971; piece centres on his life</t>
+          <t>relevance uncertain: Text overlaps heavily with 'Anti-liberation all along' (2013) - possible republication</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>43073</v>
+        <v>41350</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Waqar A Khan</t>
+          <t>Minhaj Uddin</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>From the labyrinth of memory</t>
+          <t>Hate Statue: Symbol of Razakars, Al Badar, Al-Shams</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/in-focus/the-labyrinth-memory-1499692</t>
+          <t>https://www.thedailystar.net/news/hate-statue-symbol-of-razakars-al-badar-al-shams</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -4787,67 +5164,67 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Articles</t>
+          <t>Other sections</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>relevance uncertain: Post-war aftermath rather than the war itself</t>
+          <t>relevance uncertain: About a present-day memorial</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>44283</v>
+        <v>41471</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Sadia Mahmood</t>
+          <t>Julfikar Ali Manik and Mahbubur Rahman Khan</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>The 1971 war, caste, citizenship and a war memorial in Tharparkar</t>
+          <t>Anti-liberation all along</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/slow-reads/focus/news/the-1971-war-caste-citizenship-and-war-memorial-tharparkar-2067765</t>
+          <t>https://www.thedailystar.net/news/anti-liberation-all-along</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Borderline</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Articles</t>
+          <t>Other sections</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>relevance uncertain: About the western front of the 1971 India-Pakistan war, not Bangladesh itself</t>
+          <t>relevance uncertain: Text overlaps heavily with 234068 (2012) - possible republication</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>44389</v>
+        <v>42084</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Waqar A Khan</t>
+          <t>Md Shahnawaz Khan Chandan</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>The Incorrigible Zulfikar Ali Bhutto</t>
+          <t>Their Lips are Sealed</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/slow-reads/focus/news/the-incorrigible-zulfikar-ali-bhutto-2127616</t>
+          <t>https://www.thedailystar.net/in-focus/their-lips-are-sealed-72792</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -4862,32 +5239,32 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>relevance uncertain: 1971 is one part of a whole-life biography</t>
+          <t>relevance uncertain: Witness protection broadly; tribunal is one strand</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>45861</v>
+        <v>42700</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Mofidul Hoque</t>
+          <t>ASIF MUNIER</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Tajuddin Ahmad man who shaped history</t>
+          <t>Munier Chowdhury: Personal Glimpses</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/slow-reads/focus/news/tajuddin-ahmad-man-who-shaped-history-3945746</t>
+          <t>https://www.thedailystar.net/in-focus/munier-chowdhury-personal-glimpses-1320649</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Borderline</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -4897,47 +5274,354 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>relevance uncertain: Weighs his early diaries heavily; 1971 is the culmination</t>
+          <t>relevance uncertain: Subject killed in 1971; piece centres on his life</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
+        <v>43073</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Waqar A Khan</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>From the labyrinth of memory</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/in-focus/the-labyrinth-memory-1499692</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Borderline</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Articles</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>relevance uncertain: Post-war aftermath rather than the war itself</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>44265</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Md Aminul Islam</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Indomitable March: A roving treasure trove of war stories</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/backpage/news/indomitable-march-roving-treasure-trove-war-stories-2057821</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Borderline</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Other sections</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>relevance uncertain: Present-day profile; 1971 is the subject of his work</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>44283</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Sadia Mahmood</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>The 1971 war, caste, citizenship and a war memorial in Tharparkar</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/slow-reads/focus/news/the-1971-war-caste-citizenship-and-war-memorial-tharparkar-2067765</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Borderline</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Articles</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>relevance uncertain: About the western front of the 1971 India-Pakistan war, not Bangladesh itself</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>44389</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Waqar A Khan</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>The Incorrigible Zulfikar Ali Bhutto</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/slow-reads/focus/news/the-incorrigible-zulfikar-ali-bhutto-2127616</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Borderline</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Articles</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>relevance uncertain: 1971 is one part of a whole-life biography</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>45764</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Priyam Paul</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>The Proclamation of Independence was a beacon for Bangladesh</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/opinion/views/news/the-proclamation-independence-was-beacon-bangladesh-3872661</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Other sections</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>relevance uncertain: Text largely matches 4148281 (2026, retitled) - possible republication</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>45861</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Mofidul Hoque</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Tajuddin Ahmad man who shaped history</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/slow-reads/focus/news/tajuddin-ahmad-man-who-shaped-history-3945746</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Articles</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>relevance uncertain: Weighs his early diaries heavily; 1971 is the culmination</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
         <v>45985</v>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>Serajul Islam Choudhury</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>Remembering Munier Bhai</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t>https://www.thedailystar.net/slow-reads/focus/news/remembering-munier-bhai-4042036</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>Borderline</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>Articles</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="G13" s="3" t="inlineStr">
         <is>
           <t>relevance uncertain: Subject was killed in 1971 but the piece dwells on his earlier life</t>
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>46122</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Priyam Paul</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>The proclamation that gave Bangladesh its statehood</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/slow-reads/focus/news/the-proclamation-gave-bangladesh-its-statehood-4148281</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Articles</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>relevance uncertain: Text largely matches 3872661 (2025, different title) - possible republication</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>41622</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Anthony Mascarenhas</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Genocide</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/genocide-2351</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>(not listed - duplicate)</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>likely duplicate of https://www.thedailystar.net/slow-reads/focus/news/genocide-1505440 (same title and author)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Operation Searchlight on March 25 1971: The night hell opened over Dhaka</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/slow-reads/slow-reads-special/operation-searchlight/news/operation-searchlight-the-night-hell-opened-over-dhaka-4135406</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>(not listed - could not be fetched)</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>not extracted: Redirects to the interactive microsite operationsearchlight.thedailystar.net, which this environment cannot reach; title from search results; date and author not extracted</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G7"/>
+  <autoFilter ref="A1:G16"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId2"/>
@@ -4945,6 +5629,15 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D16" r:id="rId15"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4956,7 +5649,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -5010,21 +5703,21 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>46005</v>
+        <v>39799</v>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>Md Raihan Raju</t>
+          <t>Julfikar Ali Manik, for Star Online</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>A life lit by courage</t>
+          <t>1971 remnants still active in politics</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/ds/slow-reads-special/news/life-lit-courage-4057396</t>
+          <t>https://www.thedailystar.net/news-detail-67454</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -5034,7 +5727,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>ds/slow-reads-special</t>
+          <t>news-detail-67454</t>
         </is>
       </c>
     </row>
@@ -5043,21 +5736,21 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>46005</v>
+        <v>39907</v>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Mahfuz Anam</t>
+          <t>(Translated by Mohamad Shafiqul Islam)</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>What we owe the martyred intellectuals</t>
+          <t>Two Muktijoddha Letters of 1971</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/ds/slow-reads-special/news/what-we-owe-martyred-intellectuals-4057471</t>
+          <t>https://www.thedailystar.net/news-detail-82580</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -5067,7 +5760,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>ds/slow-reads-special</t>
+          <t>news-detail-82580</t>
         </is>
       </c>
     </row>
@@ -5076,21 +5769,21 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>46005</v>
+        <v>40517</v>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Mohiuddin Alamgir</t>
+          <t>Shahriar Kabir</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Why is the martyred intellectuals’ list still incomplete?</t>
+          <t>Bangladesh holocaust of '71</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/ds/slow-reads-special/news/why-martyred-intellectuals-list-still-incomplete-4057506</t>
+          <t>https://www.thedailystar.net/news-detail-164764</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -5100,7 +5793,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>ds/slow-reads-special</t>
+          <t>news-detail-164764</t>
         </is>
       </c>
     </row>
@@ -5109,21 +5802,21 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>46007</v>
+        <v>41043</v>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Mahfuz Anam</t>
+          <t>Julfikar Ali Manik and Rizanuzzaman Laskar</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>A PEOPLE’S WAR, A WORLD’S RECKONING</t>
+          <t>Anti-Bangladesh before &amp; after '71</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/ds/slow-reads-special/news/peoples-war-worlds-reckoning-4058996</t>
+          <t>https://www.thedailystar.net/news-detail-234068</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -5133,7 +5826,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>ds/slow-reads-special</t>
+          <t>news-detail-234068</t>
         </is>
       </c>
     </row>
@@ -5142,42 +5835,1538 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="n">
+        <v>41350</v>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Minhaj Uddin</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Hate Statue: Symbol of Razakars, Al Badar, Al-Shams</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/news/hate-statue-symbol-of-razakars-al-badar-al-shams</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Borderline</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>news/hate-statue-symbol-of-razakars-al-badar-al-shams</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>41359</v>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Meghna Guhathakurta</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>1971: Re-emerging silences</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/news/1971-re-emerging-silences</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>news/1971-re-emerging-silences</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>41471</v>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Julfikar Ali Manik and Mahbubur Rahman Khan</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Anti-liberation all along</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/news/anti-liberation-all-along</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>news/anti-liberation-all-along</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>41621</v>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Fayeka Zabeen Siddiqua</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>When Words Became Weapons</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/news/when-words-became-weapons</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>news/when-words-became-weapons</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>41970</v>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>The Daily Star</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Freedom in the air documents</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/freedom-in-the-air-documents-52351</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>freedom-in-the-air-documents-52351</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>41982</v>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>The Daily Star</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>March 25, 1971</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/march-25-1971-54410</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>march-25-1971-54410</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>42346</v>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Inam Ahmed and Shakhawat Liton</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Cables of genocide</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/frontpage/news/cables-genocide-184102</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>frontpage/news</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>42350</v>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>The Daily Star</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Songs of Freedom</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/literature/news/songs-freedom-185875</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>literature/news</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>42352</v>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>REVIEWED BY MOHAMMAD SHAFIQUL ISLAM</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>A Freedom Fighter's Personal Account of 1971</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/book-reviews/freedom-fighters-personal-account-1971-186934</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>book-reviews/freedom-fighters-personal-account-1971-186934</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>42720</v>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Colonel (Retd.) Towficur Rahman</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>The Guerrillas of Dhaka in 1971</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/supplements/victory-day-2016-special/the-guerrillas-dhaka-1971-1330306</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>supplements/victory-day-2016-special</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>42724</v>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Shahnoor Wahid</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>Archer Blood - An American's sacrifice for Bangladesh</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/opinion/peripherally-yours/archer-blood-americans-sacrifice-bangladesh-1332442</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>opinion/peripherally-yours</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>43098</v>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Zaid Kalam</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>Arms for freedom</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/backpage/bangladesh-liberation-war-1971-muktijuddho-guerrilla-fighter-arms-freedom-1511812</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>backpage/bangladesh-liberation-war-1971-muktijuddho-guerrilla-fighter-arms-freedom-1511812</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>43425</v>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Syed Muhammad Ibrahim Bir Protik</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>The legacy of November 21, 1971</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/opinion/perspective/news/the-legacy-november-21-1971-1663198</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>opinion/perspective</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>43448</v>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>Pizaur Hossain</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>1971: Another chapter in world history when intellectuals were targeted</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/supplements/martyred-intellectuals-day-2017/news/1971-another-chapter-world-history-when-intellectuals-were-targeted-1672981</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>supplements/martyred-intellectuals-day-2017</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>43549</v>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>Taqbir Huda</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>Remembering the barbarities of Operation Searchlight</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/opinion/perspective/news/remembering-the-barbarities-operation-searchlight-1719859</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>opinion/perspective</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>43938</v>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>Zahid Hossain</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>Mujibnagar Day: A milestone in the War of Liberation</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/opinion/news/mujibnagar-day-milestone-the-war-liberation-1893541</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>opinion/news</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>44181</v>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>Ahmad Ahsan</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>Our pride and glory: The Mukti Bahini in 1971</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/opinion/news/our-pride-and-glory-the-mukti-bahini-1971-2011981</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>opinion/news</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>44265</v>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>Md Aminul Islam</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>Indomitable March: A roving treasure trove of war stories</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/backpage/news/indomitable-march-roving-treasure-trove-war-stories-2057821</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Borderline</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>backpage/news</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>44280</v>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>Suhan Rizwan</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>Reflections on Muktijuddho</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/online-exclusive/reflections-bangladesh-liberation-war-1971-2066617</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>online-exclusive/reflections-bangladesh-liberation-war-1971-2066617</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>44303</v>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Brig R P Singh, VSM (retired)</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>An eyewitness account of the Mujibnagar government’s swearing-in ceremony</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/opinion/news/eyewitness-account-the-mujibnagar-governments-swearing-ceremony-2078617</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>opinion/news</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>44303</v>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>The Daily Star</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>To the people of the world</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/supplements/historic-mujibnagar-day/news/the-people-the-world-2078881</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>supplements/historic-mujibnagar-day</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>44325</v>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>Brig RP Singh, VSM (Retired)</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>Die was cast for Bangladesh’s Liberation War in April 1971</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/opinion/news/die-was-cast-bangladeshs-liberation-war-april-1971-2090509</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>opinion/news</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>44546</v>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>Jayant Prasad</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>The 1971 saga</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/supplements/victory-day-special-2021/news/the-1971-saga-2917976</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>supplements/victory-day-special-2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>44735</v>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>Namrata</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>Manash Ghosh's ' Bangladesh War': Dispatches of independence</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/daily-star-books/news/dispatches-independence-3054366</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>daily-star-books/news</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>45033</v>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>Mahbub Uddin Ahmed Bir Bikram</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>Honouring Mujibnagar heroes</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/opinion/focus/news/honouring-mujibnagar-heroes-3298761</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>opinion/focus</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>45276</v>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>Marina Yasmin</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>A Testimony of Pakistan’s Cruelty, Genocide and Failure in Bangladesh</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/supplements/victory-day-special-2023/news/testimony-pakistans-cruelty-genocide-and-failure-bangladesh-3495491</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>supplements/victory-day-special-2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="2" t="n">
+        <v>45276</v>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>Ahmad Istiak</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>Battles that quickened victory</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/news/bangladesh/news/battles-quickened-victory-3495381</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>news/bangladesh</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="2" t="n">
+        <v>45277</v>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>Ahmad Istiak</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>Series genocide in 1971: Three times a survivor</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/news/bangladesh/news/series-genocide-1971-three-times-survivor-3496086</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>news/bangladesh</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="2" t="n">
+        <v>45377</v>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>Priyam Pritim Paul</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>Administrative dynamics in 1971’s War of Liberation</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/supplements/independence-day-special-2024/news/administrative-dynamics-1971s-war-liberation-3575151</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>supplements/independence-day-special-2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="2" t="n">
+        <v>45390</v>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>Khashruzzamn Choudhury</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>A freedom fighter’s journey to Mujibnagar</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/opinion/focus/news/freedom-fighters-journey-mujibnagar-3584516</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>opinion/focus</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="2" t="n">
+        <v>45641</v>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>Ahmad Istiak</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>Regional Resistance: Purbo Banglar Jatiya Mukti Bahini</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/news/bangladesh/news/regional-resistance-purbo-banglar-jatiya-mukti-bahini-3776411</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>news/bangladesh</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="2" t="n">
+        <v>45647</v>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>Anu Muhammad</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>The spirit of 1971: Reflections on liberation, aspirations, and modern challenges</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/opinion/views/news/the-spirit-1971-reflections-liberation-aspirations-and-modern-challenges-3780941</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>opinion/views</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="2" t="n">
+        <v>45741</v>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>The Daily Star</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>March 25 through the eyes of ordinary people</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/opinion/views/news/march-25-through-the-eyes-ordinary-people-3856476</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>opinion/views</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="2" t="n">
+        <v>45741</v>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>Ahmad Istiak</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>Operation searchlight: The massacre at Ctg cantonment</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/news/bangladesh/news/operation-searchlight-the-massacre-ctg-cantonment-3856676</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>news/bangladesh</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" s="2" t="n">
+        <v>45742</v>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>Rahat Minhaz</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>The People in 1971</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/supplements/independence-day-special-2025/news/the-people-1971-3857821</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>supplements/independence-day-special-2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" s="2" t="n">
+        <v>45742</v>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>Anu Muhammad</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>The road to liberation: March 1971 and the years that led to it</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/opinion/views/news/the-road-liberation-march-1971-and-the-years-led-it-3857441</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>opinion/views</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" s="2" t="n">
+        <v>45764</v>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>Priyam Paul</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>The Proclamation of Independence was a beacon for Bangladesh</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/opinion/views/news/the-proclamation-independence-was-beacon-bangladesh-3872661</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>opinion/views</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" s="2" t="n">
+        <v>46005</v>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>Md Raihan Raju</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>A life lit by courage</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/ds/slow-reads-special/news/life-lit-courage-4057396</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>ds/slow-reads-special</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" s="2" t="n">
+        <v>46005</v>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>Mahfuz Anam</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>What we owe the martyred intellectuals</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/ds/slow-reads-special/news/what-we-owe-martyred-intellectuals-4057471</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>ds/slow-reads-special</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" s="2" t="n">
+        <v>46005</v>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>Mohiuddin Alamgir</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>Why is the martyred intellectuals’ list still incomplete?</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/ds/slow-reads-special/news/why-martyred-intellectuals-list-still-incomplete-4057506</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>ds/slow-reads-special</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" s="2" t="n">
         <v>46007</v>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>Mahfuz Anam</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>A PEOPLE’S WAR, A WORLD’S RECKONING</t>
+        </is>
+      </c>
+      <c r="E46" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/ds/slow-reads-special/news/peoples-war-worlds-reckoning-4058996</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>ds/slow-reads-special</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" s="2" t="n">
+        <v>46007</v>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
         <is>
           <t>Ansar Ahmed Ullah</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D47" s="3" t="inlineStr">
         <is>
           <t>The Bangladeshi diaspora in Britain: A forgotten front of 1971</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E47" s="4" t="inlineStr">
         <is>
           <t>https://www.thedailystar.net/ds/slow-reads-special/news/bangladeshi-diaspora-britain-forgotten-front-1971-4059086</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
         <is>
           <t>ds/slow-reads-special</t>
         </is>
       </c>
     </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" s="2" t="n">
+        <v>46007</v>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>K A S Murshid</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>The unhealed wounds of 1971: Bangladesh's unfinished liberation</t>
+        </is>
+      </c>
+      <c r="E48" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/opinion/views/news/unhealed-wounds-1971-bangladeshs-unfinished-liberation-4059396</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>opinion/views</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" s="2" t="n">
+        <v>46106</v>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>Tanziral Dilshad Ditan</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>Operation Searchlight and the unrecognised genocide of 1971</t>
+        </is>
+      </c>
+      <c r="E49" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/opinion/views/news/operation-searchlight-and-the-unrecognised-genocide-1971-4134676</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>opinion/views</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" s="2" t="n">
+        <v>46107</v>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>Mohiuddin Alamgir</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>Witnesses to genocide</t>
+        </is>
+      </c>
+      <c r="E50" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/news/bangladesh/news/witnesses-genocide-4135726</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>news/bangladesh</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G6"/>
+  <autoFilter ref="A1:G50"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E50" r:id="rId49"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5189,7 +7378,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C27"/>
+  <dimension ref="A1:C35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -5217,7 +7406,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>144</v>
+        <v>157</v>
       </c>
     </row>
     <row r="3">
@@ -5227,7 +7416,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4">
@@ -5237,7 +7426,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5">
@@ -5247,7 +7436,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -5257,7 +7446,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7">
@@ -5305,10 +7494,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="C11" t="n">
-        <v>5</v>
+        <v>47</v>
       </c>
     </row>
     <row r="12">
@@ -5318,10 +7507,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13"/>
@@ -5344,136 +7533,224 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>2016</v>
+        <v>2008</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>2017</v>
+        <v>2009</v>
       </c>
       <c r="B16" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>2019</v>
+        <v>2010</v>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>2020</v>
+        <v>2012</v>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>2021</v>
+        <v>2013</v>
       </c>
       <c r="B19" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>2022</v>
+        <v>2014</v>
       </c>
       <c r="B20" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>2023</v>
+        <v>2015</v>
       </c>
       <c r="B21" t="n">
         <v>6</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>2024</v>
+        <v>2016</v>
       </c>
       <c r="B22" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>2025</v>
+        <v>2017</v>
       </c>
       <c r="B23" t="n">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="C23" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>2019</v>
+      </c>
+      <c r="B25" t="n">
+        <v>4</v>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B26" t="n">
+        <v>3</v>
+      </c>
+      <c r="C26" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B27" t="n">
+        <v>21</v>
+      </c>
+      <c r="C27" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B28" t="n">
+        <v>19</v>
+      </c>
+      <c r="C28" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B29" t="n">
+        <v>6</v>
+      </c>
+      <c r="C29" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B30" t="n">
+        <v>13</v>
+      </c>
+      <c r="C30" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B31" t="n">
+        <v>34</v>
+      </c>
+      <c r="C31" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
         <v>2026</v>
       </c>
-      <c r="B24" t="n">
-        <v>34</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25"/>
-    <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="B32" t="n">
+        <v>35</v>
+      </c>
+      <c r="C32" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33"/>
+    <row r="34">
+      <c r="A34" t="inlineStr">
         <is>
           <t>Date range – Articles</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>09-Apr-2016 to 07-Sep-2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>21-Mar-2015 to 07-Sep-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
         <is>
           <t>Date range – Other sections</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>14-Dec-2025 to 16-Dec-2025</t>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>17-Dec-2008 to 26-Mar-2026</t>
         </is>
       </c>
     </row>

--- a/liberation_war_articles.xlsx
+++ b/liberation_war_articles.xlsx
@@ -7378,7 +7378,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C35"/>
+  <dimension ref="A1:C40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -7754,6 +7754,62 @@
         </is>
       </c>
     </row>
+    <row r="36"/>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>Coverage</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>Candidates read</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>Candidates found</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Slow Reads / In Focus</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>1516</v>
+      </c>
+      <c r="C38" t="n">
+        <v>1525</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Other sections</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>55</v>
+      </c>
+      <c r="C39" t="n">
+        <v>2549</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Other sections are INCOMPLETE: the crawl stopped on an HTTP 403 from the site and was not resumed (by decision). See REPORT.md.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/liberation_war_articles.xlsx
+++ b/liberation_war_articles.xlsx
@@ -20891,7 +20891,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>2069</v>
+        <v>2149</v>
       </c>
       <c r="C45" t="n">
         <v>2840</v>

--- a/liberation_war_articles.xlsx
+++ b/liberation_war_articles.xlsx
@@ -18,12 +18,12 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Slow Reads - Liberation War'!$A$1:$E$113</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Other - Liberation War'!$A$1:$E$739</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Other - Liberation War'!$A$1:$E$770</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Slow Reads - Language Movement'!$A$1:$E$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Other - Language Movement'!$A$1:$E$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Other - Language Movement'!$A$1:$E$62</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Pre-1971'!$A$1:$F$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Present Day Discussions'!$A$1:$F$112</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Needs review'!$A$1:$F$52</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Needs review'!$A$1:$F$22</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -3192,7 +3192,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E739"/>
+  <dimension ref="A1:E770"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -16299,21 +16299,21 @@
         <v>569</v>
       </c>
       <c r="B570" s="2" t="n">
-        <v>43813</v>
+        <v>43802</v>
       </c>
       <c r="C570" s="3" t="inlineStr">
         <is>
-          <t>M Obaidur Rahman</t>
+          <t>The Daily Star</t>
         </is>
       </c>
       <c r="D570" s="3" t="inlineStr">
         <is>
-          <t>Dr Fazlul Huq Mahi- An exemplary scholar, teacher and human being</t>
+          <t>On this day in 1971</t>
         </is>
       </c>
       <c r="E570" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/supplements/martyred-intellectuals-day-2019/news/dr-fazlul-huq-mahi-exemplary-scholar-teacher-and-human-being-1840174</t>
+          <t>https://www.thedailystar.net/frontpage/news/day-1971-1834984</t>
         </is>
       </c>
     </row>
@@ -16322,21 +16322,21 @@
         <v>570</v>
       </c>
       <c r="B571" s="2" t="n">
-        <v>43813</v>
+        <v>43803</v>
       </c>
       <c r="C571" s="3" t="inlineStr">
         <is>
-          <t>Mahmooda Akhter Ali</t>
+          <t>The Daily Star</t>
         </is>
       </c>
       <c r="D571" s="3" t="inlineStr">
         <is>
-          <t>Dr Sadat Ali- My father, my hero</t>
+          <t>On this day in 1971</t>
         </is>
       </c>
       <c r="E571" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/supplements/martyred-intellectuals-day-2019/news/dr-sadat-ali-my-father-my-hero-1840186</t>
+          <t>https://www.thedailystar.net/frontpage/news/day-1971-1835425</t>
         </is>
       </c>
     </row>
@@ -16345,21 +16345,21 @@
         <v>571</v>
       </c>
       <c r="B572" s="2" t="n">
-        <v>43813</v>
+        <v>43804</v>
       </c>
       <c r="C572" s="3" t="inlineStr">
         <is>
-          <t>Ali Kadar</t>
+          <t>The Daily Star</t>
         </is>
       </c>
       <c r="D572" s="3" t="inlineStr">
         <is>
-          <t>Lutfun Nahar Helen- A teacher and revolutionary</t>
+          <t>On this day in 1971</t>
         </is>
       </c>
       <c r="E572" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/supplements/martyred-intellectuals-day-2019/news/lutfun-nahar-helen-teacher-and-revolutionary-1840204</t>
+          <t>https://www.thedailystar.net/backpage/news/day-1971-1835920</t>
         </is>
       </c>
     </row>
@@ -16368,21 +16368,21 @@
         <v>572</v>
       </c>
       <c r="B573" s="2" t="n">
-        <v>43813</v>
+        <v>43805</v>
       </c>
       <c r="C573" s="3" t="inlineStr">
         <is>
-          <t>Anwar Ali, Rajshahi</t>
+          <t>The Daily Star</t>
         </is>
       </c>
       <c r="D573" s="3" t="inlineStr">
         <is>
-          <t>MARTYRED INTELLECTUALS DAY: Freedom comes at a price</t>
+          <t>On this day in 1971</t>
         </is>
       </c>
       <c r="E573" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/frontpage/news/martyred-intellectuals-day-freedom-comes-price-1840027</t>
+          <t>https://www.thedailystar.net/backpage/news/day-1971-1836391</t>
         </is>
       </c>
     </row>
@@ -16391,21 +16391,21 @@
         <v>573</v>
       </c>
       <c r="B574" s="2" t="n">
-        <v>43813</v>
+        <v>43806</v>
       </c>
       <c r="C574" s="3" t="inlineStr">
         <is>
-          <t>A N M Shahidul</t>
+          <t>The Daily Star</t>
         </is>
       </c>
       <c r="D574" s="3" t="inlineStr">
         <is>
-          <t>Sharafat Ali- A Hero’s Humility</t>
+          <t>On this day in 1971</t>
         </is>
       </c>
       <c r="E574" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/supplements/martyred-intellectuals-day-2019/news/sharafat-ali-heros-humility-1840192</t>
+          <t>https://www.thedailystar.net/frontpage/news/day-1971-1836871</t>
         </is>
       </c>
     </row>
@@ -16414,21 +16414,21 @@
         <v>574</v>
       </c>
       <c r="B575" s="2" t="n">
-        <v>43813</v>
+        <v>43807</v>
       </c>
       <c r="C575" s="3" t="inlineStr">
         <is>
-          <t>Devi Sarma</t>
+          <t>The Daily Star</t>
         </is>
       </c>
       <c r="D575" s="3" t="inlineStr">
         <is>
-          <t>Sudhirkumar Chakrabarti- The man everyone adored</t>
+          <t>On this day in 1971</t>
         </is>
       </c>
       <c r="E575" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/supplements/martyred-intellectuals-day-2019/news/sudhirkumar-chakrabarti-the-man-everyone-adored-1840180</t>
+          <t>https://www.thedailystar.net/frontpage/news/day-1971-1837258</t>
         </is>
       </c>
     </row>
@@ -16437,21 +16437,21 @@
         <v>575</v>
       </c>
       <c r="B576" s="2" t="n">
-        <v>43813</v>
+        <v>43808</v>
       </c>
       <c r="C576" s="3" t="inlineStr">
         <is>
-          <t>Muhammad Abdul Jalil</t>
+          <t>The Daily Star</t>
         </is>
       </c>
       <c r="D576" s="3" t="inlineStr">
         <is>
-          <t>Tojammel Hossen- Someone like my brother</t>
+          <t>On this day in 1971</t>
         </is>
       </c>
       <c r="E576" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/supplements/martyred-intellectuals-day-2019/news/tojammel-hossen-someone-my-brother-1840198</t>
+          <t>https://www.thedailystar.net/frontpage/news/day-1971-1837690</t>
         </is>
       </c>
     </row>
@@ -16460,21 +16460,21 @@
         <v>576</v>
       </c>
       <c r="B577" s="2" t="n">
-        <v>43814</v>
+        <v>43809</v>
       </c>
       <c r="C577" s="3" t="inlineStr">
         <is>
-          <t>Mohammad Al-Masum Molla</t>
+          <t>The Daily Star</t>
         </is>
       </c>
       <c r="D577" s="3" t="inlineStr">
         <is>
-          <t>Perfect cover for freedom fighters</t>
+          <t>On this day in 1971</t>
         </is>
       </c>
       <c r="E577" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/backpage/news/perfect-cover-freedom-fighters-1840432</t>
+          <t>https://www.thedailystar.net/frontpage/news/day-1971-1838104</t>
         </is>
       </c>
     </row>
@@ -16483,21 +16483,21 @@
         <v>577</v>
       </c>
       <c r="B578" s="2" t="n">
-        <v>43815</v>
+        <v>43810</v>
       </c>
       <c r="C578" s="3" t="inlineStr">
         <is>
-          <t>Amanullah</t>
+          <t>The Daily Star</t>
         </is>
       </c>
       <c r="D578" s="3" t="inlineStr">
         <is>
-          <t>A bloody war and how I witnessed it</t>
+          <t>On this day in 1971</t>
         </is>
       </c>
       <c r="E578" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/supplements/news/bloody-war-and-how-i-witnessed-it-1840579</t>
+          <t>https://www.thedailystar.net/backpage/news/day-1971-1838581</t>
         </is>
       </c>
     </row>
@@ -16506,21 +16506,21 @@
         <v>578</v>
       </c>
       <c r="B579" s="2" t="n">
-        <v>43815</v>
+        <v>43811</v>
       </c>
       <c r="C579" s="3" t="inlineStr">
         <is>
-          <t>Muhammad Nurul Huda</t>
+          <t>The Daily Star</t>
         </is>
       </c>
       <c r="D579" s="3" t="inlineStr">
         <is>
-          <t>Bangladesh Police in Liberation War</t>
+          <t>On this day in 1971</t>
         </is>
       </c>
       <c r="E579" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/supplements/news/bangladesh-police-liberation-war-1840564</t>
+          <t>https://www.thedailystar.net/frontpage/news/day-1971-1839046</t>
         </is>
       </c>
     </row>
@@ -16529,21 +16529,21 @@
         <v>579</v>
       </c>
       <c r="B580" s="2" t="n">
-        <v>43815</v>
+        <v>43812</v>
       </c>
       <c r="C580" s="3" t="inlineStr">
         <is>
-          <t>Tamanna Khan and Tuhin Shubhra Adhikary</t>
+          <t>The Daily Star</t>
         </is>
       </c>
       <c r="D580" s="3" t="inlineStr">
         <is>
-          <t>Blood, sweat, tears</t>
+          <t>On this day in 1971</t>
         </is>
       </c>
       <c r="E580" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/frontpage/victory-day-2019-blood-sweat-tears-1840861</t>
+          <t>https://www.thedailystar.net/backpage/news/day-1971-1839553</t>
         </is>
       </c>
     </row>
@@ -16552,21 +16552,21 @@
         <v>580</v>
       </c>
       <c r="B581" s="2" t="n">
-        <v>43815</v>
+        <v>43813</v>
       </c>
       <c r="C581" s="3" t="inlineStr">
         <is>
-          <t>Mishuk Ashraful Awal</t>
+          <t>M Obaidur Rahman</t>
         </is>
       </c>
       <c r="D581" s="3" t="inlineStr">
         <is>
-          <t>Documenting Liberation through his Lens</t>
+          <t>Dr Fazlul Huq Mahi- An exemplary scholar, teacher and human being</t>
         </is>
       </c>
       <c r="E581" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/supplements/news/documenting-liberation-through-his-lens-1840576</t>
+          <t>https://www.thedailystar.net/supplements/martyred-intellectuals-day-2019/news/dr-fazlul-huq-mahi-exemplary-scholar-teacher-and-human-being-1840174</t>
         </is>
       </c>
     </row>
@@ -16575,21 +16575,21 @@
         <v>581</v>
       </c>
       <c r="B582" s="2" t="n">
-        <v>43815</v>
+        <v>43813</v>
       </c>
       <c r="C582" s="3" t="inlineStr">
         <is>
-          <t>Mohiuddin Alamgir</t>
+          <t>Mahmooda Akhter Ali</t>
         </is>
       </c>
       <c r="D582" s="3" t="inlineStr">
         <is>
-          <t>Of bravery, of Betiara</t>
+          <t>Dr Sadat Ali- My father, my hero</t>
         </is>
       </c>
       <c r="E582" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/frontpage/victory-day-2019-of-bravery-of-betiara-1840852</t>
+          <t>https://www.thedailystar.net/supplements/martyred-intellectuals-day-2019/news/dr-sadat-ali-my-father-my-hero-1840186</t>
         </is>
       </c>
     </row>
@@ -16598,21 +16598,21 @@
         <v>582</v>
       </c>
       <c r="B583" s="2" t="n">
-        <v>43815</v>
+        <v>43813</v>
       </c>
       <c r="C583" s="3" t="inlineStr">
         <is>
-          <t>Minam Haque</t>
+          <t>Ali Kadar</t>
         </is>
       </c>
       <c r="D583" s="3" t="inlineStr">
         <is>
-          <t>One of Kamrul Alam Khan Khasru’s valiant missions</t>
+          <t>Lutfun Nahar Helen- A teacher and revolutionary</t>
         </is>
       </c>
       <c r="E583" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/supplements/victory-day-special-2019/news/one-kamrul-alam-khan-khasrus-valiant-missions-1840585</t>
+          <t>https://www.thedailystar.net/supplements/martyred-intellectuals-day-2019/news/lutfun-nahar-helen-teacher-and-revolutionary-1840204</t>
         </is>
       </c>
     </row>
@@ -16621,21 +16621,21 @@
         <v>583</v>
       </c>
       <c r="B584" s="2" t="n">
-        <v>43815</v>
+        <v>43813</v>
       </c>
       <c r="C584" s="3" t="inlineStr">
         <is>
-          <t>Prakash Bhandari</t>
+          <t>Anwar Ali, Rajshahi</t>
         </is>
       </c>
       <c r="D584" s="3" t="inlineStr">
         <is>
-          <t>Sagat Singh — An unsung hero</t>
+          <t>MARTYRED INTELLECTUALS DAY: Freedom comes at a price</t>
         </is>
       </c>
       <c r="E584" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/supplements/news/sagat-singh-unsung-hero-1840570</t>
+          <t>https://www.thedailystar.net/frontpage/news/martyred-intellectuals-day-freedom-comes-price-1840027</t>
         </is>
       </c>
     </row>
@@ -16644,21 +16644,21 @@
         <v>584</v>
       </c>
       <c r="B585" s="2" t="n">
-        <v>43815</v>
+        <v>43813</v>
       </c>
       <c r="C585" s="3" t="inlineStr">
         <is>
-          <t>Zahangir Alom</t>
+          <t>The Daily Star</t>
         </is>
       </c>
       <c r="D585" s="3" t="inlineStr">
         <is>
-          <t>Serenading the sublime souls of the soil</t>
+          <t>On this day in 1971</t>
         </is>
       </c>
       <c r="E585" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/supplements/news/serenading-the-sublime-souls-the-soil-1840558</t>
+          <t>https://www.thedailystar.net/backpage/news/day-1971-1839985</t>
         </is>
       </c>
     </row>
@@ -16667,21 +16667,21 @@
         <v>585</v>
       </c>
       <c r="B586" s="2" t="n">
-        <v>43815</v>
+        <v>43813</v>
       </c>
       <c r="C586" s="3" t="inlineStr">
         <is>
-          <t>Anwar Ali</t>
+          <t>A N M Shahidul</t>
         </is>
       </c>
       <c r="D586" s="3" t="inlineStr">
         <is>
-          <t>‘Chose this land over my father’</t>
+          <t>Sharafat Ali- A Hero’s Humility</t>
         </is>
       </c>
       <c r="E586" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/city/news/chose-land-over-my-father-1841023</t>
+          <t>https://www.thedailystar.net/supplements/martyred-intellectuals-day-2019/news/sharafat-ali-heros-humility-1840192</t>
         </is>
       </c>
     </row>
@@ -16690,21 +16690,21 @@
         <v>586</v>
       </c>
       <c r="B587" s="2" t="n">
-        <v>43816</v>
+        <v>43813</v>
       </c>
       <c r="C587" s="3" t="inlineStr">
         <is>
-          <t>Justice Obaidul Hassan</t>
+          <t>Devi Sarma</t>
         </is>
       </c>
       <c r="D587" s="3" t="inlineStr">
         <is>
-          <t>Role of Baljit Singh Tyagi and BSF in our Liberation War</t>
+          <t>Sudhirkumar Chakrabarti- The man everyone adored</t>
         </is>
       </c>
       <c r="E587" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/opinion/news/role-baljit-singh-tyagi-and-bsf-our-liberation-war-1841140</t>
+          <t>https://www.thedailystar.net/supplements/martyred-intellectuals-day-2019/news/sudhirkumar-chakrabarti-the-man-everyone-adored-1840180</t>
         </is>
       </c>
     </row>
@@ -16713,21 +16713,21 @@
         <v>587</v>
       </c>
       <c r="B588" s="2" t="n">
-        <v>43897</v>
+        <v>43813</v>
       </c>
       <c r="C588" s="3" t="inlineStr">
         <is>
-          <t>Shah Alam Shazu</t>
+          <t>Muhammad Abdul Jalil</t>
         </is>
       </c>
       <c r="D588" s="3" t="inlineStr">
         <is>
-          <t>Dr Enamul Haq reminisces Bangabandhu’s historic 7th March speech</t>
+          <t>Tojammel Hossen- Someone like my brother</t>
         </is>
       </c>
       <c r="E588" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/arts-entertainment/news/dr-enamul-haq-reminisces-bangabandhus-historic-7th-march-speech-1877314</t>
+          <t>https://www.thedailystar.net/supplements/martyred-intellectuals-day-2019/news/tojammel-hossen-someone-my-brother-1840198</t>
         </is>
       </c>
     </row>
@@ -16736,7 +16736,7 @@
         <v>588</v>
       </c>
       <c r="B589" s="2" t="n">
-        <v>43897</v>
+        <v>43814</v>
       </c>
       <c r="C589" s="3" t="inlineStr">
         <is>
@@ -16745,12 +16745,12 @@
       </c>
       <c r="D589" s="3" t="inlineStr">
         <is>
-          <t>Historic 7th March</t>
+          <t>Martyred Intellectuals Day</t>
         </is>
       </c>
       <c r="E589" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/editorial/news/historic-7th-march-1877395</t>
+          <t>https://www.thedailystar.net/editorial/news/martyred-intellectuals-day-1840315</t>
         </is>
       </c>
     </row>
@@ -16759,21 +16759,21 @@
         <v>589</v>
       </c>
       <c r="B590" s="2" t="n">
-        <v>43914</v>
+        <v>43814</v>
       </c>
       <c r="C590" s="3" t="inlineStr">
         <is>
-          <t>Mannan Mashhur Zarif</t>
+          <t>The Daily Star</t>
         </is>
       </c>
       <c r="D590" s="3" t="inlineStr">
         <is>
-          <t>Posters of 1971 A guide to freedom</t>
+          <t>On this day in 1971</t>
         </is>
       </c>
       <c r="E590" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/lifestyle/news/posters-1971-guide-freedom-1884862</t>
+          <t>https://www.thedailystar.net/frontpage/news/day-1971-1840465</t>
         </is>
       </c>
     </row>
@@ -16782,21 +16782,21 @@
         <v>590</v>
       </c>
       <c r="B591" s="2" t="n">
-        <v>43915</v>
+        <v>43814</v>
       </c>
       <c r="C591" s="3" t="inlineStr">
         <is>
-          <t>The Daily Star</t>
+          <t>Mohammad Al-Masum Molla</t>
         </is>
       </c>
       <c r="D591" s="3" t="inlineStr">
         <is>
-          <t>Prelude to an order for genocide</t>
+          <t>Perfect cover for freedom fighters</t>
         </is>
       </c>
       <c r="E591" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/opinion/news/prelude-order-genocide-1885354</t>
+          <t>https://www.thedailystar.net/backpage/news/perfect-cover-freedom-fighters-1840432</t>
         </is>
       </c>
     </row>
@@ -16805,21 +16805,21 @@
         <v>591</v>
       </c>
       <c r="B592" s="2" t="n">
-        <v>43916</v>
+        <v>43815</v>
       </c>
       <c r="C592" s="3" t="inlineStr">
         <is>
-          <t>Mayabee Arannya</t>
+          <t>Amanullah</t>
         </is>
       </c>
       <c r="D592" s="3" t="inlineStr">
         <is>
-          <t>Counting the days to independence</t>
+          <t>A bloody war and how I witnessed it</t>
         </is>
       </c>
       <c r="E592" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/supplements/news/counting-the-days-independence-1886146</t>
+          <t>https://www.thedailystar.net/supplements/news/bloody-war-and-how-i-witnessed-it-1840579</t>
         </is>
       </c>
     </row>
@@ -16828,21 +16828,21 @@
         <v>592</v>
       </c>
       <c r="B593" s="2" t="n">
-        <v>43916</v>
+        <v>43815</v>
       </c>
       <c r="C593" s="3" t="inlineStr">
         <is>
-          <t>The Daily Star</t>
+          <t>Muhammad Nurul Huda</t>
         </is>
       </c>
       <c r="D593" s="3" t="inlineStr">
         <is>
-          <t>Stories of 71</t>
+          <t>Bangladesh Police in Liberation War</t>
         </is>
       </c>
       <c r="E593" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/shout/news/stories-71-1886185</t>
+          <t>https://www.thedailystar.net/supplements/news/bangladesh-police-liberation-war-1840564</t>
         </is>
       </c>
     </row>
@@ -16851,21 +16851,21 @@
         <v>593</v>
       </c>
       <c r="B594" s="2" t="n">
-        <v>43938</v>
+        <v>43815</v>
       </c>
       <c r="C594" s="3" t="inlineStr">
         <is>
-          <t>Zahid Hossain</t>
+          <t>Tamanna Khan and Tuhin Shubhra Adhikary</t>
         </is>
       </c>
       <c r="D594" s="3" t="inlineStr">
         <is>
-          <t>Mujibnagar Day: A milestone in the War of Liberation</t>
+          <t>Blood, sweat, tears</t>
         </is>
       </c>
       <c r="E594" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/opinion/news/mujibnagar-day-milestone-the-war-liberation-1893541</t>
+          <t>https://www.thedailystar.net/frontpage/victory-day-2019-blood-sweat-tears-1840861</t>
         </is>
       </c>
     </row>
@@ -16874,21 +16874,21 @@
         <v>594</v>
       </c>
       <c r="B595" s="2" t="n">
-        <v>44087</v>
+        <v>43815</v>
       </c>
       <c r="C595" s="3" t="inlineStr">
         <is>
-          <t>Shahnoor Wahid</t>
+          <t>Mishuk Ashraful Awal</t>
         </is>
       </c>
       <c r="D595" s="3" t="inlineStr">
         <is>
-          <t>From the archives: Freedom fight by two missionaries</t>
+          <t>Documenting Liberation through his Lens</t>
         </is>
       </c>
       <c r="E595" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/1971-liberation-war-articles/news/the-archives-freedom-fight-two-missionaries-1960529</t>
+          <t>https://www.thedailystar.net/supplements/news/documenting-liberation-through-his-lens-1840576</t>
         </is>
       </c>
     </row>
@@ -16897,21 +16897,21 @@
         <v>595</v>
       </c>
       <c r="B596" s="2" t="n">
-        <v>44168</v>
+        <v>43815</v>
       </c>
       <c r="C596" s="3" t="inlineStr">
         <is>
-          <t>S Dilip Roy and Firoz A Muzahid</t>
+          <t>Mohiuddin Alamgir</t>
         </is>
       </c>
       <c r="D596" s="3" t="inlineStr">
         <is>
-          <t>The ‘Birangona’ we never knew</t>
+          <t>Of bravery, of Betiara</t>
         </is>
       </c>
       <c r="E596" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/country/news/the-birangona-we-never-knew-2004973</t>
+          <t>https://www.thedailystar.net/frontpage/victory-day-2019-of-bravery-of-betiara-1840852</t>
         </is>
       </c>
     </row>
@@ -16920,21 +16920,21 @@
         <v>596</v>
       </c>
       <c r="B597" s="2" t="n">
-        <v>44179</v>
+        <v>43815</v>
       </c>
       <c r="C597" s="3" t="inlineStr">
         <is>
-          <t>Arun Bikash Dey</t>
+          <t>The Daily Star</t>
         </is>
       </c>
       <c r="D597" s="3" t="inlineStr">
         <is>
-          <t>Of unsung martyred intellectuals</t>
+          <t>On this day in 1971</t>
         </is>
       </c>
       <c r="E597" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/city/news/unsung-martyred-intellectuals-2011041</t>
+          <t>https://www.thedailystar.net/frontpage/news/day-1971-1840846</t>
         </is>
       </c>
     </row>
@@ -16943,21 +16943,21 @@
         <v>597</v>
       </c>
       <c r="B598" s="2" t="n">
-        <v>44179</v>
+        <v>43815</v>
       </c>
       <c r="C598" s="3" t="inlineStr">
         <is>
-          <t>Shuprova Tasneem</t>
+          <t>Minam Haque</t>
         </is>
       </c>
       <c r="D598" s="3" t="inlineStr">
         <is>
-          <t>The last days of a martyred intellectual</t>
+          <t>One of Kamrul Alam Khan Khasru’s valiant missions</t>
         </is>
       </c>
       <c r="E598" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/supplements/news/the-last-days-martyred-intellectual-2010753</t>
+          <t>https://www.thedailystar.net/supplements/victory-day-special-2019/news/one-kamrul-alam-khan-khasrus-valiant-missions-1840585</t>
         </is>
       </c>
     </row>
@@ -16966,21 +16966,21 @@
         <v>598</v>
       </c>
       <c r="B599" s="2" t="n">
-        <v>44181</v>
+        <v>43815</v>
       </c>
       <c r="C599" s="3" t="inlineStr">
         <is>
-          <t>Sartaj Alim</t>
+          <t>Prakash Bhandari</t>
         </is>
       </c>
       <c r="D599" s="3" t="inlineStr">
         <is>
-          <t>Benapole stronghold: The free land of 1971</t>
+          <t>Sagat Singh — An unsung hero</t>
         </is>
       </c>
       <c r="E599" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/opinion/news/benapole-stronghold-the-free-land-1971-2011973</t>
+          <t>https://www.thedailystar.net/supplements/news/sagat-singh-unsung-hero-1840570</t>
         </is>
       </c>
     </row>
@@ -16989,21 +16989,21 @@
         <v>599</v>
       </c>
       <c r="B600" s="2" t="n">
-        <v>44181</v>
+        <v>43815</v>
       </c>
       <c r="C600" s="3" t="inlineStr">
         <is>
-          <t>Ahmad Ahsan</t>
+          <t>Zahangir Alom</t>
         </is>
       </c>
       <c r="D600" s="3" t="inlineStr">
         <is>
-          <t>Our pride and glory: The Mukti Bahini in 1971</t>
+          <t>Serenading the sublime souls of the soil</t>
         </is>
       </c>
       <c r="E600" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/opinion/news/our-pride-and-glory-the-mukti-bahini-1971-2011981</t>
+          <t>https://www.thedailystar.net/supplements/news/serenading-the-sublime-souls-the-soil-1840558</t>
         </is>
       </c>
     </row>
@@ -17012,21 +17012,21 @@
         <v>600</v>
       </c>
       <c r="B601" s="2" t="n">
-        <v>44181</v>
+        <v>43815</v>
       </c>
       <c r="C601" s="3" t="inlineStr">
         <is>
-          <t>Abdullah Shibli</t>
+          <t>Anwar Ali</t>
         </is>
       </c>
       <c r="D601" s="3" t="inlineStr">
         <is>
-          <t>Remembering the hardships we faced in 1971</t>
+          <t>‘Chose this land over my father’</t>
         </is>
       </c>
       <c r="E601" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/opinion/open-dialogue/news/remembering-the-hardships-we-faced-1971-2011997</t>
+          <t>https://www.thedailystar.net/city/news/chose-land-over-my-father-1841023</t>
         </is>
       </c>
     </row>
@@ -17035,21 +17035,21 @@
         <v>601</v>
       </c>
       <c r="B602" s="2" t="n">
-        <v>44242</v>
+        <v>43816</v>
       </c>
       <c r="C602" s="3" t="inlineStr">
         <is>
-          <t>Shah Tazrian Ashrafi</t>
+          <t>The Daily Star</t>
         </is>
       </c>
       <c r="D602" s="3" t="inlineStr">
         <is>
-          <t>The Liberation War: A reading list</t>
+          <t>On this day in 1971</t>
         </is>
       </c>
       <c r="E602" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/supplements/30th-anniversary-supplements/agents-change/news/the-liberation-war-reading-list-2044793</t>
+          <t>https://www.thedailystar.net/backpage/news/day-1971-1841272</t>
         </is>
       </c>
     </row>
@@ -17058,21 +17058,21 @@
         <v>602</v>
       </c>
       <c r="B603" s="2" t="n">
-        <v>44258</v>
+        <v>43816</v>
       </c>
       <c r="C603" s="3" t="inlineStr">
         <is>
-          <t>Ahmed Humayun Kabir Topu</t>
+          <t>Justice Obaidul Hassan</t>
         </is>
       </c>
       <c r="D603" s="3" t="inlineStr">
         <is>
-          <t>Mosque bears horrific memories of 1971</t>
+          <t>Role of Baljit Singh Tyagi and BSF in our Liberation War</t>
         </is>
       </c>
       <c r="E603" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/country/news/mosque-bears-horrific-memories-1971-2054109</t>
+          <t>https://www.thedailystar.net/opinion/news/role-baljit-singh-tyagi-and-bsf-our-liberation-war-1841140</t>
         </is>
       </c>
     </row>
@@ -17081,21 +17081,21 @@
         <v>603</v>
       </c>
       <c r="B604" s="2" t="n">
-        <v>44262</v>
+        <v>43817</v>
       </c>
       <c r="C604" s="3" t="inlineStr">
         <is>
-          <t>M Rafiqul Islam</t>
+          <t>The Daily Star</t>
         </is>
       </c>
       <c r="D604" s="3" t="inlineStr">
         <is>
-          <t>The Historic Seventh March Speech of Bangabandhu: Its Influence on International Legal Discourse and Reform</t>
+          <t>On this day in 1971</t>
         </is>
       </c>
       <c r="E604" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/law-our-rights/news/the-historic-seventh-march-speech-bangabandhu-its-influence-international-legal-discourse-and-reform-2056313</t>
+          <t>https://www.thedailystar.net/backpage/news/day-1971-1841626</t>
         </is>
       </c>
     </row>
@@ -17104,21 +17104,21 @@
         <v>604</v>
       </c>
       <c r="B605" s="2" t="n">
-        <v>44262</v>
+        <v>43818</v>
       </c>
       <c r="C605" s="3" t="inlineStr">
         <is>
-          <t>Asif Muztaba Hassan</t>
+          <t>The Daily Star</t>
         </is>
       </c>
       <c r="D605" s="3" t="inlineStr">
         <is>
-          <t>What makes the 7th March speech one of the best?</t>
+          <t>On this day in 1971</t>
         </is>
       </c>
       <c r="E605" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/opinion/online-exclusive/news/what-makes-the-7th-march-speech-one-the-best-2056453</t>
+          <t>https://www.thedailystar.net/backpage/news/day-1971-1842187</t>
         </is>
       </c>
     </row>
@@ -17127,21 +17127,21 @@
         <v>605</v>
       </c>
       <c r="B606" s="2" t="n">
-        <v>44271</v>
+        <v>43819</v>
       </c>
       <c r="C606" s="3" t="inlineStr">
         <is>
-          <t>Shamsuddoza Sajen</t>
+          <t>The Daily Star</t>
         </is>
       </c>
       <c r="D606" s="3" t="inlineStr">
         <is>
-          <t>Road to Freedom: This Day in Bangladesh Liberation War History</t>
+          <t>On this day in 1971</t>
         </is>
       </c>
       <c r="E606" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/backpage/news/road-freedom-day-bangladesh-liberation-war-history-2061241</t>
+          <t>https://www.thedailystar.net/backpage/news/day-1971-1842628</t>
         </is>
       </c>
     </row>
@@ -17150,21 +17150,21 @@
         <v>606</v>
       </c>
       <c r="B607" s="2" t="n">
-        <v>44273</v>
+        <v>43820</v>
       </c>
       <c r="C607" s="3" t="inlineStr">
         <is>
-          <t>Shamsuddoza Sajen</t>
+          <t>The Daily Star</t>
         </is>
       </c>
       <c r="D607" s="3" t="inlineStr">
         <is>
-          <t>Operation searchlight inked</t>
+          <t>On this day in 1971</t>
         </is>
       </c>
       <c r="E607" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/backpage/news/operation-searchlight-inked-2062417</t>
+          <t>https://www.thedailystar.net/frontpage/news/day-1971-1843123</t>
         </is>
       </c>
     </row>
@@ -17173,21 +17173,21 @@
         <v>607</v>
       </c>
       <c r="B608" s="2" t="n">
-        <v>44275</v>
+        <v>43822</v>
       </c>
       <c r="C608" s="3" t="inlineStr">
         <is>
-          <t>Zakia Afrin</t>
+          <t>The Daily Star</t>
         </is>
       </c>
       <c r="D608" s="3" t="inlineStr">
         <is>
-          <t>A Review of War heroines Speak: The Rape of Bangladeshi Women in 1971 War of Independence</t>
+          <t>On this day in 1971</t>
         </is>
       </c>
       <c r="E608" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/literature/news/review-war-heroines-speak-the-rape-bangladeshi-women-1971-war-independence-2063693</t>
+          <t>https://www.thedailystar.net/backpage/news/day-1971-1843864</t>
         </is>
       </c>
     </row>
@@ -17196,21 +17196,21 @@
         <v>608</v>
       </c>
       <c r="B609" s="2" t="n">
-        <v>44278</v>
+        <v>43823</v>
       </c>
       <c r="C609" s="3" t="inlineStr">
         <is>
-          <t>Sanaul Huq Chowdhury</t>
+          <t>The Daily Star</t>
         </is>
       </c>
       <c r="D609" s="3" t="inlineStr">
         <is>
-          <t>The dark night memories of 25 March 1971</t>
+          <t>On this day in 1971</t>
         </is>
       </c>
       <c r="E609" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/lifestyle/perspective/news/the-dark-night-memories-25-march-1971-2065057</t>
+          <t>https://www.thedailystar.net/backpage/news/day-1971-1844326</t>
         </is>
       </c>
     </row>
@@ -17219,21 +17219,21 @@
         <v>609</v>
       </c>
       <c r="B610" s="2" t="n">
-        <v>44280</v>
+        <v>43824</v>
       </c>
       <c r="C610" s="3" t="inlineStr">
         <is>
-          <t>Partha Pratim Bhattacharjee and Wasim Bin Habib</t>
+          <t>The Daily Star</t>
         </is>
       </c>
       <c r="D610" s="3" t="inlineStr">
         <is>
-          <t>Operation Searchlight: Never seen so many bodies</t>
+          <t>On this day in 1971</t>
         </is>
       </c>
       <c r="E610" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/news/bangladesh/news/operation-searchlight-never-seen-so-many-bodies-2066229</t>
+          <t>https://www.thedailystar.net/backpage/news/day-1971-1844836</t>
         </is>
       </c>
     </row>
@@ -17242,21 +17242,21 @@
         <v>610</v>
       </c>
       <c r="B611" s="2" t="n">
-        <v>44280</v>
+        <v>43825</v>
       </c>
       <c r="C611" s="3" t="inlineStr">
         <is>
-          <t>Asrar Chowdhury</t>
+          <t>The Daily Star</t>
         </is>
       </c>
       <c r="D611" s="3" t="inlineStr">
         <is>
-          <t>Swadhin Bangla Betar Kendra</t>
+          <t>On this day in 1971</t>
         </is>
       </c>
       <c r="E611" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/shout/news/swadhin-bangla-betar-kendra-2066373</t>
+          <t>https://www.thedailystar.net/frontpage/news/day-1971-1845265</t>
         </is>
       </c>
     </row>
@@ -17265,21 +17265,21 @@
         <v>611</v>
       </c>
       <c r="B612" s="2" t="n">
-        <v>44281</v>
+        <v>43826</v>
       </c>
       <c r="C612" s="3" t="inlineStr">
         <is>
-          <t>Shamsuddoza Sajen</t>
+          <t>The Daily Star</t>
         </is>
       </c>
       <c r="D612" s="3" t="inlineStr">
         <is>
-          <t>Bangabandhu declares independence</t>
+          <t>On this day in 1971</t>
         </is>
       </c>
       <c r="E612" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/backpage/news/bangabandhu-declares-independence-2066861</t>
+          <t>https://www.thedailystar.net/backpage/news/day-1971-1845622</t>
         </is>
       </c>
     </row>
@@ -17288,21 +17288,21 @@
         <v>612</v>
       </c>
       <c r="B613" s="2" t="n">
-        <v>44281</v>
+        <v>43827</v>
       </c>
       <c r="C613" s="3" t="inlineStr">
         <is>
-          <t>Rasheek Tabassum Mondira</t>
+          <t>The Daily Star</t>
         </is>
       </c>
       <c r="D613" s="3" t="inlineStr">
         <is>
-          <t>Dhanua Kamalpur Cooperative High School: Home of sixty freedom fighters</t>
+          <t>On this day in 1971</t>
         </is>
       </c>
       <c r="E613" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/star-youth/news/dhanua-kamalpur-cooperative-high-school-home-sixty-freedom-fighters-2067181</t>
+          <t>https://www.thedailystar.net/backpage/news/day-1971-1846141</t>
         </is>
       </c>
     </row>
@@ -17311,21 +17311,21 @@
         <v>613</v>
       </c>
       <c r="B614" s="2" t="n">
-        <v>44281</v>
+        <v>43828</v>
       </c>
       <c r="C614" s="3" t="inlineStr">
         <is>
-          <t>Amanur Aman</t>
+          <t>The Daily Star</t>
         </is>
       </c>
       <c r="D614" s="3" t="inlineStr">
         <is>
-          <t>Kohinoor Villa Massacre: Blood-soaked house of horror of 1971</t>
+          <t>On this day in 1971</t>
         </is>
       </c>
       <c r="E614" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/supplements/71-memory-lane/news/kohinoor-villa-massacre-blood-soaked-house-horror-1971-2066769</t>
+          <t>https://www.thedailystar.net/backpage/news/day-1971-1846756</t>
         </is>
       </c>
     </row>
@@ -17334,21 +17334,21 @@
         <v>614</v>
       </c>
       <c r="B615" s="2" t="n">
-        <v>44281</v>
+        <v>43829</v>
       </c>
       <c r="C615" s="3" t="inlineStr">
         <is>
-          <t>Mirza Shakil</t>
+          <t>The Daily Star</t>
         </is>
       </c>
       <c r="D615" s="3" t="inlineStr">
         <is>
-          <t>Operation Jahajmara: A turning point in the Liberation War history</t>
+          <t>On this day in 1971</t>
         </is>
       </c>
       <c r="E615" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/country/news/operation-jahajmara-turning-point-the-liberation-war-history-2067061</t>
+          <t>https://www.thedailystar.net/backpage/news/day-1971-1847032</t>
         </is>
       </c>
     </row>
@@ -17357,21 +17357,21 @@
         <v>615</v>
       </c>
       <c r="B616" s="2" t="n">
-        <v>44281</v>
+        <v>43830</v>
       </c>
       <c r="C616" s="3" t="inlineStr">
         <is>
-          <t>Jinat Jahan Khan</t>
+          <t>The Daily Star</t>
         </is>
       </c>
       <c r="D616" s="3" t="inlineStr">
         <is>
-          <t>Swadhin Bangla Betar Kendra: the source of inspiration and bravado during the liberation war</t>
+          <t>On this day in 1971</t>
         </is>
       </c>
       <c r="E616" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/tech-startup/news/swadhin-bangla-betar-kendra-the-source-inspiration-and-bravado-during-the-liberation-war-2067077</t>
+          <t>https://www.thedailystar.net/backpage/news/day-1971-1847383</t>
         </is>
       </c>
     </row>
@@ -17380,21 +17380,21 @@
         <v>616</v>
       </c>
       <c r="B617" s="2" t="n">
-        <v>44281</v>
+        <v>43897</v>
       </c>
       <c r="C617" s="3" t="inlineStr">
         <is>
-          <t>Sushanta Ghosh</t>
+          <t>Shah Alam Shazu</t>
         </is>
       </c>
       <c r="D617" s="3" t="inlineStr">
         <is>
-          <t>The battle of Beni Commander</t>
+          <t>Dr Enamul Haq reminisces Bangabandhu’s historic 7th March speech</t>
         </is>
       </c>
       <c r="E617" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/supplements/71-memory-lane/news/the-battle-beni-commander-2066761</t>
+          <t>https://www.thedailystar.net/arts-entertainment/news/dr-enamul-haq-reminisces-bangabandhus-historic-7th-march-speech-1877314</t>
         </is>
       </c>
     </row>
@@ -17403,21 +17403,21 @@
         <v>617</v>
       </c>
       <c r="B618" s="2" t="n">
-        <v>44281</v>
+        <v>43897</v>
       </c>
       <c r="C618" s="3" t="inlineStr">
         <is>
-          <t>Anwar Ali</t>
+          <t>The Daily Star</t>
         </is>
       </c>
       <c r="D618" s="3" t="inlineStr">
         <is>
-          <t>Words unsaid, wounds deep</t>
+          <t>Historic 7th March</t>
         </is>
       </c>
       <c r="E618" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/supplements/71-memory-lane/news/words-unsaid-wounds-deep-2066801</t>
+          <t>https://www.thedailystar.net/editorial/news/historic-7th-march-1877395</t>
         </is>
       </c>
     </row>
@@ -17426,21 +17426,21 @@
         <v>618</v>
       </c>
       <c r="B619" s="2" t="n">
-        <v>44303</v>
+        <v>43914</v>
       </c>
       <c r="C619" s="3" t="inlineStr">
         <is>
-          <t>The Daily Star</t>
+          <t>Mannan Mashhur Zarif</t>
         </is>
       </c>
       <c r="D619" s="3" t="inlineStr">
         <is>
-          <t>A Nation Rises</t>
+          <t>Posters of 1971 A guide to freedom</t>
         </is>
       </c>
       <c r="E619" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/supplements/historic-mujibnagar-day/news/nation-rises-2078869</t>
+          <t>https://www.thedailystar.net/lifestyle/news/posters-1971-guide-freedom-1884862</t>
         </is>
       </c>
     </row>
@@ -17449,21 +17449,21 @@
         <v>619</v>
       </c>
       <c r="B620" s="2" t="n">
-        <v>44303</v>
+        <v>43915</v>
       </c>
       <c r="C620" s="3" t="inlineStr">
         <is>
-          <t>Brig R P Singh, VSM (retired)</t>
+          <t>The Daily Star</t>
         </is>
       </c>
       <c r="D620" s="3" t="inlineStr">
         <is>
-          <t>An eyewitness account of the Mujibnagar government’s swearing-in ceremony</t>
+          <t>Prelude to an order for genocide</t>
         </is>
       </c>
       <c r="E620" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/opinion/news/eyewitness-account-the-mujibnagar-governments-swearing-ceremony-2078617</t>
+          <t>https://www.thedailystar.net/opinion/news/prelude-order-genocide-1885354</t>
         </is>
       </c>
     </row>
@@ -17472,21 +17472,21 @@
         <v>620</v>
       </c>
       <c r="B621" s="2" t="n">
-        <v>44303</v>
+        <v>43916</v>
       </c>
       <c r="C621" s="3" t="inlineStr">
         <is>
-          <t>Subho Basu</t>
+          <t>Mayabee Arannya</t>
         </is>
       </c>
       <c r="D621" s="3" t="inlineStr">
         <is>
-          <t>From movement to a nation</t>
+          <t>Counting the days to independence</t>
         </is>
       </c>
       <c r="E621" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/supplements/historic-mujibnagar-day/news/movement-nation-2078873</t>
+          <t>https://www.thedailystar.net/supplements/news/counting-the-days-independence-1886146</t>
         </is>
       </c>
     </row>
@@ -17495,21 +17495,21 @@
         <v>621</v>
       </c>
       <c r="B622" s="2" t="n">
-        <v>44303</v>
+        <v>43916</v>
       </c>
       <c r="C622" s="3" t="inlineStr">
         <is>
-          <t>Mohiuddin Alamgir</t>
+          <t>The Daily Star</t>
         </is>
       </c>
       <c r="D622" s="3" t="inlineStr">
         <is>
-          <t>Historic Mujibnagar Day: A milestone in our history</t>
+          <t>Stories of 71</t>
         </is>
       </c>
       <c r="E622" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/frontpage/news/historic-mujibnagar-day-milestone-our-history-2078673</t>
+          <t>https://www.thedailystar.net/shout/news/stories-71-1886185</t>
         </is>
       </c>
     </row>
@@ -17518,21 +17518,21 @@
         <v>622</v>
       </c>
       <c r="B623" s="2" t="n">
-        <v>44303</v>
+        <v>43938</v>
       </c>
       <c r="C623" s="3" t="inlineStr">
         <is>
-          <t>Tawfiq-e-Elahi Chowdhury and Bir Bikram</t>
+          <t>Zahid Hossain</t>
         </is>
       </c>
       <c r="D623" s="3" t="inlineStr">
         <is>
-          <t>Looking back: April 17, 1971</t>
+          <t>Mujibnagar Day: A milestone in the War of Liberation</t>
         </is>
       </c>
       <c r="E623" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/supplements/historic-mujibnagar-day/news/looking-back-april-17-1971-2078865</t>
+          <t>https://www.thedailystar.net/opinion/news/mujibnagar-day-milestone-the-war-liberation-1893541</t>
         </is>
       </c>
     </row>
@@ -17541,21 +17541,21 @@
         <v>623</v>
       </c>
       <c r="B624" s="2" t="n">
-        <v>44303</v>
+        <v>44087</v>
       </c>
       <c r="C624" s="3" t="inlineStr">
         <is>
-          <t>Shamsuddoza Sajen</t>
+          <t>Shahnoor Wahid</t>
         </is>
       </c>
       <c r="D624" s="3" t="inlineStr">
         <is>
-          <t>Mujibnagar government sworn in</t>
+          <t>From the archives: Freedom fight by two missionaries</t>
         </is>
       </c>
       <c r="E624" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/backpage/news/mujibnagar-government-sworn-2078841</t>
+          <t>https://www.thedailystar.net/1971-liberation-war-articles/news/the-archives-freedom-fight-two-missionaries-1960529</t>
         </is>
       </c>
     </row>
@@ -17564,21 +17564,21 @@
         <v>624</v>
       </c>
       <c r="B625" s="2" t="n">
-        <v>44303</v>
+        <v>44168</v>
       </c>
       <c r="C625" s="3" t="inlineStr">
         <is>
-          <t>The Daily Star</t>
+          <t>S Dilip Roy and Firoz A Muzahid</t>
         </is>
       </c>
       <c r="D625" s="3" t="inlineStr">
         <is>
-          <t>To the people of the world</t>
+          <t>The ‘Birangona’ we never knew</t>
         </is>
       </c>
       <c r="E625" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/supplements/historic-mujibnagar-day/news/the-people-the-world-2078881</t>
+          <t>https://www.thedailystar.net/country/news/the-birangona-we-never-knew-2004973</t>
         </is>
       </c>
     </row>
@@ -17587,21 +17587,21 @@
         <v>625</v>
       </c>
       <c r="B626" s="2" t="n">
-        <v>44309</v>
+        <v>44179</v>
       </c>
       <c r="C626" s="3" t="inlineStr">
         <is>
-          <t>Shamsuddoza Sajen</t>
+          <t>Arun Bikash Dey</t>
         </is>
       </c>
       <c r="D626" s="3" t="inlineStr">
         <is>
-          <t>Mujibnagar cabinet meets</t>
+          <t>Of unsung martyred intellectuals</t>
         </is>
       </c>
       <c r="E626" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/backpage/news/mujibnagar-cabinet-meets-2082201</t>
+          <t>https://www.thedailystar.net/city/news/unsung-martyred-intellectuals-2011041</t>
         </is>
       </c>
     </row>
@@ -17610,21 +17610,21 @@
         <v>626</v>
       </c>
       <c r="B627" s="2" t="n">
-        <v>44325</v>
+        <v>44179</v>
       </c>
       <c r="C627" s="3" t="inlineStr">
         <is>
-          <t>Brig RP Singh, VSM (Retired)</t>
+          <t>Shuprova Tasneem</t>
         </is>
       </c>
       <c r="D627" s="3" t="inlineStr">
         <is>
-          <t>Die was cast for Bangladesh’s Liberation War in April 1971</t>
+          <t>The last days of a martyred intellectual</t>
         </is>
       </c>
       <c r="E627" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/opinion/news/die-was-cast-bangladeshs-liberation-war-april-1971-2090509</t>
+          <t>https://www.thedailystar.net/supplements/news/the-last-days-martyred-intellectual-2010753</t>
         </is>
       </c>
     </row>
@@ -17633,21 +17633,21 @@
         <v>627</v>
       </c>
       <c r="B628" s="2" t="n">
-        <v>44360</v>
+        <v>44181</v>
       </c>
       <c r="C628" s="3" t="inlineStr">
         <is>
-          <t>Brig RP Singh, VSM (Retd)</t>
+          <t>Sartaj Alim</t>
         </is>
       </c>
       <c r="D628" s="3" t="inlineStr">
         <is>
-          <t>How Mascarenhas’s report changed Bangladesh’s Liberation War</t>
+          <t>Benapole stronghold: The free land of 1971</t>
         </is>
       </c>
       <c r="E628" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/opinion/news/how-mascarenhass-report-changed-bangladeshs-liberation-war-2109609</t>
+          <t>https://www.thedailystar.net/opinion/news/benapole-stronghold-the-free-land-1971-2011973</t>
         </is>
       </c>
     </row>
@@ -17656,21 +17656,21 @@
         <v>628</v>
       </c>
       <c r="B629" s="2" t="n">
-        <v>44364</v>
+        <v>44181</v>
       </c>
       <c r="C629" s="3" t="inlineStr">
         <is>
-          <t>Ishrat Jahan and Nahaly Nafisa Khan</t>
+          <t>Ahmad Ahsan</t>
         </is>
       </c>
       <c r="D629" s="3" t="inlineStr">
         <is>
-          <t>Remembering the Birangona: The power of personal narratives</t>
+          <t>Our pride and glory: The Mukti Bahini in 1971</t>
         </is>
       </c>
       <c r="E629" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/daily-star-books/news/remembering-the-birangona-the-power-personal-narratives-2112633</t>
+          <t>https://www.thedailystar.net/opinion/news/our-pride-and-glory-the-mukti-bahini-1971-2011981</t>
         </is>
       </c>
     </row>
@@ -17679,21 +17679,21 @@
         <v>629</v>
       </c>
       <c r="B630" s="2" t="n">
-        <v>44384</v>
+        <v>44181</v>
       </c>
       <c r="C630" s="3" t="inlineStr">
         <is>
-          <t>Brig RP Singh, VSM (Retd); Hitesh Singh</t>
+          <t>Abdullah Shibli</t>
         </is>
       </c>
       <c r="D630" s="3" t="inlineStr">
         <is>
-          <t>The Kissinger-Yahya plot against Bangladesh’s liberation</t>
+          <t>Remembering the hardships we faced in 1971</t>
         </is>
       </c>
       <c r="E630" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/views/opinion/news/the-kissinger-yahya-plot-against-bangladeshs-liberation-2124321</t>
+          <t>https://www.thedailystar.net/opinion/open-dialogue/news/remembering-the-hardships-we-faced-1971-2011997</t>
         </is>
       </c>
     </row>
@@ -17702,21 +17702,21 @@
         <v>630</v>
       </c>
       <c r="B631" s="2" t="n">
-        <v>44454</v>
+        <v>44242</v>
       </c>
       <c r="C631" s="3" t="inlineStr">
         <is>
-          <t>Shamsuddoza Sajen</t>
+          <t>Shah Tazrian Ashrafi</t>
         </is>
       </c>
       <c r="D631" s="3" t="inlineStr">
         <is>
-          <t>Malraux wants to join Bangladesh Liberation War</t>
+          <t>The Liberation War: A reading list</t>
         </is>
       </c>
       <c r="E631" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/news/bangladesh/news/malraux-wants-join-bangladesh-liberation-war-2176021</t>
+          <t>https://www.thedailystar.net/supplements/30th-anniversary-supplements/agents-change/news/the-liberation-war-reading-list-2044793</t>
         </is>
       </c>
     </row>
@@ -17725,21 +17725,21 @@
         <v>631</v>
       </c>
       <c r="B632" s="2" t="n">
-        <v>44458</v>
+        <v>44258</v>
       </c>
       <c r="C632" s="3" t="inlineStr">
         <is>
-          <t>Kamal Ahmed</t>
+          <t>Ahmed Humayun Kabir Topu</t>
         </is>
       </c>
       <c r="D632" s="3" t="inlineStr">
         <is>
-          <t>Looking back at the 1971 Concert in Sympathy</t>
+          <t>Mosque bears horrific memories of 1971</t>
         </is>
       </c>
       <c r="E632" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/views/opinion/news/looking-back-the-1971-concert-sympathy-2178786</t>
+          <t>https://www.thedailystar.net/country/news/mosque-bears-horrific-memories-1971-2054109</t>
         </is>
       </c>
     </row>
@@ -17748,21 +17748,21 @@
         <v>632</v>
       </c>
       <c r="B633" s="2" t="n">
-        <v>44464</v>
+        <v>44262</v>
       </c>
       <c r="C633" s="3" t="inlineStr">
         <is>
-          <t>Shamsuddoza Sajen</t>
+          <t>M Rafiqul Islam</t>
         </is>
       </c>
       <c r="D633" s="3" t="inlineStr">
         <is>
-          <t>Mukti Bahini expanded</t>
+          <t>The Historic Seventh March Speech of Bangabandhu: Its Influence on International Legal Discourse and Reform</t>
         </is>
       </c>
       <c r="E633" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/news/bangladesh/news/mukti-bahini-expanded-2183406</t>
+          <t>https://www.thedailystar.net/law-our-rights/news/the-historic-seventh-march-speech-bangabandhu-its-influence-international-legal-discourse-and-reform-2056313</t>
         </is>
       </c>
     </row>
@@ -17771,21 +17771,21 @@
         <v>633</v>
       </c>
       <c r="B634" s="2" t="n">
-        <v>44544</v>
+        <v>44262</v>
       </c>
       <c r="C634" s="3" t="inlineStr">
         <is>
-          <t>Pabitra Sarkar</t>
+          <t>Asif Muztaba Hassan</t>
         </is>
       </c>
       <c r="D634" s="3" t="inlineStr">
         <is>
-          <t>A Squirrel’s Tale</t>
+          <t>What makes the 7th March speech one of the best?</t>
         </is>
       </c>
       <c r="E634" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/supplements/martyred-intellectuals-day-2021/news/squirrels-tale-2916751</t>
+          <t>https://www.thedailystar.net/opinion/online-exclusive/news/what-makes-the-7th-march-speech-one-the-best-2056453</t>
         </is>
       </c>
     </row>
@@ -17794,21 +17794,21 @@
         <v>634</v>
       </c>
       <c r="B635" s="2" t="n">
-        <v>44544</v>
+        <v>44271</v>
       </c>
       <c r="C635" s="3" t="inlineStr">
         <is>
-          <t>Subhash Mukhopadhyay</t>
+          <t>Shamsuddoza Sajen</t>
         </is>
       </c>
       <c r="D635" s="3" t="inlineStr">
         <is>
-          <t>Bhai Zahir Raihan ...</t>
+          <t>Road to Freedom: This Day in Bangladesh Liberation War History</t>
         </is>
       </c>
       <c r="E635" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/supplements/martyred-intellectuals-day-2021/news/bhai-zahir-raihan-2916766</t>
+          <t>https://www.thedailystar.net/backpage/news/road-freedom-day-bangladesh-liberation-war-history-2061241</t>
         </is>
       </c>
     </row>
@@ -17817,21 +17817,21 @@
         <v>635</v>
       </c>
       <c r="B636" s="2" t="n">
-        <v>44544</v>
+        <v>44273</v>
       </c>
       <c r="C636" s="3" t="inlineStr">
         <is>
-          <t>Wasim Bin Habib</t>
+          <t>Shamsuddoza Sajen</t>
         </is>
       </c>
       <c r="D636" s="3" t="inlineStr">
         <is>
-          <t>Martyred Intellectuals Day: A loss not entirely personal</t>
+          <t>Operation searchlight inked</t>
         </is>
       </c>
       <c r="E636" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/news/bangladesh/news/martyred-intellectuals-day-loss-not-entirely-personal-2916891</t>
+          <t>https://www.thedailystar.net/backpage/news/operation-searchlight-inked-2062417</t>
         </is>
       </c>
     </row>
@@ -17840,21 +17840,21 @@
         <v>636</v>
       </c>
       <c r="B637" s="2" t="n">
-        <v>44544</v>
+        <v>44275</v>
       </c>
       <c r="C637" s="3" t="inlineStr">
         <is>
-          <t>Mahmud Shah Qureshi</t>
+          <t>Zakia Afrin</t>
         </is>
       </c>
       <c r="D637" s="3" t="inlineStr">
         <is>
-          <t>The War of Liberation and my humble participation</t>
+          <t>A Review of War heroines Speak: The Rape of Bangladeshi Women in 1971 War of Independence</t>
         </is>
       </c>
       <c r="E637" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/supplements/martyred-intellectuals-day-2021/news/the-war-liberation-and-my-humble-participation-2916741</t>
+          <t>https://www.thedailystar.net/literature/news/review-war-heroines-speak-the-rape-bangladeshi-women-1971-war-independence-2063693</t>
         </is>
       </c>
     </row>
@@ -17863,21 +17863,21 @@
         <v>637</v>
       </c>
       <c r="B638" s="2" t="n">
-        <v>44544</v>
+        <v>44278</v>
       </c>
       <c r="C638" s="3" t="inlineStr">
         <is>
-          <t>The Daily Star</t>
+          <t>Sanaul Huq Chowdhury</t>
         </is>
       </c>
       <c r="D638" s="3" t="inlineStr">
         <is>
-          <t>To Opu and Topu ...</t>
+          <t>The dark night memories of 25 March 1971</t>
         </is>
       </c>
       <c r="E638" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/supplements/martyred-intellectuals-day-2021/news/opu-and-topu-2916771</t>
+          <t>https://www.thedailystar.net/lifestyle/perspective/news/the-dark-night-memories-25-march-1971-2065057</t>
         </is>
       </c>
     </row>
@@ -17886,21 +17886,21 @@
         <v>638</v>
       </c>
       <c r="B639" s="2" t="n">
-        <v>44546</v>
+        <v>44280</v>
       </c>
       <c r="C639" s="3" t="inlineStr">
         <is>
-          <t>Muyeedul Hasan</t>
+          <t>Partha Pratim Bhattacharjee and Wasim Bin Habib</t>
         </is>
       </c>
       <c r="D639" s="3" t="inlineStr">
         <is>
-          <t>1971: PN Haksar in bridging the security gap</t>
+          <t>Operation Searchlight: Never seen so many bodies</t>
         </is>
       </c>
       <c r="E639" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/supplements/victory-day-special-2021/news/1971-pn-haksar-bridging-the-security-gap-2917996</t>
+          <t>https://www.thedailystar.net/news/bangladesh/news/operation-searchlight-never-seen-so-many-bodies-2066229</t>
         </is>
       </c>
     </row>
@@ -17909,21 +17909,21 @@
         <v>639</v>
       </c>
       <c r="B640" s="2" t="n">
-        <v>44546</v>
+        <v>44280</v>
       </c>
       <c r="C640" s="3" t="inlineStr">
         <is>
-          <t>Kaiser Haq</t>
+          <t>Asrar Chowdhury</t>
         </is>
       </c>
       <c r="D640" s="3" t="inlineStr">
         <is>
-          <t>1971: Some fragments of memory</t>
+          <t>Swadhin Bangla Betar Kendra</t>
         </is>
       </c>
       <c r="E640" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/supplements/victory-day-special-2021/news/1971-some-fragments-memory-2918026</t>
+          <t>https://www.thedailystar.net/shout/news/swadhin-bangla-betar-kendra-2066373</t>
         </is>
       </c>
     </row>
@@ -17932,21 +17932,21 @@
         <v>640</v>
       </c>
       <c r="B641" s="2" t="n">
-        <v>44546</v>
+        <v>44281</v>
       </c>
       <c r="C641" s="3" t="inlineStr">
         <is>
-          <t>Sugata Bose</t>
+          <t>Shamsuddoza Sajen</t>
         </is>
       </c>
       <c r="D641" s="3" t="inlineStr">
         <is>
-          <t>A year of sacrificial patriotism</t>
+          <t>Bangabandhu declares independence</t>
         </is>
       </c>
       <c r="E641" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/supplements/victory-day-special-2021/news/year-sacrificial-patriotism-2918006</t>
+          <t>https://www.thedailystar.net/backpage/news/bangabandhu-declares-independence-2066861</t>
         </is>
       </c>
     </row>
@@ -17955,21 +17955,21 @@
         <v>641</v>
       </c>
       <c r="B642" s="2" t="n">
-        <v>44546</v>
+        <v>44281</v>
       </c>
       <c r="C642" s="3" t="inlineStr">
         <is>
-          <t>Capt. (Retd.) Humayun Kabir Chowdhury, Bir Pratik</t>
+          <t>Rasheek Tabassum Mondira</t>
         </is>
       </c>
       <c r="D642" s="3" t="inlineStr">
         <is>
-          <t>An ode to 1971</t>
+          <t>Dhanua Kamalpur Cooperative High School: Home of sixty freedom fighters</t>
         </is>
       </c>
       <c r="E642" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/supplements/victory-day-special-2021/news/ode-1971-2917971</t>
+          <t>https://www.thedailystar.net/star-youth/news/dhanua-kamalpur-cooperative-high-school-home-sixty-freedom-fighters-2067181</t>
         </is>
       </c>
     </row>
@@ -17978,21 +17978,21 @@
         <v>642</v>
       </c>
       <c r="B643" s="2" t="n">
-        <v>44546</v>
+        <v>44281</v>
       </c>
       <c r="C643" s="3" t="inlineStr">
         <is>
-          <t>Inqiad Bin Ali</t>
+          <t>Amanur Aman</t>
         </is>
       </c>
       <c r="D643" s="3" t="inlineStr">
         <is>
-          <t>Behind enemy lines: Story of a Bengali family stuck in Pakistan during 1971</t>
+          <t>Kohinoor Villa Massacre: Blood-soaked house of horror of 1971</t>
         </is>
       </c>
       <c r="E643" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/shout/news/behind-enemy-lines-2917606</t>
+          <t>https://www.thedailystar.net/supplements/71-memory-lane/news/kohinoor-villa-massacre-blood-soaked-house-horror-1971-2066769</t>
         </is>
       </c>
     </row>
@@ -18001,21 +18001,21 @@
         <v>643</v>
       </c>
       <c r="B644" s="2" t="n">
-        <v>44546</v>
+        <v>44281</v>
       </c>
       <c r="C644" s="3" t="inlineStr">
         <is>
-          <t>Syed Jamil Ahmed, PhD</t>
+          <t>Mirza Shakil</t>
         </is>
       </c>
       <c r="D644" s="3" t="inlineStr">
         <is>
-          <t>How nationalist imaginaries were reconstituted in 1971</t>
+          <t>Operation Jahajmara: A turning point in the Liberation War history</t>
         </is>
       </c>
       <c r="E644" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/supplements/victory-day-special-2021/news/how-nationalist-imaginaries-were-reconstituted-1971-2918021</t>
+          <t>https://www.thedailystar.net/country/news/operation-jahajmara-turning-point-the-liberation-war-history-2067061</t>
         </is>
       </c>
     </row>
@@ -18024,21 +18024,21 @@
         <v>644</v>
       </c>
       <c r="B645" s="2" t="n">
-        <v>44546</v>
+        <v>44281</v>
       </c>
       <c r="C645" s="3" t="inlineStr">
         <is>
-          <t>Mohiuddin Alamgir</t>
+          <t>Jinat Jahan Khan</t>
         </is>
       </c>
       <c r="D645" s="3" t="inlineStr">
         <is>
-          <t>Liberated, at last</t>
+          <t>Swadhin Bangla Betar Kendra: the source of inspiration and bravado during the liberation war</t>
         </is>
       </c>
       <c r="E645" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/supplements/victory-day-special-2021/news/liberated-last-2918636</t>
+          <t>https://www.thedailystar.net/tech-startup/news/swadhin-bangla-betar-kendra-the-source-inspiration-and-bravado-during-the-liberation-war-2067077</t>
         </is>
       </c>
     </row>
@@ -18047,21 +18047,21 @@
         <v>645</v>
       </c>
       <c r="B646" s="2" t="n">
-        <v>44546</v>
+        <v>44281</v>
       </c>
       <c r="C646" s="3" t="inlineStr">
         <is>
-          <t>Maisha Islam Monamee</t>
+          <t>Sushanta Ghosh</t>
         </is>
       </c>
       <c r="D646" s="3" t="inlineStr">
         <is>
-          <t>Nonfiction books on the Liberation War released this year</t>
+          <t>The battle of Beni Commander</t>
         </is>
       </c>
       <c r="E646" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/daily-star-books/news/nonfiction-books-the-liberation-war-released-year-2918841</t>
+          <t>https://www.thedailystar.net/supplements/71-memory-lane/news/the-battle-beni-commander-2066761</t>
         </is>
       </c>
     </row>
@@ -18070,21 +18070,21 @@
         <v>646</v>
       </c>
       <c r="B647" s="2" t="n">
-        <v>44546</v>
+        <v>44281</v>
       </c>
       <c r="C647" s="3" t="inlineStr">
         <is>
-          <t>Dwoha Chowdhury and Mintu Deshwara</t>
+          <t>Anwar Ali</t>
         </is>
       </c>
       <c r="D647" s="3" t="inlineStr">
         <is>
-          <t>Red stains in green gardens</t>
+          <t>Words unsaid, wounds deep</t>
         </is>
       </c>
       <c r="E647" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/supplements/victory-day-special-2021/news/red-stains-green-gardens-2918616</t>
+          <t>https://www.thedailystar.net/supplements/71-memory-lane/news/words-unsaid-wounds-deep-2066801</t>
         </is>
       </c>
     </row>
@@ -18093,21 +18093,21 @@
         <v>647</v>
       </c>
       <c r="B648" s="2" t="n">
-        <v>44546</v>
+        <v>44303</v>
       </c>
       <c r="C648" s="3" t="inlineStr">
         <is>
-          <t>Dr. Rudabeh Shahid</t>
+          <t>The Daily Star</t>
         </is>
       </c>
       <c r="D648" s="3" t="inlineStr">
         <is>
-          <t>Retracing the 1971 exodus</t>
+          <t>A Nation Rises</t>
         </is>
       </c>
       <c r="E648" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/supplements/victory-day-special-2021/news/retracing-the-1971-exodus-2918041</t>
+          <t>https://www.thedailystar.net/supplements/historic-mujibnagar-day/news/nation-rises-2078869</t>
         </is>
       </c>
     </row>
@@ -18116,21 +18116,21 @@
         <v>648</v>
       </c>
       <c r="B649" s="2" t="n">
-        <v>44546</v>
+        <v>44303</v>
       </c>
       <c r="C649" s="3" t="inlineStr">
         <is>
-          <t>Mahbub Uddin Ahmed Bir Bikram</t>
+          <t>Brig R P Singh, VSM (retired)</t>
         </is>
       </c>
       <c r="D649" s="3" t="inlineStr">
         <is>
-          <t>Tales of courage and patriotism</t>
+          <t>An eyewitness account of the Mujibnagar government’s swearing-in ceremony</t>
         </is>
       </c>
       <c r="E649" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/supplements/victory-day-special-2021/news/tales-courage-and-patriotism-2917981</t>
+          <t>https://www.thedailystar.net/opinion/news/eyewitness-account-the-mujibnagar-governments-swearing-ceremony-2078617</t>
         </is>
       </c>
     </row>
@@ -18139,21 +18139,21 @@
         <v>649</v>
       </c>
       <c r="B650" s="2" t="n">
-        <v>44546</v>
+        <v>44303</v>
       </c>
       <c r="C650" s="3" t="inlineStr">
         <is>
-          <t>Jayant Prasad</t>
+          <t>Subho Basu</t>
         </is>
       </c>
       <c r="D650" s="3" t="inlineStr">
         <is>
-          <t>The 1971 saga</t>
+          <t>From movement to a nation</t>
         </is>
       </c>
       <c r="E650" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/supplements/victory-day-special-2021/news/the-1971-saga-2917976</t>
+          <t>https://www.thedailystar.net/supplements/historic-mujibnagar-day/news/movement-nation-2078873</t>
         </is>
       </c>
     </row>
@@ -18162,21 +18162,21 @@
         <v>650</v>
       </c>
       <c r="B651" s="2" t="n">
-        <v>44546</v>
+        <v>44303</v>
       </c>
       <c r="C651" s="3" t="inlineStr">
         <is>
-          <t>Priyam Pritim Paul</t>
+          <t>Mohiuddin Alamgir</t>
         </is>
       </c>
       <c r="D651" s="3" t="inlineStr">
         <is>
-          <t>The Chattogram Resistance</t>
+          <t>Historic Mujibnagar Day: A milestone in our history</t>
         </is>
       </c>
       <c r="E651" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/supplements/victory-day-special-2021/news/the-chattogram-resistance-2918051</t>
+          <t>https://www.thedailystar.net/frontpage/news/historic-mujibnagar-day-milestone-our-history-2078673</t>
         </is>
       </c>
     </row>
@@ -18185,21 +18185,21 @@
         <v>651</v>
       </c>
       <c r="B652" s="2" t="n">
-        <v>44546</v>
+        <v>44303</v>
       </c>
       <c r="C652" s="3" t="inlineStr">
         <is>
-          <t>Azibor Rahman</t>
+          <t>Tawfiq-e-Elahi Chowdhury and Bir Bikram</t>
         </is>
       </c>
       <c r="D652" s="3" t="inlineStr">
         <is>
-          <t>They went to sleep never to wake up</t>
+          <t>Looking back: April 17, 1971</t>
         </is>
       </c>
       <c r="E652" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/supplements/victory-day-special-2021/news/they-went-sleep-never-wake-2918631</t>
+          <t>https://www.thedailystar.net/supplements/historic-mujibnagar-day/news/looking-back-april-17-1971-2078865</t>
         </is>
       </c>
     </row>
@@ -18208,21 +18208,21 @@
         <v>652</v>
       </c>
       <c r="B653" s="2" t="n">
-        <v>44546</v>
+        <v>44303</v>
       </c>
       <c r="C653" s="3" t="inlineStr">
         <is>
-          <t>Ahmed Humayun Kabir Topu</t>
+          <t>Shamsuddoza Sajen</t>
         </is>
       </c>
       <c r="D653" s="3" t="inlineStr">
         <is>
-          <t>When living is even more painful</t>
+          <t>Mujibnagar government sworn in</t>
         </is>
       </c>
       <c r="E653" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/supplements/victory-day-special-2021/news/when-living-even-more-painful-2918621</t>
+          <t>https://www.thedailystar.net/backpage/news/mujibnagar-government-sworn-2078841</t>
         </is>
       </c>
     </row>
@@ -18231,21 +18231,21 @@
         <v>653</v>
       </c>
       <c r="B654" s="2" t="n">
-        <v>44547</v>
+        <v>44303</v>
       </c>
       <c r="C654" s="3" t="inlineStr">
         <is>
-          <t>Mahfuz Anam</t>
+          <t>The Daily Star</t>
         </is>
       </c>
       <c r="D654" s="3" t="inlineStr">
         <is>
-          <t>Column by Mahfuz Anam: Golden Jubilee Celebration - Media’s role and the diplomatic challenges in 1971</t>
+          <t>To the people of the world</t>
         </is>
       </c>
       <c r="E654" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/opinion/the-third-view/news/column-mahfuz-anam-golden-jubilee-celebration-medias-role-and-the-diplomatic-challenges-1971-2919256</t>
+          <t>https://www.thedailystar.net/supplements/historic-mujibnagar-day/news/the-people-the-world-2078881</t>
         </is>
       </c>
     </row>
@@ -18254,21 +18254,21 @@
         <v>654</v>
       </c>
       <c r="B655" s="2" t="n">
-        <v>44551</v>
+        <v>44309</v>
       </c>
       <c r="C655" s="3" t="inlineStr">
         <is>
-          <t>Adnan Zillur Morshed</t>
+          <t>Shamsuddoza Sajen</t>
         </is>
       </c>
       <c r="D655" s="3" t="inlineStr">
         <is>
-          <t>Understanding a freedom fighter’s prison letters</t>
+          <t>Mujibnagar cabinet meets</t>
         </is>
       </c>
       <c r="E655" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/opinion/the-grudging-urbanist/news/understanding-freedom-fighters-prison-letters-2921966</t>
+          <t>https://www.thedailystar.net/backpage/news/mujibnagar-cabinet-meets-2082201</t>
         </is>
       </c>
     </row>
@@ -18277,21 +18277,21 @@
         <v>655</v>
       </c>
       <c r="B656" s="2" t="n">
-        <v>44554</v>
+        <v>44323</v>
       </c>
       <c r="C656" s="3" t="inlineStr">
         <is>
-          <t>Pallab Bhattacharya</t>
+          <t>Shamsuddoza Sajen</t>
         </is>
       </c>
       <c r="D656" s="3" t="inlineStr">
         <is>
-          <t>The political rumblings in India over 1971</t>
+          <t>Road to Freedom: This Day in Bangladesh Liberation War History</t>
         </is>
       </c>
       <c r="E656" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/views/opinion/news/the-political-rumblings-india-over-1971-2924301</t>
+          <t>https://www.thedailystar.net/backpage/news/road-freedom-day-bangladesh-liberation-war-history-2089641</t>
         </is>
       </c>
     </row>
@@ -18300,21 +18300,21 @@
         <v>656</v>
       </c>
       <c r="B657" s="2" t="n">
-        <v>44621</v>
+        <v>44325</v>
       </c>
       <c r="C657" s="3" t="inlineStr">
         <is>
-          <t>Mirza Shakil</t>
+          <t>Brig RP Singh, VSM (Retired)</t>
         </is>
       </c>
       <c r="D657" s="3" t="inlineStr">
         <is>
-          <t>Tangail water tank: Mute witness to 1971 massacre</t>
+          <t>Die was cast for Bangladesh’s Liberation War in April 1971</t>
         </is>
       </c>
       <c r="E657" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/news/bangladesh/news/tangail-water-tank-mute-witness-1971-massacre-2972621</t>
+          <t>https://www.thedailystar.net/opinion/news/die-was-cast-bangladeshs-liberation-war-april-1971-2090509</t>
         </is>
       </c>
     </row>
@@ -18323,21 +18323,21 @@
         <v>657</v>
       </c>
       <c r="B658" s="2" t="n">
-        <v>44646</v>
+        <v>44360</v>
       </c>
       <c r="C658" s="3" t="inlineStr">
         <is>
-          <t>Mannan Mashhur Zarif</t>
+          <t>Brig RP Singh, VSM (Retd)</t>
         </is>
       </c>
       <c r="D658" s="3" t="inlineStr">
         <is>
-          <t>London 1971 — A political frontier of the Liberation War</t>
+          <t>How Mascarenhas’s report changed Bangladesh’s Liberation War</t>
         </is>
       </c>
       <c r="E658" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/life-living/news/london-1971-political-frontier-the-liberation-war-2990981</t>
+          <t>https://www.thedailystar.net/opinion/news/how-mascarenhass-report-changed-bangladeshs-liberation-war-2109609</t>
         </is>
       </c>
     </row>
@@ -18346,21 +18346,21 @@
         <v>658</v>
       </c>
       <c r="B659" s="2" t="n">
-        <v>44646</v>
+        <v>44364</v>
       </c>
       <c r="C659" s="3" t="inlineStr">
         <is>
-          <t>Priyam Pritim Paul</t>
+          <t>Ishrat Jahan and Nahaly Nafisa Khan</t>
         </is>
       </c>
       <c r="D659" s="3" t="inlineStr">
         <is>
-          <t>Revisiting 1971 sagas through the lens of a silent witness</t>
+          <t>Remembering the Birangona: The power of personal narratives</t>
         </is>
       </c>
       <c r="E659" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/supplements/celebrating-51-years-independence/news/revisiting-1971-sagas-through-the-lens-silent-witness-2990456</t>
+          <t>https://www.thedailystar.net/daily-star-books/news/remembering-the-birangona-the-power-personal-narratives-2112633</t>
         </is>
       </c>
     </row>
@@ -18369,21 +18369,21 @@
         <v>659</v>
       </c>
       <c r="B660" s="2" t="n">
-        <v>44646</v>
+        <v>44384</v>
       </c>
       <c r="C660" s="3" t="inlineStr">
         <is>
-          <t>Shishir Bhattacharja</t>
+          <t>Brig RP Singh, VSM (Retd); Hitesh Singh</t>
         </is>
       </c>
       <c r="D660" s="3" t="inlineStr">
         <is>
-          <t>Shoronarthir Dinolipi: The diary of a 1971 refugee</t>
+          <t>The Kissinger-Yahya plot against Bangladesh’s liberation</t>
         </is>
       </c>
       <c r="E660" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/supplements/celebrating-51-years-independence/news/shoronarthir-dinolipi-the-diary-1971-refugee-2990481</t>
+          <t>https://www.thedailystar.net/views/opinion/news/the-kissinger-yahya-plot-against-bangladeshs-liberation-2124321</t>
         </is>
       </c>
     </row>
@@ -18392,21 +18392,21 @@
         <v>660</v>
       </c>
       <c r="B661" s="2" t="n">
-        <v>44646</v>
+        <v>44454</v>
       </c>
       <c r="C661" s="3" t="inlineStr">
         <is>
-          <t>Muyeedul Hasan</t>
+          <t>Shamsuddoza Sajen</t>
         </is>
       </c>
       <c r="D661" s="3" t="inlineStr">
         <is>
-          <t>‘1971 Bangladesh – With Unbound Accounts’</t>
+          <t>Malraux wants to join Bangladesh Liberation War</t>
         </is>
       </c>
       <c r="E661" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/supplements/celebrating-51-years-independence/news/1971-bangladesh-unbound-accounts-2990451</t>
+          <t>https://www.thedailystar.net/news/bangladesh/news/malraux-wants-join-bangladesh-liberation-war-2176021</t>
         </is>
       </c>
     </row>
@@ -18415,21 +18415,21 @@
         <v>661</v>
       </c>
       <c r="B662" s="2" t="n">
-        <v>44654</v>
+        <v>44458</v>
       </c>
       <c r="C662" s="3" t="inlineStr">
         <is>
-          <t>BSS, Dhaka</t>
+          <t>Kamal Ahmed</t>
         </is>
       </c>
       <c r="D662" s="3" t="inlineStr">
         <is>
-          <t>Kissinger who called Bangladesh 'basket case' says US role in 1971 was a 'misjudgment'</t>
+          <t>Looking back at the 1971 Concert in Sympathy</t>
         </is>
       </c>
       <c r="E662" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/news/bangladesh/news/kissinger-who-called-bangladesh-basket-case-says-us-role-1971-was-misjudgment-2997121</t>
+          <t>https://www.thedailystar.net/views/opinion/news/looking-back-the-1971-concert-sympathy-2178786</t>
         </is>
       </c>
     </row>
@@ -18438,21 +18438,21 @@
         <v>662</v>
       </c>
       <c r="B663" s="2" t="n">
-        <v>44668</v>
+        <v>44464</v>
       </c>
       <c r="C663" s="3" t="inlineStr">
         <is>
-          <t>Mohiuddin Alamgir</t>
+          <t>Shamsuddoza Sajen</t>
         </is>
       </c>
       <c r="D663" s="3" t="inlineStr">
         <is>
-          <t>Historic Mujibnagar Day: No ordinary guard of honour</t>
+          <t>Mukti Bahini expanded</t>
         </is>
       </c>
       <c r="E663" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/news/bangladesh/news/historic-mujibnagar-day-no-ordinary-guard-honour-3005891</t>
+          <t>https://www.thedailystar.net/news/bangladesh/news/mukti-bahini-expanded-2183406</t>
         </is>
       </c>
     </row>
@@ -18461,21 +18461,21 @@
         <v>663</v>
       </c>
       <c r="B664" s="2" t="n">
-        <v>44668</v>
+        <v>44531</v>
       </c>
       <c r="C664" s="3" t="inlineStr">
         <is>
-          <t>Shams Rahman</t>
+          <t>Shamsuddoza Sajen</t>
         </is>
       </c>
       <c r="D664" s="3" t="inlineStr">
         <is>
-          <t>Mujibnagar Day: How the Mujibnagar government turned the dream for freedom into reality</t>
+          <t>Road to Freedom: This Day in Bangladesh Liberation War History</t>
         </is>
       </c>
       <c r="E664" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/views/opinion/news/mujibnagar-day-how-the-mujibnagar-government-turned-the-dream-freedom-reality-3005976</t>
+          <t>https://www.thedailystar.net/news/bangladesh/news/road-freedom-day-bangladesh-liberation-war-history-2906801</t>
         </is>
       </c>
     </row>
@@ -18484,21 +18484,21 @@
         <v>664</v>
       </c>
       <c r="B665" s="2" t="n">
-        <v>44668</v>
+        <v>44544</v>
       </c>
       <c r="C665" s="3" t="inlineStr">
         <is>
-          <t>Mahbub Uddin Ahmed Bir Bikram</t>
+          <t>Pabitra Sarkar</t>
         </is>
       </c>
       <c r="D665" s="3" t="inlineStr">
         <is>
-          <t>Remembering the oath-taking of Mujibnagar government</t>
+          <t>A Squirrel’s Tale</t>
         </is>
       </c>
       <c r="E665" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/opinion/online-exclusive/news/remembering-the-oath-taking-mujibnagar-government-3006526</t>
+          <t>https://www.thedailystar.net/supplements/martyred-intellectuals-day-2021/news/squirrels-tale-2916751</t>
         </is>
       </c>
     </row>
@@ -18507,21 +18507,21 @@
         <v>665</v>
       </c>
       <c r="B666" s="2" t="n">
-        <v>44735</v>
+        <v>44544</v>
       </c>
       <c r="C666" s="3" t="inlineStr">
         <is>
-          <t>Namrata</t>
+          <t>Subhash Mukhopadhyay</t>
         </is>
       </c>
       <c r="D666" s="3" t="inlineStr">
         <is>
-          <t>Manash Ghosh's ' Bangladesh War': Dispatches of independence</t>
+          <t>Bhai Zahir Raihan ...</t>
         </is>
       </c>
       <c r="E666" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/daily-star-books/news/dispatches-independence-3054366</t>
+          <t>https://www.thedailystar.net/supplements/martyred-intellectuals-day-2021/news/bhai-zahir-raihan-2916766</t>
         </is>
       </c>
     </row>
@@ -18530,21 +18530,21 @@
         <v>666</v>
       </c>
       <c r="B667" s="2" t="n">
-        <v>44765</v>
+        <v>44544</v>
       </c>
       <c r="C667" s="3" t="inlineStr">
         <is>
-          <t>Arunav Das</t>
+          <t>Wasim Bin Habib</t>
         </is>
       </c>
       <c r="D667" s="3" t="inlineStr">
         <is>
-          <t>"Garos of 71": A documentary in search of history</t>
+          <t>Martyred Intellectuals Day: A loss not entirely personal</t>
         </is>
       </c>
       <c r="E667" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/star-literature/news/garos-71-documentary-search-history-3077121</t>
+          <t>https://www.thedailystar.net/news/bangladesh/news/martyred-intellectuals-day-loss-not-entirely-personal-2916891</t>
         </is>
       </c>
     </row>
@@ -18553,21 +18553,21 @@
         <v>667</v>
       </c>
       <c r="B668" s="2" t="n">
-        <v>44854</v>
+        <v>44544</v>
       </c>
       <c r="C668" s="3" t="inlineStr">
         <is>
-          <t>Kazi Zawad</t>
+          <t>Mahmud Shah Qureshi</t>
         </is>
       </c>
       <c r="D668" s="3" t="inlineStr">
         <is>
-          <t>Contradictions in a book on the Bangladesh Liberation War</t>
+          <t>The War of Liberation and my humble participation</t>
         </is>
       </c>
       <c r="E668" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/daily-star-books/news/contradictions-book-the-bangladesh-liberation-war-3147461</t>
+          <t>https://www.thedailystar.net/supplements/martyred-intellectuals-day-2021/news/the-war-liberation-and-my-humble-participation-2916741</t>
         </is>
       </c>
     </row>
@@ -18576,21 +18576,21 @@
         <v>668</v>
       </c>
       <c r="B669" s="2" t="n">
-        <v>44909</v>
+        <v>44544</v>
       </c>
       <c r="C669" s="3" t="inlineStr">
         <is>
-          <t>Kaberi Gayen</t>
+          <t>The Daily Star</t>
         </is>
       </c>
       <c r="D669" s="3" t="inlineStr">
         <is>
-          <t>Legacies of Loss</t>
+          <t>To Opu and Topu ...</t>
         </is>
       </c>
       <c r="E669" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/supplements/martyred-intellectuals-day-2022/news/legacies-loss-3195766</t>
+          <t>https://www.thedailystar.net/supplements/martyred-intellectuals-day-2021/news/opu-and-topu-2916771</t>
         </is>
       </c>
     </row>
@@ -18599,21 +18599,21 @@
         <v>669</v>
       </c>
       <c r="B670" s="2" t="n">
-        <v>44909</v>
+        <v>44546</v>
       </c>
       <c r="C670" s="3" t="inlineStr">
         <is>
-          <t>Ahmad Istiak</t>
+          <t>Muyeedul Hasan</t>
         </is>
       </c>
       <c r="D670" s="3" t="inlineStr">
         <is>
-          <t>Martyred intellectuals day: Murderous scheme</t>
+          <t>1971: PN Haksar in bridging the security gap</t>
         </is>
       </c>
       <c r="E670" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/news/bangladesh/news/martyred-intellectuals-day-murderous-scheme-3195581</t>
+          <t>https://www.thedailystar.net/supplements/victory-day-special-2021/news/1971-pn-haksar-bridging-the-security-gap-2917996</t>
         </is>
       </c>
     </row>
@@ -18622,21 +18622,21 @@
         <v>670</v>
       </c>
       <c r="B671" s="2" t="n">
-        <v>44909</v>
+        <v>44546</v>
       </c>
       <c r="C671" s="3" t="inlineStr">
         <is>
-          <t>Abdul Momin Chowdhury</t>
+          <t>Kaiser Haq</t>
         </is>
       </c>
       <c r="D671" s="3" t="inlineStr">
         <is>
-          <t>My three martyred teachers</t>
+          <t>1971: Some fragments of memory</t>
         </is>
       </c>
       <c r="E671" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/supplements/martyred-intellectuals-day-2022/news/my-three-martyred-teachers-3195776</t>
+          <t>https://www.thedailystar.net/supplements/victory-day-special-2021/news/1971-some-fragments-memory-2918026</t>
         </is>
       </c>
     </row>
@@ -18645,21 +18645,21 @@
         <v>671</v>
       </c>
       <c r="B672" s="2" t="n">
-        <v>44909</v>
+        <v>44546</v>
       </c>
       <c r="C672" s="3" t="inlineStr">
         <is>
-          <t>Meghna Guhathakurta</t>
+          <t>Sugata Bose</t>
         </is>
       </c>
       <c r="D672" s="3" t="inlineStr">
         <is>
-          <t>My ’71: Experiencing Genocide, Understanding Violence</t>
+          <t>A year of sacrificial patriotism</t>
         </is>
       </c>
       <c r="E672" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/supplements/martyred-intellectuals-day-2022/news/my-71-experiencing-genocide-understanding-violence-3195761</t>
+          <t>https://www.thedailystar.net/supplements/victory-day-special-2021/news/year-sacrificial-patriotism-2918006</t>
         </is>
       </c>
     </row>
@@ -18668,21 +18668,21 @@
         <v>672</v>
       </c>
       <c r="B673" s="2" t="n">
-        <v>44910</v>
+        <v>44546</v>
       </c>
       <c r="C673" s="3" t="inlineStr">
         <is>
-          <t>Fabiha Afifa</t>
+          <t>Capt. (Retd.) Humayun Kabir Chowdhury, Bir Pratik</t>
         </is>
       </c>
       <c r="D673" s="3" t="inlineStr">
         <is>
-          <t>The price of victory: 1971 and the mental health of a generation</t>
+          <t>An ode to 1971</t>
         </is>
       </c>
       <c r="E673" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/shout/cover-story/news/the-price-victory-1971-and-the-mental-health-generation-3196816</t>
+          <t>https://www.thedailystar.net/supplements/victory-day-special-2021/news/ode-1971-2917971</t>
         </is>
       </c>
     </row>
@@ -18691,21 +18691,21 @@
         <v>673</v>
       </c>
       <c r="B674" s="2" t="n">
-        <v>44911</v>
+        <v>44546</v>
       </c>
       <c r="C674" s="3" t="inlineStr">
         <is>
-          <t>Chandrashekhar Dasgupta</t>
+          <t>Inqiad Bin Ali</t>
         </is>
       </c>
       <c r="D674" s="3" t="inlineStr">
         <is>
-          <t>Global diplomacy and the birth of Bangladesh</t>
+          <t>Behind enemy lines: Story of a Bengali family stuck in Pakistan during 1971</t>
         </is>
       </c>
       <c r="E674" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/supplements/victory-day-special-2022/news/global-diplomacy-and-the-birth-bangladesh-3197051</t>
+          <t>https://www.thedailystar.net/shout/news/behind-enemy-lines-2917606</t>
         </is>
       </c>
     </row>
@@ -18714,21 +18714,21 @@
         <v>674</v>
       </c>
       <c r="B675" s="2" t="n">
-        <v>44911</v>
+        <v>44546</v>
       </c>
       <c r="C675" s="3" t="inlineStr">
         <is>
-          <t>Priyam Pritim Paul</t>
+          <t>Syed Jamil Ahmed, PhD</t>
         </is>
       </c>
       <c r="D675" s="3" t="inlineStr">
         <is>
-          <t>Mahboobul Alam: An early historian of the 1971 war</t>
+          <t>How nationalist imaginaries were reconstituted in 1971</t>
         </is>
       </c>
       <c r="E675" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/supplements/victory-day-special-2022/news/mahboobul-alam-early-historian-the-1971-war-3197266</t>
+          <t>https://www.thedailystar.net/supplements/victory-day-special-2021/news/how-nationalist-imaginaries-were-reconstituted-1971-2918021</t>
         </is>
       </c>
     </row>
@@ -18737,21 +18737,21 @@
         <v>675</v>
       </c>
       <c r="B676" s="2" t="n">
-        <v>44911</v>
+        <v>44546</v>
       </c>
       <c r="C676" s="3" t="inlineStr">
         <is>
-          <t>Mahbub Uddin Ahmed Bir Bikram</t>
+          <t>Mohiuddin Alamgir</t>
         </is>
       </c>
       <c r="D676" s="3" t="inlineStr">
         <is>
-          <t>Mukti Bahini: The Real Heroes of Liberation War</t>
+          <t>Liberated, at last</t>
         </is>
       </c>
       <c r="E676" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/supplements/victory-day-special-2022/news/mukti-bahini-the-real-heroes-liberation-war-3197061</t>
+          <t>https://www.thedailystar.net/supplements/victory-day-special-2021/news/liberated-last-2918636</t>
         </is>
       </c>
     </row>
@@ -18760,21 +18760,21 @@
         <v>676</v>
       </c>
       <c r="B677" s="2" t="n">
-        <v>44989</v>
+        <v>44546</v>
       </c>
       <c r="C677" s="3" t="inlineStr">
         <is>
-          <t>Ahmad Istiak</t>
+          <t>Maisha Islam Monamee</t>
         </is>
       </c>
       <c r="D677" s="3" t="inlineStr">
         <is>
-          <t>Those turbulent first days of ‘71 March</t>
+          <t>Nonfiction books on the Liberation War released this year</t>
         </is>
       </c>
       <c r="E677" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/weekend-read/news/those-turbulent-first-days-71-march-3262536</t>
+          <t>https://www.thedailystar.net/daily-star-books/news/nonfiction-books-the-liberation-war-released-year-2918841</t>
         </is>
       </c>
     </row>
@@ -18783,21 +18783,21 @@
         <v>677</v>
       </c>
       <c r="B678" s="2" t="n">
-        <v>45007</v>
+        <v>44546</v>
       </c>
       <c r="C678" s="3" t="inlineStr">
         <is>
-          <t>Arun Bikash Dey</t>
+          <t>Dwoha Chowdhury and Mintu Deshwara</t>
         </is>
       </c>
       <c r="D678" s="3" t="inlineStr">
         <is>
-          <t>Chittagong College’s pivotal role in 1971</t>
+          <t>Red stains in green gardens</t>
         </is>
       </c>
       <c r="E678" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/chattogram/news/chittagong-colleges-pivotal-role-1971-3277501</t>
+          <t>https://www.thedailystar.net/supplements/victory-day-special-2021/news/red-stains-green-gardens-2918616</t>
         </is>
       </c>
     </row>
@@ -18806,21 +18806,21 @@
         <v>678</v>
       </c>
       <c r="B679" s="2" t="n">
-        <v>45008</v>
+        <v>44546</v>
       </c>
       <c r="C679" s="3" t="inlineStr">
         <is>
-          <t>Shamsuddoza Sajen</t>
+          <t>Dr. Rudabeh Shahid</t>
         </is>
       </c>
       <c r="D679" s="3" t="inlineStr">
         <is>
-          <t>Reading as a form of resistance: Some anecdotes from the 1971 war</t>
+          <t>Retracing the 1971 exodus</t>
         </is>
       </c>
       <c r="E679" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/daily-star-books/news/reading-form-resistance-some-anecdotes-the-1971-war-3278586</t>
+          <t>https://www.thedailystar.net/supplements/victory-day-special-2021/news/retracing-the-1971-exodus-2918041</t>
         </is>
       </c>
     </row>
@@ -18829,21 +18829,21 @@
         <v>679</v>
       </c>
       <c r="B680" s="2" t="n">
-        <v>45010</v>
+        <v>44546</v>
       </c>
       <c r="C680" s="3" t="inlineStr">
         <is>
-          <t>Shamsuddoza Sajen</t>
+          <t>Mahbub Uddin Ahmed Bir Bikram</t>
         </is>
       </c>
       <c r="D680" s="3" t="inlineStr">
         <is>
-          <t>The genocide of March 25 as a metaphor</t>
+          <t>Tales of courage and patriotism</t>
         </is>
       </c>
       <c r="E680" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/opinion/views/news/the-genocide-march-25-metaphor-3279591</t>
+          <t>https://www.thedailystar.net/supplements/victory-day-special-2021/news/tales-courage-and-patriotism-2917981</t>
         </is>
       </c>
     </row>
@@ -18852,21 +18852,21 @@
         <v>680</v>
       </c>
       <c r="B681" s="2" t="n">
-        <v>45022</v>
+        <v>44546</v>
       </c>
       <c r="C681" s="3" t="inlineStr">
         <is>
-          <t>Emran Mahfuz</t>
+          <t>Jayant Prasad</t>
         </is>
       </c>
       <c r="D681" s="3" t="inlineStr">
         <is>
-          <t>War in the waters: Looking back at Operation Jackpot, 1971</t>
+          <t>The 1971 saga</t>
         </is>
       </c>
       <c r="E681" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/books-literature/news/war-the-waters-looking-back-operation-jackpot-1971-3290041</t>
+          <t>https://www.thedailystar.net/supplements/victory-day-special-2021/news/the-1971-saga-2917976</t>
         </is>
       </c>
     </row>
@@ -18875,21 +18875,21 @@
         <v>681</v>
       </c>
       <c r="B682" s="2" t="n">
-        <v>45033</v>
+        <v>44546</v>
       </c>
       <c r="C682" s="3" t="inlineStr">
         <is>
-          <t>Mahbub Uddin Ahmed Bir Bikram</t>
+          <t>Priyam Pritim Paul</t>
         </is>
       </c>
       <c r="D682" s="3" t="inlineStr">
         <is>
-          <t>Honouring Mujibnagar heroes</t>
+          <t>The Chattogram Resistance</t>
         </is>
       </c>
       <c r="E682" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/opinion/focus/news/honouring-mujibnagar-heroes-3298761</t>
+          <t>https://www.thedailystar.net/supplements/victory-day-special-2021/news/the-chattogram-resistance-2918051</t>
         </is>
       </c>
     </row>
@@ -18898,21 +18898,21 @@
         <v>682</v>
       </c>
       <c r="B683" s="2" t="n">
-        <v>45044</v>
+        <v>44546</v>
       </c>
       <c r="C683" s="3" t="inlineStr">
         <is>
-          <t>The Daily Star</t>
+          <t>Azibor Rahman</t>
         </is>
       </c>
       <c r="D683" s="3" t="inlineStr">
         <is>
-          <t>The Proclamation of Independence 1971</t>
+          <t>They went to sleep never to wake up</t>
         </is>
       </c>
       <c r="E683" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/law-our-rights/news/the-proclamation-independence-1971-3306236</t>
+          <t>https://www.thedailystar.net/supplements/victory-day-special-2021/news/they-went-sleep-never-wake-2918631</t>
         </is>
       </c>
     </row>
@@ -18921,21 +18921,21 @@
         <v>683</v>
       </c>
       <c r="B684" s="2" t="n">
-        <v>45061</v>
+        <v>44546</v>
       </c>
       <c r="C684" s="3" t="inlineStr">
         <is>
-          <t>Sara Rashid</t>
+          <t>Ahmed Humayun Kabir Topu</t>
         </is>
       </c>
       <c r="D684" s="3" t="inlineStr">
         <is>
-          <t>Motherhood, martyrdom and the spirit of female resistance in 1971</t>
+          <t>When living is even more painful</t>
         </is>
       </c>
       <c r="E684" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/daily-star-books/news/motherhood-martyrdom-and-the-spirit-female-resistance-1971-3320831</t>
+          <t>https://www.thedailystar.net/supplements/victory-day-special-2021/news/when-living-even-more-painful-2918621</t>
         </is>
       </c>
     </row>
@@ -18944,21 +18944,21 @@
         <v>684</v>
       </c>
       <c r="B685" s="2" t="n">
-        <v>45261</v>
+        <v>44547</v>
       </c>
       <c r="C685" s="3" t="inlineStr">
         <is>
-          <t>Azmin Azran</t>
+          <t>Mahfuz Anam</t>
         </is>
       </c>
       <c r="D685" s="3" t="inlineStr">
         <is>
-          <t>Henry Kissinger’s influence on Bangladesh’s history</t>
+          <t>Column by Mahfuz Anam: Golden Jubilee Celebration - Media’s role and the diplomatic challenges in 1971</t>
         </is>
       </c>
       <c r="E685" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/opinion/views/news/henry-kissingers-influence-bangladeshs-history-3483221</t>
+          <t>https://www.thedailystar.net/opinion/the-third-view/news/column-mahfuz-anam-golden-jubilee-celebration-medias-role-and-the-diplomatic-challenges-1971-2919256</t>
         </is>
       </c>
     </row>
@@ -18967,21 +18967,21 @@
         <v>685</v>
       </c>
       <c r="B686" s="2" t="n">
-        <v>45274</v>
+        <v>44551</v>
       </c>
       <c r="C686" s="3" t="inlineStr">
         <is>
-          <t>Ahmad Istiak</t>
+          <t>Adnan Zillur Morshed</t>
         </is>
       </c>
       <c r="D686" s="3" t="inlineStr">
         <is>
-          <t>Martyred Intellectuals Day: In search of the forgotten killing fields</t>
+          <t>Understanding a freedom fighter’s prison letters</t>
         </is>
       </c>
       <c r="E686" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/news/bangladesh/news/martyred-intellectuals-day-search-the-forgotten-killing-fields-3493941</t>
+          <t>https://www.thedailystar.net/opinion/the-grudging-urbanist/news/understanding-freedom-fighters-prison-letters-2921966</t>
         </is>
       </c>
     </row>
@@ -18990,21 +18990,21 @@
         <v>686</v>
       </c>
       <c r="B687" s="2" t="n">
-        <v>45275</v>
+        <v>44554</v>
       </c>
       <c r="C687" s="3" t="inlineStr">
         <is>
-          <t>Shah Alam Shazu</t>
+          <t>Pallab Bhattacharya</t>
         </is>
       </c>
       <c r="D687" s="3" t="inlineStr">
         <is>
-          <t>Actor Sohel Rana recalls heroic days of Liberation War</t>
+          <t>The political rumblings in India over 1971</t>
         </is>
       </c>
       <c r="E687" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/entertainment/tv-film/news/actor-sohel-rana-recalls-heroic-days-liberation-war-3495281</t>
+          <t>https://www.thedailystar.net/views/opinion/news/the-political-rumblings-india-over-1971-2924301</t>
         </is>
       </c>
     </row>
@@ -19013,21 +19013,21 @@
         <v>687</v>
       </c>
       <c r="B688" s="2" t="n">
-        <v>45276</v>
+        <v>44621</v>
       </c>
       <c r="C688" s="3" t="inlineStr">
         <is>
-          <t>Marina Yasmin</t>
+          <t>Mirza Shakil</t>
         </is>
       </c>
       <c r="D688" s="3" t="inlineStr">
         <is>
-          <t>A Testimony of Pakistan’s Cruelty, Genocide and Failure in Bangladesh</t>
+          <t>Tangail water tank: Mute witness to 1971 massacre</t>
         </is>
       </c>
       <c r="E688" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/supplements/victory-day-special-2023/news/testimony-pakistans-cruelty-genocide-and-failure-bangladesh-3495491</t>
+          <t>https://www.thedailystar.net/news/bangladesh/news/tangail-water-tank-mute-witness-1971-massacre-2972621</t>
         </is>
       </c>
     </row>
@@ -19036,21 +19036,21 @@
         <v>688</v>
       </c>
       <c r="B689" s="2" t="n">
-        <v>45276</v>
+        <v>44646</v>
       </c>
       <c r="C689" s="3" t="inlineStr">
         <is>
-          <t>Ahmad Istiak</t>
+          <t>Mannan Mashhur Zarif</t>
         </is>
       </c>
       <c r="D689" s="3" t="inlineStr">
         <is>
-          <t>Battles that quickened victory</t>
+          <t>London 1971 — A political frontier of the Liberation War</t>
         </is>
       </c>
       <c r="E689" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/news/bangladesh/news/battles-quickened-victory-3495381</t>
+          <t>https://www.thedailystar.net/life-living/news/london-1971-political-frontier-the-liberation-war-2990981</t>
         </is>
       </c>
     </row>
@@ -19059,21 +19059,21 @@
         <v>689</v>
       </c>
       <c r="B690" s="2" t="n">
-        <v>45276</v>
+        <v>44646</v>
       </c>
       <c r="C690" s="3" t="inlineStr">
         <is>
-          <t>Ansar Ahmed Ullah</t>
+          <t>Priyam Pritim Paul</t>
         </is>
       </c>
       <c r="D690" s="3" t="inlineStr">
         <is>
-          <t>Connetts risked their lives for Bangladesh in ,71</t>
+          <t>Revisiting 1971 sagas through the lens of a silent witness</t>
         </is>
       </c>
       <c r="E690" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/supplements/victory-day-special-2023/news/connetts-risked-their-lives-bangladesh-71-3495556</t>
+          <t>https://www.thedailystar.net/supplements/celebrating-51-years-independence/news/revisiting-1971-sagas-through-the-lens-silent-witness-2990456</t>
         </is>
       </c>
     </row>
@@ -19082,21 +19082,21 @@
         <v>690</v>
       </c>
       <c r="B691" s="2" t="n">
-        <v>45276</v>
+        <v>44646</v>
       </c>
       <c r="C691" s="3" t="inlineStr">
         <is>
-          <t>The Daily Star</t>
+          <t>Shishir Bhattacharja</t>
         </is>
       </c>
       <c r="D691" s="3" t="inlineStr">
         <is>
-          <t>Echoes from the Archives</t>
+          <t>Shoronarthir Dinolipi: The diary of a 1971 refugee</t>
         </is>
       </c>
       <c r="E691" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/supplements/victory-day-special-2023/news/echoes-the-archives-3495576</t>
+          <t>https://www.thedailystar.net/supplements/celebrating-51-years-independence/news/shoronarthir-dinolipi-the-diary-1971-refugee-2990481</t>
         </is>
       </c>
     </row>
@@ -19105,21 +19105,21 @@
         <v>691</v>
       </c>
       <c r="B692" s="2" t="n">
-        <v>45276</v>
+        <v>44646</v>
       </c>
       <c r="C692" s="3" t="inlineStr">
         <is>
-          <t>Mofidul Hoque</t>
+          <t>Muyeedul Hasan</t>
         </is>
       </c>
       <c r="D692" s="3" t="inlineStr">
         <is>
-          <t>The Finale of the Bangladesh Battle</t>
+          <t>‘1971 Bangladesh – With Unbound Accounts’</t>
         </is>
       </c>
       <c r="E692" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/supplements/victory-day-special-2023/news/the-finale-the-bangladesh-battle-3495586</t>
+          <t>https://www.thedailystar.net/supplements/celebrating-51-years-independence/news/1971-bangladesh-unbound-accounts-2990451</t>
         </is>
       </c>
     </row>
@@ -19128,21 +19128,21 @@
         <v>692</v>
       </c>
       <c r="B693" s="2" t="n">
-        <v>45276</v>
+        <v>44654</v>
       </c>
       <c r="C693" s="3" t="inlineStr">
         <is>
-          <t>Priyam Pritim Paul</t>
+          <t>BSS, Dhaka</t>
         </is>
       </c>
       <c r="D693" s="3" t="inlineStr">
         <is>
-          <t>The Heroic Role of the BMA, UK in 1971</t>
+          <t>Kissinger who called Bangladesh 'basket case' says US role in 1971 was a 'misjudgment'</t>
         </is>
       </c>
       <c r="E693" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/supplements/victory-day-special-2023/news/the-heroic-role-the-bma-uk-1971-3495501</t>
+          <t>https://www.thedailystar.net/news/bangladesh/news/kissinger-who-called-bangladesh-basket-case-says-us-role-1971-was-misjudgment-2997121</t>
         </is>
       </c>
     </row>
@@ -19151,21 +19151,21 @@
         <v>693</v>
       </c>
       <c r="B694" s="2" t="n">
-        <v>45276</v>
+        <v>44668</v>
       </c>
       <c r="C694" s="3" t="inlineStr">
         <is>
-          <t>Niaz Zaman</t>
+          <t>Mohiuddin Alamgir</t>
         </is>
       </c>
       <c r="D694" s="3" t="inlineStr">
         <is>
-          <t>The Journey Home</t>
+          <t>Historic Mujibnagar Day: No ordinary guard of honour</t>
         </is>
       </c>
       <c r="E694" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/supplements/victory-day-special-2023/news/the-journey-home-3495571</t>
+          <t>https://www.thedailystar.net/news/bangladesh/news/historic-mujibnagar-day-no-ordinary-guard-honour-3005891</t>
         </is>
       </c>
     </row>
@@ -19174,21 +19174,21 @@
         <v>694</v>
       </c>
       <c r="B695" s="2" t="n">
-        <v>45276</v>
+        <v>44668</v>
       </c>
       <c r="C695" s="3" t="inlineStr">
         <is>
-          <t>Priyam Paul</t>
+          <t>Shams Rahman</t>
         </is>
       </c>
       <c r="D695" s="3" t="inlineStr">
         <is>
-          <t>“Due to a lack of firsthand experiences of the writers, there is a notable absence of works solely dedicated to our Liberation War”</t>
+          <t>Mujibnagar Day: How the Mujibnagar government turned the dream for freedom into reality</t>
         </is>
       </c>
       <c r="E695" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/supplements/victory-day-special-2023/news/due-lack-firsthand-experiences-the-writers-there-notable-absence-works-solely-dedicated-our-3495561</t>
+          <t>https://www.thedailystar.net/views/opinion/news/mujibnagar-day-how-the-mujibnagar-government-turned-the-dream-freedom-reality-3005976</t>
         </is>
       </c>
     </row>
@@ -19197,21 +19197,21 @@
         <v>695</v>
       </c>
       <c r="B696" s="2" t="n">
-        <v>45277</v>
+        <v>44668</v>
       </c>
       <c r="C696" s="3" t="inlineStr">
         <is>
-          <t>Ahmad Istiak</t>
+          <t>Mahbub Uddin Ahmed Bir Bikram</t>
         </is>
       </c>
       <c r="D696" s="3" t="inlineStr">
         <is>
-          <t>Series genocide in 1971: Three times a survivor</t>
+          <t>Remembering the oath-taking of Mujibnagar government</t>
         </is>
       </c>
       <c r="E696" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/news/bangladesh/news/series-genocide-1971-three-times-survivor-3496086</t>
+          <t>https://www.thedailystar.net/opinion/online-exclusive/news/remembering-the-oath-taking-mujibnagar-government-3006526</t>
         </is>
       </c>
     </row>
@@ -19220,21 +19220,21 @@
         <v>696</v>
       </c>
       <c r="B697" s="2" t="n">
-        <v>45278</v>
+        <v>44735</v>
       </c>
       <c r="C697" s="3" t="inlineStr">
         <is>
-          <t>K S Nair</t>
+          <t>Namrata</t>
         </is>
       </c>
       <c r="D697" s="3" t="inlineStr">
         <is>
-          <t>Remembering 1971</t>
+          <t>Manash Ghosh's ' Bangladesh War': Dispatches of independence</t>
         </is>
       </c>
       <c r="E697" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/opinion/focus/news/remembering-1971-3497021</t>
+          <t>https://www.thedailystar.net/daily-star-books/news/dispatches-independence-3054366</t>
         </is>
       </c>
     </row>
@@ -19243,21 +19243,21 @@
         <v>697</v>
       </c>
       <c r="B698" s="2" t="n">
-        <v>45330</v>
+        <v>44765</v>
       </c>
       <c r="C698" s="3" t="inlineStr">
         <is>
-          <t>Fakrul Alam</t>
+          <t>Arunav Das</t>
         </is>
       </c>
       <c r="D698" s="3" t="inlineStr">
         <is>
-          <t>Rehman Sobhan’s recollections of the road he took towards December 16, 1971</t>
+          <t>"Garos of 71": A documentary in search of history</t>
         </is>
       </c>
       <c r="E698" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/daily-star-books/news/rehman-sobhans-recollections-the-road-he-took-towards-december-16-1971-3539121</t>
+          <t>https://www.thedailystar.net/star-literature/news/garos-71-documentary-search-history-3077121</t>
         </is>
       </c>
     </row>
@@ -19266,21 +19266,21 @@
         <v>698</v>
       </c>
       <c r="B699" s="2" t="n">
-        <v>45358</v>
+        <v>44854</v>
       </c>
       <c r="C699" s="3" t="inlineStr">
         <is>
-          <t>Mahfuz Anam</t>
+          <t>Kazi Zawad</t>
         </is>
       </c>
       <c r="D699" s="3" t="inlineStr">
         <is>
-          <t>The speech and those transformative days of March ‘71</t>
+          <t>Contradictions in a book on the Bangladesh Liberation War</t>
         </is>
       </c>
       <c r="E699" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/opinion/views/the-third-view/news/the-speech-and-those-transformative-days-march-71-3560896</t>
+          <t>https://www.thedailystar.net/daily-star-books/news/contradictions-book-the-bangladesh-liberation-war-3147461</t>
         </is>
       </c>
     </row>
@@ -19289,21 +19289,21 @@
         <v>699</v>
       </c>
       <c r="B700" s="2" t="n">
-        <v>45377</v>
+        <v>44909</v>
       </c>
       <c r="C700" s="3" t="inlineStr">
         <is>
-          <t>Ramisa Rob</t>
+          <t>Kaberi Gayen</t>
         </is>
       </c>
       <c r="D700" s="3" t="inlineStr">
         <is>
-          <t>'The Liberation War became a centre of big power rivalry'</t>
+          <t>Legacies of Loss</t>
         </is>
       </c>
       <c r="E700" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/opinion/geopolitical-insights/news/the-liberation-war-became-centre-big-power-rivalry-3575196</t>
+          <t>https://www.thedailystar.net/supplements/martyred-intellectuals-day-2022/news/legacies-loss-3195766</t>
         </is>
       </c>
     </row>
@@ -19312,21 +19312,21 @@
         <v>700</v>
       </c>
       <c r="B701" s="2" t="n">
-        <v>45377</v>
+        <v>44909</v>
       </c>
       <c r="C701" s="3" t="inlineStr">
         <is>
-          <t>Priyam Pritim Paul</t>
+          <t>Ahmad Istiak</t>
         </is>
       </c>
       <c r="D701" s="3" t="inlineStr">
         <is>
-          <t>Administrative dynamics in 1971’s War of Liberation</t>
+          <t>Martyred intellectuals day: Murderous scheme</t>
         </is>
       </c>
       <c r="E701" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/supplements/independence-day-special-2024/news/administrative-dynamics-1971s-war-liberation-3575151</t>
+          <t>https://www.thedailystar.net/news/bangladesh/news/martyred-intellectuals-day-murderous-scheme-3195581</t>
         </is>
       </c>
     </row>
@@ -19335,21 +19335,21 @@
         <v>701</v>
       </c>
       <c r="B702" s="2" t="n">
-        <v>45377</v>
+        <v>44909</v>
       </c>
       <c r="C702" s="3" t="inlineStr">
         <is>
-          <t>Priyam Paul and Rachel Stevens</t>
+          <t>Abdul Momin Chowdhury</t>
         </is>
       </c>
       <c r="D702" s="3" t="inlineStr">
         <is>
-          <t>Australia’s Response to the 1971 Refugee Crisis</t>
+          <t>My three martyred teachers</t>
         </is>
       </c>
       <c r="E702" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/supplements/independence-day-special-2024/news/australias-response-the-1971-refugee-crisis-3575126</t>
+          <t>https://www.thedailystar.net/supplements/martyred-intellectuals-day-2022/news/my-three-martyred-teachers-3195776</t>
         </is>
       </c>
     </row>
@@ -19358,21 +19358,21 @@
         <v>702</v>
       </c>
       <c r="B703" s="2" t="n">
-        <v>45377</v>
+        <v>44909</v>
       </c>
       <c r="C703" s="3" t="inlineStr">
         <is>
-          <t>Mohammad Afzalur Rahman</t>
+          <t>Meghna Guhathakurta</t>
         </is>
       </c>
       <c r="D703" s="3" t="inlineStr">
         <is>
-          <t>Echoes of 1971: A journey through memories</t>
+          <t>My ’71: Experiencing Genocide, Understanding Violence</t>
         </is>
       </c>
       <c r="E703" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/supplements/independence-day-special-2024/news/echoes-1971-journey-through-memories-3575181</t>
+          <t>https://www.thedailystar.net/supplements/martyred-intellectuals-day-2022/news/my-71-experiencing-genocide-understanding-violence-3195761</t>
         </is>
       </c>
     </row>
@@ -19381,21 +19381,21 @@
         <v>703</v>
       </c>
       <c r="B704" s="2" t="n">
-        <v>45377</v>
+        <v>44910</v>
       </c>
       <c r="C704" s="3" t="inlineStr">
         <is>
-          <t>Muntassir Mamoon</t>
+          <t>Fabiha Afifa</t>
         </is>
       </c>
       <c r="D704" s="3" t="inlineStr">
         <is>
-          <t>Rao Farman Ali and 1971</t>
+          <t>The price of victory: 1971 and the mental health of a generation</t>
         </is>
       </c>
       <c r="E704" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/supplements/independence-day-special-2024/news/rao-farman-ali-and-1971-3575166</t>
+          <t>https://www.thedailystar.net/shout/cover-story/news/the-price-victory-1971-and-the-mental-health-generation-3196816</t>
         </is>
       </c>
     </row>
@@ -19404,21 +19404,21 @@
         <v>704</v>
       </c>
       <c r="B705" s="2" t="n">
-        <v>45377</v>
+        <v>44911</v>
       </c>
       <c r="C705" s="3" t="inlineStr">
         <is>
-          <t>Amrin Tasnim Rafa</t>
+          <t>Chandrashekhar Dasgupta</t>
         </is>
       </c>
       <c r="D705" s="3" t="inlineStr">
         <is>
-          <t>The significance of Bangladesh's Independence Day and Victory Day</t>
+          <t>Global diplomacy and the birth of Bangladesh</t>
         </is>
       </c>
       <c r="E705" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/rising-stars/news/the-significance-bangladeshs-independence-day-and-victory-day-3575421</t>
+          <t>https://www.thedailystar.net/supplements/victory-day-special-2022/news/global-diplomacy-and-the-birth-bangladesh-3197051</t>
         </is>
       </c>
     </row>
@@ -19427,21 +19427,21 @@
         <v>705</v>
       </c>
       <c r="B706" s="2" t="n">
-        <v>45377</v>
+        <v>44911</v>
       </c>
       <c r="C706" s="3" t="inlineStr">
         <is>
-          <t>Priyam Paul</t>
+          <t>Priyam Pritim Paul</t>
         </is>
       </c>
       <c r="D706" s="3" t="inlineStr">
         <is>
-          <t>The untold story of Jashore’s resistance during the Liberation War</t>
+          <t>Mahboobul Alam: An early historian of the 1971 war</t>
         </is>
       </c>
       <c r="E706" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/supplements/independence-day-special-2024/news/the-untold-story-jashores-resistance-during-the-liberation-war-3575086</t>
+          <t>https://www.thedailystar.net/supplements/victory-day-special-2022/news/mahboobul-alam-early-historian-the-1971-war-3197266</t>
         </is>
       </c>
     </row>
@@ -19450,21 +19450,21 @@
         <v>706</v>
       </c>
       <c r="B707" s="2" t="n">
-        <v>45377</v>
+        <v>44911</v>
       </c>
       <c r="C707" s="3" t="inlineStr">
         <is>
-          <t>Kanak Das Gupta</t>
+          <t>Mahbub Uddin Ahmed Bir Bikram</t>
         </is>
       </c>
       <c r="D707" s="3" t="inlineStr">
         <is>
-          <t>Two Martyred Pandits: Sharada &amp; Annada Charan</t>
+          <t>Mukti Bahini: The Real Heroes of Liberation War</t>
         </is>
       </c>
       <c r="E707" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/supplements/independence-day-special-2024/news/two-martyred-pandits-sharada-annada-charan-3575171</t>
+          <t>https://www.thedailystar.net/supplements/victory-day-special-2022/news/mukti-bahini-the-real-heroes-liberation-war-3197061</t>
         </is>
       </c>
     </row>
@@ -19473,21 +19473,21 @@
         <v>707</v>
       </c>
       <c r="B708" s="2" t="n">
-        <v>45390</v>
+        <v>44989</v>
       </c>
       <c r="C708" s="3" t="inlineStr">
         <is>
-          <t>Khashruzzamn Choudhury</t>
+          <t>Ahmad Istiak</t>
         </is>
       </c>
       <c r="D708" s="3" t="inlineStr">
         <is>
-          <t>A freedom fighter’s journey to Mujibnagar</t>
+          <t>Those turbulent first days of ‘71 March</t>
         </is>
       </c>
       <c r="E708" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/opinion/focus/news/freedom-fighters-journey-mujibnagar-3584516</t>
+          <t>https://www.thedailystar.net/weekend-read/news/those-turbulent-first-days-71-march-3262536</t>
         </is>
       </c>
     </row>
@@ -19496,21 +19496,21 @@
         <v>708</v>
       </c>
       <c r="B709" s="2" t="n">
-        <v>45421</v>
+        <v>45007</v>
       </c>
       <c r="C709" s="3" t="inlineStr">
         <is>
-          <t>Maliha Mashiat</t>
+          <t>Arun Bikash Dey</t>
         </is>
       </c>
       <c r="D709" s="3" t="inlineStr">
         <is>
-          <t>‘Rise of Nation’: Liberation War through the ‘eyes’ of refugees at Raghu Rai’s exhibition</t>
+          <t>Chittagong College’s pivotal role in 1971</t>
         </is>
       </c>
       <c r="E709" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/entertainment/theatre-arts/news/rise-nation-liberation-war-through-the-eyes-refugees-raghu-rais-exhibition-3605911</t>
+          <t>https://www.thedailystar.net/chattogram/news/chittagong-colleges-pivotal-role-1971-3277501</t>
         </is>
       </c>
     </row>
@@ -19519,21 +19519,21 @@
         <v>709</v>
       </c>
       <c r="B710" s="2" t="n">
-        <v>45638</v>
+        <v>45008</v>
       </c>
       <c r="C710" s="3" t="inlineStr">
         <is>
-          <t>Our Correspondent, Mymensingh</t>
+          <t>Shamsuddoza Sajen</t>
         </is>
       </c>
       <c r="D710" s="3" t="inlineStr">
         <is>
-          <t>The forgotten lens of Liberation War</t>
+          <t>Reading as a form of resistance: Some anecdotes from the 1971 war</t>
         </is>
       </c>
       <c r="E710" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/news/bangladesh/news/the-forgotten-lens-liberation-war-3774166</t>
+          <t>https://www.thedailystar.net/daily-star-books/news/reading-form-resistance-some-anecdotes-the-1971-war-3278586</t>
         </is>
       </c>
     </row>
@@ -19542,21 +19542,21 @@
         <v>710</v>
       </c>
       <c r="B711" s="2" t="n">
-        <v>45640</v>
+        <v>45010</v>
       </c>
       <c r="C711" s="3" t="inlineStr">
         <is>
-          <t>Kamrul Hassan Mamun</t>
+          <t>Shamsuddoza Sajen</t>
         </is>
       </c>
       <c r="D711" s="3" t="inlineStr">
         <is>
-          <t>A Loss That Still Haunts Bangladesh</t>
+          <t>The genocide of March 25 as a metaphor</t>
         </is>
       </c>
       <c r="E711" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/martyred-intellectuals-day-2024/news/loss-still-haunts-bangladesh-3775566</t>
+          <t>https://www.thedailystar.net/opinion/views/news/the-genocide-march-25-metaphor-3279591</t>
         </is>
       </c>
     </row>
@@ -19565,21 +19565,21 @@
         <v>711</v>
       </c>
       <c r="B712" s="2" t="n">
-        <v>45640</v>
+        <v>45022</v>
       </c>
       <c r="C712" s="3" t="inlineStr">
         <is>
-          <t>Priyam Paul</t>
+          <t>Emran Mahfuz</t>
         </is>
       </c>
       <c r="D712" s="3" t="inlineStr">
         <is>
-          <t>Martyrs of Freedom</t>
+          <t>War in the waters: Looking back at Operation Jackpot, 1971</t>
         </is>
       </c>
       <c r="E712" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/martyred-intellectuals-day-2024/news/martyrs-freedom-3775576</t>
+          <t>https://www.thedailystar.net/books-literature/news/war-the-waters-looking-back-operation-jackpot-1971-3290041</t>
         </is>
       </c>
     </row>
@@ -19588,21 +19588,21 @@
         <v>712</v>
       </c>
       <c r="B713" s="2" t="n">
-        <v>45641</v>
+        <v>45033</v>
       </c>
       <c r="C713" s="3" t="inlineStr">
         <is>
-          <t>Ahmad Istiak</t>
+          <t>Mahbub Uddin Ahmed Bir Bikram</t>
         </is>
       </c>
       <c r="D713" s="3" t="inlineStr">
         <is>
-          <t>Regional Resistance: Purbo Banglar Jatiya Mukti Bahini</t>
+          <t>Honouring Mujibnagar heroes</t>
         </is>
       </c>
       <c r="E713" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/news/bangladesh/news/regional-resistance-purbo-banglar-jatiya-mukti-bahini-3776411</t>
+          <t>https://www.thedailystar.net/opinion/focus/news/honouring-mujibnagar-heroes-3298761</t>
         </is>
       </c>
     </row>
@@ -19611,21 +19611,21 @@
         <v>713</v>
       </c>
       <c r="B714" s="2" t="n">
-        <v>45642</v>
+        <v>45044</v>
       </c>
       <c r="C714" s="3" t="inlineStr">
         <is>
-          <t>RBR</t>
+          <t>The Daily Star</t>
         </is>
       </c>
       <c r="D714" s="3" t="inlineStr">
         <is>
-          <t>1971 War Through a Child’s Eyes: Innocence Meets Reality</t>
+          <t>The Proclamation of Independence 1971</t>
         </is>
       </c>
       <c r="E714" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/my-dhaka/news/1971-war-through-childs-eyes-innocence-meets-reality-3777481</t>
+          <t>https://www.thedailystar.net/law-our-rights/news/the-proclamation-independence-1971-3306236</t>
         </is>
       </c>
     </row>
@@ -19634,21 +19634,21 @@
         <v>714</v>
       </c>
       <c r="B715" s="2" t="n">
-        <v>45644</v>
+        <v>45061</v>
       </c>
       <c r="C715" s="3" t="inlineStr">
         <is>
-          <t>Mirza Shakil</t>
+          <t>Sara Rashid</t>
         </is>
       </c>
       <c r="D715" s="3" t="inlineStr">
         <is>
-          <t>The wonder of guerilla warfare in 1971</t>
+          <t>Motherhood, martyrdom and the spirit of female resistance in 1971</t>
         </is>
       </c>
       <c r="E715" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/news/bangladesh/news/the-wonder-guerilla-warfare-1971-3778801</t>
+          <t>https://www.thedailystar.net/daily-star-books/news/motherhood-martyrdom-and-the-spirit-female-resistance-1971-3320831</t>
         </is>
       </c>
     </row>
@@ -19657,21 +19657,21 @@
         <v>715</v>
       </c>
       <c r="B716" s="2" t="n">
-        <v>45723</v>
+        <v>45261</v>
       </c>
       <c r="C716" s="3" t="inlineStr">
         <is>
-          <t>Mohiuddin Alamgir</t>
+          <t>Azmin Azran</t>
         </is>
       </c>
       <c r="D716" s="3" t="inlineStr">
         <is>
-          <t>‘A speech more notable for what wasn’t said’</t>
+          <t>Henry Kissinger’s influence on Bangladesh’s history</t>
         </is>
       </c>
       <c r="E716" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/news/bangladesh/news/speech-more-notable-what-wasnt-said-3841511</t>
+          <t>https://www.thedailystar.net/opinion/views/news/henry-kissingers-influence-bangladeshs-history-3483221</t>
         </is>
       </c>
     </row>
@@ -19680,21 +19680,21 @@
         <v>716</v>
       </c>
       <c r="B717" s="2" t="n">
-        <v>45741</v>
+        <v>45274</v>
       </c>
       <c r="C717" s="3" t="inlineStr">
         <is>
-          <t>Kollol Kibria</t>
+          <t>Ahmad Istiak</t>
         </is>
       </c>
       <c r="D717" s="3" t="inlineStr">
         <is>
-          <t>Henry Kissinger’s role in 1971</t>
+          <t>Martyred Intellectuals Day: In search of the forgotten killing fields</t>
         </is>
       </c>
       <c r="E717" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/opinion/views/news/henry-kissingers-role-1971-3857056</t>
+          <t>https://www.thedailystar.net/news/bangladesh/news/martyred-intellectuals-day-search-the-forgotten-killing-fields-3493941</t>
         </is>
       </c>
     </row>
@@ -19703,21 +19703,21 @@
         <v>717</v>
       </c>
       <c r="B718" s="2" t="n">
-        <v>45741</v>
+        <v>45275</v>
       </c>
       <c r="C718" s="3" t="inlineStr">
         <is>
-          <t>The Daily Star</t>
+          <t>Shah Alam Shazu</t>
         </is>
       </c>
       <c r="D718" s="3" t="inlineStr">
         <is>
-          <t>March 25 through the eyes of ordinary people</t>
+          <t>Actor Sohel Rana recalls heroic days of Liberation War</t>
         </is>
       </c>
       <c r="E718" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/opinion/views/news/march-25-through-the-eyes-ordinary-people-3856476</t>
+          <t>https://www.thedailystar.net/entertainment/tv-film/news/actor-sohel-rana-recalls-heroic-days-liberation-war-3495281</t>
         </is>
       </c>
     </row>
@@ -19726,21 +19726,21 @@
         <v>718</v>
       </c>
       <c r="B719" s="2" t="n">
-        <v>45741</v>
+        <v>45276</v>
       </c>
       <c r="C719" s="3" t="inlineStr">
         <is>
-          <t>Ahmad Istiak</t>
+          <t>Marina Yasmin</t>
         </is>
       </c>
       <c r="D719" s="3" t="inlineStr">
         <is>
-          <t>Operation searchlight: The massacre at Ctg cantonment</t>
+          <t>A Testimony of Pakistan’s Cruelty, Genocide and Failure in Bangladesh</t>
         </is>
       </c>
       <c r="E719" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/news/bangladesh/news/operation-searchlight-the-massacre-ctg-cantonment-3856676</t>
+          <t>https://www.thedailystar.net/supplements/victory-day-special-2023/news/testimony-pakistans-cruelty-genocide-and-failure-bangladesh-3495491</t>
         </is>
       </c>
     </row>
@@ -19749,21 +19749,21 @@
         <v>719</v>
       </c>
       <c r="B720" s="2" t="n">
-        <v>45742</v>
+        <v>45276</v>
       </c>
       <c r="C720" s="3" t="inlineStr">
         <is>
-          <t>Shahidul Islam and Priyam Paul</t>
+          <t>Ahmad Istiak</t>
         </is>
       </c>
       <c r="D720" s="3" t="inlineStr">
         <is>
-          <t>Between bullets and borders Fleeing the Rajshahi massacre</t>
+          <t>Battles that quickened victory</t>
         </is>
       </c>
       <c r="E720" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/supplements/independence-day-special-2025/news/between-bullets-and-borders-fleeing-the-rajshahi-massacre-3857846</t>
+          <t>https://www.thedailystar.net/news/bangladesh/news/battles-quickened-victory-3495381</t>
         </is>
       </c>
     </row>
@@ -19772,21 +19772,21 @@
         <v>720</v>
       </c>
       <c r="B721" s="2" t="n">
-        <v>45742</v>
+        <v>45276</v>
       </c>
       <c r="C721" s="3" t="inlineStr">
         <is>
-          <t>Miftahul Jannat</t>
+          <t>Ansar Ahmed Ullah</t>
         </is>
       </c>
       <c r="D721" s="3" t="inlineStr">
         <is>
-          <t>Global Chords of Freedom</t>
+          <t>Connetts risked their lives for Bangladesh in ,71</t>
         </is>
       </c>
       <c r="E721" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/supplements/independence-day-special-2025/news/global-chords-freedom-3857811</t>
+          <t>https://www.thedailystar.net/supplements/victory-day-special-2023/news/connetts-risked-their-lives-bangladesh-71-3495556</t>
         </is>
       </c>
     </row>
@@ -19795,21 +19795,21 @@
         <v>721</v>
       </c>
       <c r="B722" s="2" t="n">
-        <v>45742</v>
+        <v>45276</v>
       </c>
       <c r="C722" s="3" t="inlineStr">
         <is>
-          <t>Ahmad Istiak</t>
+          <t>The Daily Star</t>
         </is>
       </c>
       <c r="D722" s="3" t="inlineStr">
         <is>
-          <t>The legend of Nader gunda</t>
+          <t>Echoes from the Archives</t>
         </is>
       </c>
       <c r="E722" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/news/bangladesh/news/the-legend-nader-gunda-3857581</t>
+          <t>https://www.thedailystar.net/supplements/victory-day-special-2023/news/echoes-the-archives-3495576</t>
         </is>
       </c>
     </row>
@@ -19818,21 +19818,21 @@
         <v>722</v>
       </c>
       <c r="B723" s="2" t="n">
-        <v>45742</v>
+        <v>45276</v>
       </c>
       <c r="C723" s="3" t="inlineStr">
         <is>
-          <t>Rahat Minhaz</t>
+          <t>Mofidul Hoque</t>
         </is>
       </c>
       <c r="D723" s="3" t="inlineStr">
         <is>
-          <t>The People in 1971</t>
+          <t>The Finale of the Bangladesh Battle</t>
         </is>
       </c>
       <c r="E723" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/supplements/independence-day-special-2025/news/the-people-1971-3857821</t>
+          <t>https://www.thedailystar.net/supplements/victory-day-special-2023/news/the-finale-the-bangladesh-battle-3495586</t>
         </is>
       </c>
     </row>
@@ -19841,21 +19841,21 @@
         <v>723</v>
       </c>
       <c r="B724" s="2" t="n">
-        <v>45742</v>
+        <v>45276</v>
       </c>
       <c r="C724" s="3" t="inlineStr">
         <is>
-          <t>Anu Muhammad</t>
+          <t>Priyam Pritim Paul</t>
         </is>
       </c>
       <c r="D724" s="3" t="inlineStr">
         <is>
-          <t>The road to liberation: March 1971 and the years that led to it</t>
+          <t>The Heroic Role of the BMA, UK in 1971</t>
         </is>
       </c>
       <c r="E724" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/opinion/views/news/the-road-liberation-march-1971-and-the-years-led-it-3857441</t>
+          <t>https://www.thedailystar.net/supplements/victory-day-special-2023/news/the-heroic-role-the-bma-uk-1971-3495501</t>
         </is>
       </c>
     </row>
@@ -19864,21 +19864,21 @@
         <v>724</v>
       </c>
       <c r="B725" s="2" t="n">
-        <v>45742</v>
+        <v>45276</v>
       </c>
       <c r="C725" s="3" t="inlineStr">
         <is>
-          <t>Priyam Paul</t>
+          <t>Niaz Zaman</t>
         </is>
       </c>
       <c r="D725" s="3" t="inlineStr">
         <is>
-          <t>‘The truths written in blood cannot be erased by lies’</t>
+          <t>The Journey Home</t>
         </is>
       </c>
       <c r="E725" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/supplements/independence-day-special-2025/news/the-truths-written-blood-cannot-be-erased-lies-3857806</t>
+          <t>https://www.thedailystar.net/supplements/victory-day-special-2023/news/the-journey-home-3495571</t>
         </is>
       </c>
     </row>
@@ -19887,7 +19887,7 @@
         <v>725</v>
       </c>
       <c r="B726" s="2" t="n">
-        <v>45764</v>
+        <v>45276</v>
       </c>
       <c r="C726" s="3" t="inlineStr">
         <is>
@@ -19896,12 +19896,12 @@
       </c>
       <c r="D726" s="3" t="inlineStr">
         <is>
-          <t>The Proclamation of Independence was a beacon for Bangladesh</t>
+          <t>“Due to a lack of firsthand experiences of the writers, there is a notable absence of works solely dedicated to our Liberation War”</t>
         </is>
       </c>
       <c r="E726" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/opinion/views/news/the-proclamation-independence-was-beacon-bangladesh-3872661</t>
+          <t>https://www.thedailystar.net/supplements/victory-day-special-2023/news/due-lack-firsthand-experiences-the-writers-there-notable-absence-works-solely-dedicated-our-3495561</t>
         </is>
       </c>
     </row>
@@ -19910,21 +19910,21 @@
         <v>726</v>
       </c>
       <c r="B727" s="2" t="n">
-        <v>45764</v>
+        <v>45277</v>
       </c>
       <c r="C727" s="3" t="inlineStr">
         <is>
-          <t>Mohiuddin Alamgir</t>
+          <t>Ahmad Istiak</t>
         </is>
       </c>
       <c r="D727" s="3" t="inlineStr">
         <is>
-          <t>The spirit of Mujibnagar government can still guide us</t>
+          <t>Series genocide in 1971: Three times a survivor</t>
         </is>
       </c>
       <c r="E727" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/news/bangladesh/news/the-spirit-mujibnagar-government-can-still-guide-us-3873231</t>
+          <t>https://www.thedailystar.net/news/bangladesh/news/series-genocide-1971-three-times-survivor-3496086</t>
         </is>
       </c>
     </row>
@@ -19933,21 +19933,21 @@
         <v>727</v>
       </c>
       <c r="B728" s="2" t="n">
-        <v>45997</v>
+        <v>45278</v>
       </c>
       <c r="C728" s="3" t="inlineStr">
         <is>
-          <t>Our Correspondent, Benapole</t>
+          <t>K S Nair</t>
         </is>
       </c>
       <c r="D728" s="3" t="inlineStr">
         <is>
-          <t>Jashore: First district to be freed on December 6, 1971</t>
+          <t>Remembering 1971</t>
         </is>
       </c>
       <c r="E728" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/news/bangladesh/news/jashore-first-district-be-freed-december-6-1971-4052301</t>
+          <t>https://www.thedailystar.net/opinion/focus/news/remembering-1971-3497021</t>
         </is>
       </c>
     </row>
@@ -19956,21 +19956,21 @@
         <v>728</v>
       </c>
       <c r="B729" s="2" t="n">
-        <v>46005</v>
+        <v>45330</v>
       </c>
       <c r="C729" s="3" t="inlineStr">
         <is>
-          <t>Miftahul Jannat</t>
+          <t>Fakrul Alam</t>
         </is>
       </c>
       <c r="D729" s="3" t="inlineStr">
         <is>
-          <t>A compassionate rebel in a doctor’s coat</t>
+          <t>Rehman Sobhan’s recollections of the road he took towards December 16, 1971</t>
         </is>
       </c>
       <c r="E729" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/supplements/martyred-intellectuals-day-2025/news/compassionate-rebel-doctors-coat-4057356</t>
+          <t>https://www.thedailystar.net/daily-star-books/news/rehman-sobhans-recollections-the-road-he-took-towards-december-16-1971-3539121</t>
         </is>
       </c>
     </row>
@@ -19979,21 +19979,21 @@
         <v>729</v>
       </c>
       <c r="B730" s="2" t="n">
-        <v>46005</v>
+        <v>45358</v>
       </c>
       <c r="C730" s="3" t="inlineStr">
         <is>
-          <t>The Daily Star</t>
+          <t>Mahfuz Anam</t>
         </is>
       </c>
       <c r="D730" s="3" t="inlineStr">
         <is>
-          <t>Martyred intellectuals are our guiding lights</t>
+          <t>The speech and those transformative days of March ‘71</t>
         </is>
       </c>
       <c r="E730" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/opinion/editorial/news/martyred-intellectuals-are-our-guiding-lights-4058291</t>
+          <t>https://www.thedailystar.net/opinion/views/the-third-view/news/the-speech-and-those-transformative-days-march-71-3560896</t>
         </is>
       </c>
     </row>
@@ -20002,21 +20002,21 @@
         <v>730</v>
       </c>
       <c r="B731" s="2" t="n">
-        <v>46005</v>
+        <v>45377</v>
       </c>
       <c r="C731" s="3" t="inlineStr">
         <is>
-          <t>Mohammed Ishtiaque Khan</t>
+          <t>Ramisa Rob</t>
         </is>
       </c>
       <c r="D731" s="3" t="inlineStr">
         <is>
-          <t>Martyred intellectuals: The torchbearers of our nation</t>
+          <t>'The Liberation War became a centre of big power rivalry'</t>
         </is>
       </c>
       <c r="E731" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/opinion/views/news/martyred-intellectuals-torchbearers-our-nation-4057646</t>
+          <t>https://www.thedailystar.net/opinion/geopolitical-insights/news/the-liberation-war-became-centre-big-power-rivalry-3575196</t>
         </is>
       </c>
     </row>
@@ -20025,21 +20025,21 @@
         <v>731</v>
       </c>
       <c r="B732" s="2" t="n">
-        <v>46005</v>
+        <v>45377</v>
       </c>
       <c r="C732" s="3" t="inlineStr">
         <is>
-          <t>Ahmad Istiak</t>
+          <t>Priyam Pritim Paul</t>
         </is>
       </c>
       <c r="D732" s="3" t="inlineStr">
         <is>
-          <t>Martyred Intellectuals’ Day: Horrors of Saidpur’s intellectual massacre</t>
+          <t>Administrative dynamics in 1971’s War of Liberation</t>
         </is>
       </c>
       <c r="E732" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/news/bangladesh/news/martyred-intellectuals-day-horrors-saidpurs-intellectual-massacre-4057741</t>
+          <t>https://www.thedailystar.net/supplements/independence-day-special-2024/news/administrative-dynamics-1971s-war-liberation-3575151</t>
         </is>
       </c>
     </row>
@@ -20048,21 +20048,21 @@
         <v>732</v>
       </c>
       <c r="B733" s="2" t="n">
-        <v>46005</v>
+        <v>45377</v>
       </c>
       <c r="C733" s="3" t="inlineStr">
         <is>
-          <t>Asif Bin Ali</t>
+          <t>Priyam Paul and Rachel Stevens</t>
         </is>
       </c>
       <c r="D733" s="3" t="inlineStr">
         <is>
-          <t>What does it mean to honour the legacy of Bangladesh’s martyred intellectuals?</t>
+          <t>Australia’s Response to the 1971 Refugee Crisis</t>
         </is>
       </c>
       <c r="E733" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/opinion/views/news/what-does-it-mean-honour-legacy-bangladeshs-martyred-intellectuals-4057641</t>
+          <t>https://www.thedailystar.net/supplements/independence-day-special-2024/news/australias-response-the-1971-refugee-crisis-3575126</t>
         </is>
       </c>
     </row>
@@ -20071,21 +20071,21 @@
         <v>733</v>
       </c>
       <c r="B734" s="2" t="n">
-        <v>46006</v>
+        <v>45377</v>
       </c>
       <c r="C734" s="3" t="inlineStr">
         <is>
-          <t>Ahmad Istiak</t>
+          <t>Mohammad Afzalur Rahman</t>
         </is>
       </c>
       <c r="D734" s="3" t="inlineStr">
         <is>
-          <t>The funding network of 1971</t>
+          <t>Echoes of 1971: A journey through memories</t>
         </is>
       </c>
       <c r="E734" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/news/bangladesh/news/funding-network-1971-4058551</t>
+          <t>https://www.thedailystar.net/supplements/independence-day-special-2024/news/echoes-1971-journey-through-memories-3575181</t>
         </is>
       </c>
     </row>
@@ -20094,21 +20094,21 @@
         <v>734</v>
       </c>
       <c r="B735" s="2" t="n">
-        <v>46007</v>
+        <v>45377</v>
       </c>
       <c r="C735" s="3" t="inlineStr">
         <is>
-          <t>Ahmad Istiak</t>
+          <t>Muntassir Mamoon</t>
         </is>
       </c>
       <c r="D735" s="3" t="inlineStr">
         <is>
-          <t>From the plains to the hills: The indigenous bravery in Liberation War</t>
+          <t>Rao Farman Ali and 1971</t>
         </is>
       </c>
       <c r="E735" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/news/bangladesh/news/plains-hills-indigenous-bravery-liberation-war-4059446</t>
+          <t>https://www.thedailystar.net/supplements/independence-day-special-2024/news/rao-farman-ali-and-1971-3575166</t>
         </is>
       </c>
     </row>
@@ -20117,21 +20117,21 @@
         <v>735</v>
       </c>
       <c r="B736" s="2" t="n">
-        <v>46050</v>
+        <v>45377</v>
       </c>
       <c r="C736" s="3" t="inlineStr">
         <is>
-          <t>Rahat Minhaz</t>
+          <t>Amrin Tasnim Rafa</t>
         </is>
       </c>
       <c r="D736" s="3" t="inlineStr">
         <is>
-          <t>Remembering Mark Tully, the trusted chronicler of 1971</t>
+          <t>The significance of Bangladesh's Independence Day and Victory Day</t>
         </is>
       </c>
       <c r="E736" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/opinion/views/news/remembering-mark-tully-the-trusted-chronicler-1971-4092006</t>
+          <t>https://www.thedailystar.net/rising-stars/news/the-significance-bangladeshs-independence-day-and-victory-day-3575421</t>
         </is>
       </c>
     </row>
@@ -20140,21 +20140,21 @@
         <v>736</v>
       </c>
       <c r="B737" s="2" t="n">
-        <v>46107</v>
+        <v>45377</v>
       </c>
       <c r="C737" s="3" t="inlineStr">
         <is>
-          <t>Sushanta Ghosh</t>
+          <t>Priyam Paul</t>
         </is>
       </c>
       <c r="D737" s="3" t="inlineStr">
         <is>
-          <t>Morar Bhita: a ’71 massacre site still frozen in fear</t>
+          <t>The untold story of Jashore’s resistance during the Liberation War</t>
         </is>
       </c>
       <c r="E737" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/news/bangladesh/news/morar-bhita-71-massacre-site-still-frozen-fear-4135791</t>
+          <t>https://www.thedailystar.net/supplements/independence-day-special-2024/news/the-untold-story-jashores-resistance-during-the-liberation-war-3575086</t>
         </is>
       </c>
     </row>
@@ -20163,21 +20163,21 @@
         <v>737</v>
       </c>
       <c r="B738" s="2" t="n">
-        <v>46107</v>
+        <v>45377</v>
       </c>
       <c r="C738" s="3" t="inlineStr">
         <is>
-          <t>Mohiuddin Alamgir</t>
+          <t>Kanak Das Gupta</t>
         </is>
       </c>
       <c r="D738" s="3" t="inlineStr">
         <is>
-          <t>Witnesses to genocide</t>
+          <t>Two Martyred Pandits: Sharada &amp; Annada Charan</t>
         </is>
       </c>
       <c r="E738" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/news/bangladesh/news/witnesses-genocide-4135726</t>
+          <t>https://www.thedailystar.net/supplements/independence-day-special-2024/news/two-martyred-pandits-sharada-annada-charan-3575171</t>
         </is>
       </c>
     </row>
@@ -20186,26 +20186,739 @@
         <v>738</v>
       </c>
       <c r="B739" s="2" t="n">
+        <v>45390</v>
+      </c>
+      <c r="C739" s="3" t="inlineStr">
+        <is>
+          <t>Khashruzzamn Choudhury</t>
+        </is>
+      </c>
+      <c r="D739" s="3" t="inlineStr">
+        <is>
+          <t>A freedom fighter’s journey to Mujibnagar</t>
+        </is>
+      </c>
+      <c r="E739" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/opinion/focus/news/freedom-fighters-journey-mujibnagar-3584516</t>
+        </is>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" t="n">
+        <v>739</v>
+      </c>
+      <c r="B740" s="2" t="n">
+        <v>45421</v>
+      </c>
+      <c r="C740" s="3" t="inlineStr">
+        <is>
+          <t>Maliha Mashiat</t>
+        </is>
+      </c>
+      <c r="D740" s="3" t="inlineStr">
+        <is>
+          <t>‘Rise of Nation’: Liberation War through the ‘eyes’ of refugees at Raghu Rai’s exhibition</t>
+        </is>
+      </c>
+      <c r="E740" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/entertainment/theatre-arts/news/rise-nation-liberation-war-through-the-eyes-refugees-raghu-rais-exhibition-3605911</t>
+        </is>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" t="n">
+        <v>740</v>
+      </c>
+      <c r="B741" s="2" t="n">
+        <v>45638</v>
+      </c>
+      <c r="C741" s="3" t="inlineStr">
+        <is>
+          <t>Our Correspondent, Mymensingh</t>
+        </is>
+      </c>
+      <c r="D741" s="3" t="inlineStr">
+        <is>
+          <t>The forgotten lens of Liberation War</t>
+        </is>
+      </c>
+      <c r="E741" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/news/bangladesh/news/the-forgotten-lens-liberation-war-3774166</t>
+        </is>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" t="n">
+        <v>741</v>
+      </c>
+      <c r="B742" s="2" t="n">
+        <v>45640</v>
+      </c>
+      <c r="C742" s="3" t="inlineStr">
+        <is>
+          <t>Kamrul Hassan Mamun</t>
+        </is>
+      </c>
+      <c r="D742" s="3" t="inlineStr">
+        <is>
+          <t>A Loss That Still Haunts Bangladesh</t>
+        </is>
+      </c>
+      <c r="E742" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/martyred-intellectuals-day-2024/news/loss-still-haunts-bangladesh-3775566</t>
+        </is>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" t="n">
+        <v>742</v>
+      </c>
+      <c r="B743" s="2" t="n">
+        <v>45640</v>
+      </c>
+      <c r="C743" s="3" t="inlineStr">
+        <is>
+          <t>Priyam Paul</t>
+        </is>
+      </c>
+      <c r="D743" s="3" t="inlineStr">
+        <is>
+          <t>Martyrs of Freedom</t>
+        </is>
+      </c>
+      <c r="E743" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/martyred-intellectuals-day-2024/news/martyrs-freedom-3775576</t>
+        </is>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" t="n">
+        <v>743</v>
+      </c>
+      <c r="B744" s="2" t="n">
+        <v>45641</v>
+      </c>
+      <c r="C744" s="3" t="inlineStr">
+        <is>
+          <t>Ahmad Istiak</t>
+        </is>
+      </c>
+      <c r="D744" s="3" t="inlineStr">
+        <is>
+          <t>Regional Resistance: Purbo Banglar Jatiya Mukti Bahini</t>
+        </is>
+      </c>
+      <c r="E744" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/news/bangladesh/news/regional-resistance-purbo-banglar-jatiya-mukti-bahini-3776411</t>
+        </is>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" t="n">
+        <v>744</v>
+      </c>
+      <c r="B745" s="2" t="n">
+        <v>45642</v>
+      </c>
+      <c r="C745" s="3" t="inlineStr">
+        <is>
+          <t>RBR</t>
+        </is>
+      </c>
+      <c r="D745" s="3" t="inlineStr">
+        <is>
+          <t>1971 War Through a Child’s Eyes: Innocence Meets Reality</t>
+        </is>
+      </c>
+      <c r="E745" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/my-dhaka/news/1971-war-through-childs-eyes-innocence-meets-reality-3777481</t>
+        </is>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" t="n">
+        <v>745</v>
+      </c>
+      <c r="B746" s="2" t="n">
+        <v>45644</v>
+      </c>
+      <c r="C746" s="3" t="inlineStr">
+        <is>
+          <t>Mirza Shakil</t>
+        </is>
+      </c>
+      <c r="D746" s="3" t="inlineStr">
+        <is>
+          <t>The wonder of guerilla warfare in 1971</t>
+        </is>
+      </c>
+      <c r="E746" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/news/bangladesh/news/the-wonder-guerilla-warfare-1971-3778801</t>
+        </is>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" t="n">
+        <v>746</v>
+      </c>
+      <c r="B747" s="2" t="n">
+        <v>45723</v>
+      </c>
+      <c r="C747" s="3" t="inlineStr">
+        <is>
+          <t>Mohiuddin Alamgir</t>
+        </is>
+      </c>
+      <c r="D747" s="3" t="inlineStr">
+        <is>
+          <t>‘A speech more notable for what wasn’t said’</t>
+        </is>
+      </c>
+      <c r="E747" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/news/bangladesh/news/speech-more-notable-what-wasnt-said-3841511</t>
+        </is>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" t="n">
+        <v>747</v>
+      </c>
+      <c r="B748" s="2" t="n">
+        <v>45741</v>
+      </c>
+      <c r="C748" s="3" t="inlineStr">
+        <is>
+          <t>Kollol Kibria</t>
+        </is>
+      </c>
+      <c r="D748" s="3" t="inlineStr">
+        <is>
+          <t>Henry Kissinger’s role in 1971</t>
+        </is>
+      </c>
+      <c r="E748" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/opinion/views/news/henry-kissingers-role-1971-3857056</t>
+        </is>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" t="n">
+        <v>748</v>
+      </c>
+      <c r="B749" s="2" t="n">
+        <v>45741</v>
+      </c>
+      <c r="C749" s="3" t="inlineStr">
+        <is>
+          <t>The Daily Star</t>
+        </is>
+      </c>
+      <c r="D749" s="3" t="inlineStr">
+        <is>
+          <t>March 25 through the eyes of ordinary people</t>
+        </is>
+      </c>
+      <c r="E749" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/opinion/views/news/march-25-through-the-eyes-ordinary-people-3856476</t>
+        </is>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" t="n">
+        <v>749</v>
+      </c>
+      <c r="B750" s="2" t="n">
+        <v>45741</v>
+      </c>
+      <c r="C750" s="3" t="inlineStr">
+        <is>
+          <t>Ahmad Istiak</t>
+        </is>
+      </c>
+      <c r="D750" s="3" t="inlineStr">
+        <is>
+          <t>Operation searchlight: The massacre at Ctg cantonment</t>
+        </is>
+      </c>
+      <c r="E750" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/news/bangladesh/news/operation-searchlight-the-massacre-ctg-cantonment-3856676</t>
+        </is>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" t="n">
+        <v>750</v>
+      </c>
+      <c r="B751" s="2" t="n">
+        <v>45742</v>
+      </c>
+      <c r="C751" s="3" t="inlineStr">
+        <is>
+          <t>Shahidul Islam and Priyam Paul</t>
+        </is>
+      </c>
+      <c r="D751" s="3" t="inlineStr">
+        <is>
+          <t>Between bullets and borders Fleeing the Rajshahi massacre</t>
+        </is>
+      </c>
+      <c r="E751" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/supplements/independence-day-special-2025/news/between-bullets-and-borders-fleeing-the-rajshahi-massacre-3857846</t>
+        </is>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" t="n">
+        <v>751</v>
+      </c>
+      <c r="B752" s="2" t="n">
+        <v>45742</v>
+      </c>
+      <c r="C752" s="3" t="inlineStr">
+        <is>
+          <t>Miftahul Jannat</t>
+        </is>
+      </c>
+      <c r="D752" s="3" t="inlineStr">
+        <is>
+          <t>Global Chords of Freedom</t>
+        </is>
+      </c>
+      <c r="E752" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/supplements/independence-day-special-2025/news/global-chords-freedom-3857811</t>
+        </is>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" t="n">
+        <v>752</v>
+      </c>
+      <c r="B753" s="2" t="n">
+        <v>45742</v>
+      </c>
+      <c r="C753" s="3" t="inlineStr">
+        <is>
+          <t>Ahmad Istiak</t>
+        </is>
+      </c>
+      <c r="D753" s="3" t="inlineStr">
+        <is>
+          <t>The legend of Nader gunda</t>
+        </is>
+      </c>
+      <c r="E753" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/news/bangladesh/news/the-legend-nader-gunda-3857581</t>
+        </is>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" t="n">
+        <v>753</v>
+      </c>
+      <c r="B754" s="2" t="n">
+        <v>45742</v>
+      </c>
+      <c r="C754" s="3" t="inlineStr">
+        <is>
+          <t>Rahat Minhaz</t>
+        </is>
+      </c>
+      <c r="D754" s="3" t="inlineStr">
+        <is>
+          <t>The People in 1971</t>
+        </is>
+      </c>
+      <c r="E754" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/supplements/independence-day-special-2025/news/the-people-1971-3857821</t>
+        </is>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" t="n">
+        <v>754</v>
+      </c>
+      <c r="B755" s="2" t="n">
+        <v>45742</v>
+      </c>
+      <c r="C755" s="3" t="inlineStr">
+        <is>
+          <t>Anu Muhammad</t>
+        </is>
+      </c>
+      <c r="D755" s="3" t="inlineStr">
+        <is>
+          <t>The road to liberation: March 1971 and the years that led to it</t>
+        </is>
+      </c>
+      <c r="E755" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/opinion/views/news/the-road-liberation-march-1971-and-the-years-led-it-3857441</t>
+        </is>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" t="n">
+        <v>755</v>
+      </c>
+      <c r="B756" s="2" t="n">
+        <v>45742</v>
+      </c>
+      <c r="C756" s="3" t="inlineStr">
+        <is>
+          <t>Priyam Paul</t>
+        </is>
+      </c>
+      <c r="D756" s="3" t="inlineStr">
+        <is>
+          <t>‘The truths written in blood cannot be erased by lies’</t>
+        </is>
+      </c>
+      <c r="E756" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/supplements/independence-day-special-2025/news/the-truths-written-blood-cannot-be-erased-lies-3857806</t>
+        </is>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" t="n">
+        <v>756</v>
+      </c>
+      <c r="B757" s="2" t="n">
+        <v>45764</v>
+      </c>
+      <c r="C757" s="3" t="inlineStr">
+        <is>
+          <t>Priyam Paul</t>
+        </is>
+      </c>
+      <c r="D757" s="3" t="inlineStr">
+        <is>
+          <t>The Proclamation of Independence was a beacon for Bangladesh</t>
+        </is>
+      </c>
+      <c r="E757" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/opinion/views/news/the-proclamation-independence-was-beacon-bangladesh-3872661</t>
+        </is>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" t="n">
+        <v>757</v>
+      </c>
+      <c r="B758" s="2" t="n">
+        <v>45764</v>
+      </c>
+      <c r="C758" s="3" t="inlineStr">
+        <is>
+          <t>Mohiuddin Alamgir</t>
+        </is>
+      </c>
+      <c r="D758" s="3" t="inlineStr">
+        <is>
+          <t>The spirit of Mujibnagar government can still guide us</t>
+        </is>
+      </c>
+      <c r="E758" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/news/bangladesh/news/the-spirit-mujibnagar-government-can-still-guide-us-3873231</t>
+        </is>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" t="n">
+        <v>758</v>
+      </c>
+      <c r="B759" s="2" t="n">
+        <v>45997</v>
+      </c>
+      <c r="C759" s="3" t="inlineStr">
+        <is>
+          <t>Our Correspondent, Benapole</t>
+        </is>
+      </c>
+      <c r="D759" s="3" t="inlineStr">
+        <is>
+          <t>Jashore: First district to be freed on December 6, 1971</t>
+        </is>
+      </c>
+      <c r="E759" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/news/bangladesh/news/jashore-first-district-be-freed-december-6-1971-4052301</t>
+        </is>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" t="n">
+        <v>759</v>
+      </c>
+      <c r="B760" s="2" t="n">
+        <v>46005</v>
+      </c>
+      <c r="C760" s="3" t="inlineStr">
+        <is>
+          <t>Miftahul Jannat</t>
+        </is>
+      </c>
+      <c r="D760" s="3" t="inlineStr">
+        <is>
+          <t>A compassionate rebel in a doctor’s coat</t>
+        </is>
+      </c>
+      <c r="E760" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/supplements/martyred-intellectuals-day-2025/news/compassionate-rebel-doctors-coat-4057356</t>
+        </is>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" t="n">
+        <v>760</v>
+      </c>
+      <c r="B761" s="2" t="n">
+        <v>46005</v>
+      </c>
+      <c r="C761" s="3" t="inlineStr">
+        <is>
+          <t>The Daily Star</t>
+        </is>
+      </c>
+      <c r="D761" s="3" t="inlineStr">
+        <is>
+          <t>Martyred intellectuals are our guiding lights</t>
+        </is>
+      </c>
+      <c r="E761" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/opinion/editorial/news/martyred-intellectuals-are-our-guiding-lights-4058291</t>
+        </is>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" t="n">
+        <v>761</v>
+      </c>
+      <c r="B762" s="2" t="n">
+        <v>46005</v>
+      </c>
+      <c r="C762" s="3" t="inlineStr">
+        <is>
+          <t>Mohammed Ishtiaque Khan</t>
+        </is>
+      </c>
+      <c r="D762" s="3" t="inlineStr">
+        <is>
+          <t>Martyred intellectuals: The torchbearers of our nation</t>
+        </is>
+      </c>
+      <c r="E762" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/opinion/views/news/martyred-intellectuals-torchbearers-our-nation-4057646</t>
+        </is>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" t="n">
+        <v>762</v>
+      </c>
+      <c r="B763" s="2" t="n">
+        <v>46005</v>
+      </c>
+      <c r="C763" s="3" t="inlineStr">
+        <is>
+          <t>Ahmad Istiak</t>
+        </is>
+      </c>
+      <c r="D763" s="3" t="inlineStr">
+        <is>
+          <t>Martyred Intellectuals’ Day: Horrors of Saidpur’s intellectual massacre</t>
+        </is>
+      </c>
+      <c r="E763" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/news/bangladesh/news/martyred-intellectuals-day-horrors-saidpurs-intellectual-massacre-4057741</t>
+        </is>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" t="n">
+        <v>763</v>
+      </c>
+      <c r="B764" s="2" t="n">
+        <v>46005</v>
+      </c>
+      <c r="C764" s="3" t="inlineStr">
+        <is>
+          <t>Asif Bin Ali</t>
+        </is>
+      </c>
+      <c r="D764" s="3" t="inlineStr">
+        <is>
+          <t>What does it mean to honour the legacy of Bangladesh’s martyred intellectuals?</t>
+        </is>
+      </c>
+      <c r="E764" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/opinion/views/news/what-does-it-mean-honour-legacy-bangladeshs-martyred-intellectuals-4057641</t>
+        </is>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" t="n">
+        <v>764</v>
+      </c>
+      <c r="B765" s="2" t="n">
+        <v>46006</v>
+      </c>
+      <c r="C765" s="3" t="inlineStr">
+        <is>
+          <t>Ahmad Istiak</t>
+        </is>
+      </c>
+      <c r="D765" s="3" t="inlineStr">
+        <is>
+          <t>The funding network of 1971</t>
+        </is>
+      </c>
+      <c r="E765" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/news/bangladesh/news/funding-network-1971-4058551</t>
+        </is>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" t="n">
+        <v>765</v>
+      </c>
+      <c r="B766" s="2" t="n">
+        <v>46007</v>
+      </c>
+      <c r="C766" s="3" t="inlineStr">
+        <is>
+          <t>Ahmad Istiak</t>
+        </is>
+      </c>
+      <c r="D766" s="3" t="inlineStr">
+        <is>
+          <t>From the plains to the hills: The indigenous bravery in Liberation War</t>
+        </is>
+      </c>
+      <c r="E766" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/news/bangladesh/news/plains-hills-indigenous-bravery-liberation-war-4059446</t>
+        </is>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" t="n">
+        <v>766</v>
+      </c>
+      <c r="B767" s="2" t="n">
+        <v>46050</v>
+      </c>
+      <c r="C767" s="3" t="inlineStr">
+        <is>
+          <t>Rahat Minhaz</t>
+        </is>
+      </c>
+      <c r="D767" s="3" t="inlineStr">
+        <is>
+          <t>Remembering Mark Tully, the trusted chronicler of 1971</t>
+        </is>
+      </c>
+      <c r="E767" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/opinion/views/news/remembering-mark-tully-the-trusted-chronicler-1971-4092006</t>
+        </is>
+      </c>
+    </row>
+    <row r="768">
+      <c r="A768" t="n">
+        <v>767</v>
+      </c>
+      <c r="B768" s="2" t="n">
+        <v>46107</v>
+      </c>
+      <c r="C768" s="3" t="inlineStr">
+        <is>
+          <t>Sushanta Ghosh</t>
+        </is>
+      </c>
+      <c r="D768" s="3" t="inlineStr">
+        <is>
+          <t>Morar Bhita: a ’71 massacre site still frozen in fear</t>
+        </is>
+      </c>
+      <c r="E768" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/news/bangladesh/news/morar-bhita-71-massacre-site-still-frozen-fear-4135791</t>
+        </is>
+      </c>
+    </row>
+    <row r="769">
+      <c r="A769" t="n">
+        <v>768</v>
+      </c>
+      <c r="B769" s="2" t="n">
+        <v>46107</v>
+      </c>
+      <c r="C769" s="3" t="inlineStr">
+        <is>
+          <t>Mohiuddin Alamgir</t>
+        </is>
+      </c>
+      <c r="D769" s="3" t="inlineStr">
+        <is>
+          <t>Witnesses to genocide</t>
+        </is>
+      </c>
+      <c r="E769" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/news/bangladesh/news/witnesses-genocide-4135726</t>
+        </is>
+      </c>
+    </row>
+    <row r="770">
+      <c r="A770" t="n">
+        <v>769</v>
+      </c>
+      <c r="B770" s="2" t="n">
         <v>46139</v>
       </c>
-      <c r="C739" s="3" t="inlineStr">
+      <c r="C770" s="3" t="inlineStr">
         <is>
           <t>Karim Waheed</t>
         </is>
       </c>
-      <c r="D739" s="3" t="inlineStr">
+      <c r="D770" s="3" t="inlineStr">
         <is>
           <t>Thank you, Raghu Rai, for showing me the 1971 I had not known</t>
         </is>
       </c>
-      <c r="E739" s="4" t="inlineStr">
+      <c r="E770" s="4" t="inlineStr">
         <is>
           <t>https://www.thedailystar.net/culture/news/thank-you-raghu-rai-showing-me-the-1971-i-had-not-known-4162106</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E739"/>
+  <autoFilter ref="A1:E770"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId2"/>
@@ -20945,6 +21658,37 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E737" r:id="rId736"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E738" r:id="rId737"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E739" r:id="rId738"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E740" r:id="rId739"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E741" r:id="rId740"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E742" r:id="rId741"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E743" r:id="rId742"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E744" r:id="rId743"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E745" r:id="rId744"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E746" r:id="rId745"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E747" r:id="rId746"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E748" r:id="rId747"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E749" r:id="rId748"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E750" r:id="rId749"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E751" r:id="rId750"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E752" r:id="rId751"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E753" r:id="rId752"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E754" r:id="rId753"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E755" r:id="rId754"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E756" r:id="rId755"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E757" r:id="rId756"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E758" r:id="rId757"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E759" r:id="rId758"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E760" r:id="rId759"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E761" r:id="rId760"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E762" r:id="rId761"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E763" r:id="rId762"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E764" r:id="rId763"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E765" r:id="rId764"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E766" r:id="rId765"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E767" r:id="rId766"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E768" r:id="rId767"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E769" r:id="rId768"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E770" r:id="rId769"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -21368,7 +22112,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -21434,21 +22178,21 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>44179</v>
+        <v>42054</v>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Naznin Tithi</t>
+          <t>EAM Asaduzzaman, Nilphamari</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>Kobor: A unique artistic representation of an unusual situation</t>
+          <t>Women Language Movement heroes of Nilphamari</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/supplements/news/kobor-unique-artistic-representation-unusual-situation-2010757</t>
+          <t>https://www.thedailystar.net/country/women-language-movement-heroes-nilphamari-2785</t>
         </is>
       </c>
     </row>
@@ -21457,21 +22201,21 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>44238</v>
+        <v>42056</v>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Nahaly Nafisa Khan</t>
+          <t>The Daily Star</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>How 1952 paved the way for 1971</t>
+          <t>Ekushey, the eternal beacon</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/book-reviews/news/how-1952-paved-the-way-1971-2042985</t>
+          <t>https://www.thedailystar.net/editorial/ekushey-the-eternal-beacon-3042</t>
         </is>
       </c>
     </row>
@@ -21480,31 +22224,1399 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="n">
+        <v>42056</v>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Mahbub Ul Alam Chowdhury</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>First Poem on Ekushey</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/literature/news/first-poem-ekushey-3055</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>42419</v>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>EAM Asaduzzaman</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>School students played glorious role in Language Movement</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/country/news/school-students-played-glorious-role-language-movement-574438</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>42429</v>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Ahmed Humayun Kabir Topu</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>A nearly forgotten chapter of Language Movement</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/country/news/nearly-forgotten-chapter-language-movement-783760</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>42783</v>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Our Correspondent, Jhenidah</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Reminiscence of days of 1952</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/country/reminiscence-days-1952-1362472</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>42787</v>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>M. Waheeduzzaman Manik</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>A literary history of the Language Movement</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/op-ed/literary-history-the-language-movement-1364386</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>42787</v>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Mofidul Hoque</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>How February 21 became 'Ekushey'</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/supplements/how-february-21-became-ekushey-1364308</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>42787</v>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>The Daily Star</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Remembering Ekushey</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/editorial/remembering-ekushey-1364368</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>42792</v>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Our Correspondent, Mymensingh</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>1952 still etched on his memory</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/country/1952-still-etched-his-memory-1367233</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>43148</v>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Sohana Manzoor</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Prof. Rafiqul Islam: A Witness to the Language Movement and the Liberation of Bangladesh</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/literature/news/prof-rafiqul-islam-witness-the-language-movement-and-the-liberation-bangladesh-1535875</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>43152</v>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Nazmul Ahasan</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>Shahidullah, a linguist and language activist</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/supplements/amar-ekushey-2018/shahidullah-linguist-and-language-activist-1537948</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>43152</v>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>The Daily Star</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>The eternal Ekushey</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/editorial/the-eternal-ekushey-1537672</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>43152</v>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Sadya Afreen Mallick</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>TRIBUTE TO OUR LANGUAGE MARTYRS</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/arts-entertainment/international-mother-language-day-21st-february-2018-tribute-our-language-martyrs-1537546</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>43155</v>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Fakrul Alam</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>From Ekushey to International Mother Language Day and Beyond</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/literature/ekushey-february-1952-to-international-mother-language-day-and-beyond-1539088</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>43517</v>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>MR MAHBUB</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>A booklet that changed the course of history</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/supplements/amar-ekushey-2019/news/booklet-changed-the-course-history-1704736</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>43517</v>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>Syed Mansur Hashim</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>Bhasha Andolon Museum: A private initiative by a few</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/business/news/bhasha-andolon-museum-private-initiative-few-1704724</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>43517</v>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>The Daily Star</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>The eternal flame of Ekushey</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/editorial/news/the-eternal-flame-ekushey-1704946</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>43517</v>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>Adnan Zillur Morshed</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>The political algorithm of 21st February</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/opinion/the-grudging-urbanist/news/the-political-algorithm-21st-february-1704925</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>43518</v>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>The Daily Star</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>Central Shaheed Minar</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/star-weekend/history/news/central-shaheed-minar-1705651</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>43518</v>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>Md Shahnawaz Khan Chandan</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>The Forgotten Museum of Language Movement</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/star-weekend/heritage/news/the-forgotten-museum-language-movement-1705684</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>43882</v>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>Sarah Anjum Bari</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>ANWARA KHATUN: The outspoken voice</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/supplements/amar-ekushey-2020/news/anwara-khatun-the-outspoken-voice-1871038</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>43882</v>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Shuprova Tasneem</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>Halima Khatun: On the frontline</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/supplements/amar-ekushey-2020/news/halima-begum-the-frontline-1871053</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>43882</v>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>M R Mahbub</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>Jobeda Khanam Chowdhury: Rallying the women of the north-east</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/supplements/amar-ekushey-2020/news/jobeda-khanam-chowdhury-rallying-the-women-the-north-east-1871047</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>43882</v>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>Maliha Khan</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>LAILA NUR: A force of resilience</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/supplements/amar-ekushey-2020/news/laila-nur-force-resilience-1871035</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>43882</v>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>Ahmed Humayun Kabir Topu</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>Language Movement in Pabna: Two heroes still not recognised</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/country/news/language-movement-pabna-two-female-heroes-still-not-recognised-1870948</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>43882</v>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>Naznin Tithi</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>Protibha Mutsuddi: An Indomitable Spirit</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/supplements/amar-ekushey-2020/news/protibha-mutsuddi-indomitable-spirit-1871056</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>43882</v>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>Wasim Bin Habib</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>Rowshon Ara Bachchu: On the grounds with Salam, Barkat and Rafiq</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/supplements/amar-ekushey-2020/news/rowshon-ara-bachchu-the-grounds-salam-barkat-and-rafiq-1871041</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>43882</v>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>M R Mahbub</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>Sofia Khan: Resolute in her fight against oppression</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/supplements/amar-ekushey-2020/news/sofia-khan-resolute-her-fight-against-oppression-1871050</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="2" t="n">
+        <v>43882</v>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>CHEMAN ARA</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>The women who broke the barricades</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/supplements/amar-ekushey-2020/news/the-women-who-broke-the-barricades-1871062</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="2" t="n">
+        <v>44179</v>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>Naznin Tithi</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>Kobor: A unique artistic representation of an unusual situation</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/supplements/news/kobor-unique-artistic-representation-unusual-situation-2010757</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="2" t="n">
+        <v>44238</v>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>Nahaly Nafisa Khan</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>How 1952 paved the way for 1971</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/book-reviews/news/how-1952-paved-the-way-1971-2042985</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="2" t="n">
         <v>44247</v>
       </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>The Daily Star</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>The Daily Star</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
         <is>
           <t>The Spirit of 1971 – The Beginning</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E35" s="4" t="inlineStr">
         <is>
           <t>https://www.thedailystar.net/literature/news/the-spirit-1971-the-beginning-2048021</t>
         </is>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="2" t="n">
+        <v>44613</v>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>Niaz Zaman</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>I have not come to weep</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/international-mother-language-day-2022/news/i-have-not-come-weep-2966746</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="2" t="n">
+        <v>44613</v>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>The Daily Star</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>Indomitable Ekushey</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/views/editorial/news/indomitable-ekushey-2966781</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="2" t="n">
+        <v>44613</v>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>Kamruddin Ahmad</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>Language Movement: The Momentous Phase</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/international-mother-language-day-2022/news/language-movement-the-momentous-phase-2966716</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="2" t="n">
+        <v>44613</v>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>Azfar Hussain</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>Our Language Movement: Moments, Momentum, Milieu</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/views/opinion/news/our-language-movement-moments-momentum-milieu-2966801</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" s="2" t="n">
+        <v>44613</v>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>Dr Mahmud Shah Qureshi</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>Struggle for the State Language</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/international-mother-language-day-2022/news/struggle-the-state-language-2966761</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" s="2" t="n">
+        <v>44613</v>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>Mohammad Afzalur Rahman</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>The Language Movement Revisited</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/international-mother-language-day-2022/news/the-language-movement-revisited-2966711</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" s="2" t="n">
+        <v>44615</v>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>Ahmed Humayun Kabir Topu</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>The bell ringer of language movement</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/news/bangladesh/news/the-bell-ringer-language-movement-2968276</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" s="2" t="n">
+        <v>44977</v>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>Ashif Ahmed Rudro</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>4 Lesser-known facts about Ekushey February</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/life-living/news/4-lesser-known-facts-about-ekushey-february-3252941</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" s="2" t="n">
+        <v>44978</v>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>Maisha Islam Monamee</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>5 books to read this year in observance of Ekushey February</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/daily-star-books/news/5-books-read-year-observance-ekushey-february-3253736</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" s="2" t="n">
+        <v>44978</v>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>Ahmed Kamal</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>An unexplored facet of the language movement’s historiography</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/supplements/amar-ekushe-2023/news/unexplored-facet-the-language-movements-historiography-3253326</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" s="2" t="n">
+        <v>44978</v>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>Mahmud Shah Qureshi</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>Remembering Zahir Raihan: A Language Activist and Trailblazer</t>
+        </is>
+      </c>
+      <c r="E46" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/supplements/amar-ekushe-2023/news/remembering-zahir-raihan-language-activist-and-trailblazer-3253316</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" s="2" t="n">
+        <v>45343</v>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>Priyam Pritim Paul</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>Dr Shahidullah’s thoughts on India and Pakistan’s language problem</t>
+        </is>
+      </c>
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/supplements/amar-ekushe-2024/news/dr-shahidullahs-thoughts-india-and-pakistans-language-problem-3549096</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" s="2" t="n">
+        <v>45343</v>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>M Abdul Alim</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>Through the lens of Rafiqul Islam</t>
+        </is>
+      </c>
+      <c r="E48" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/supplements/amar-ekushe-2024/news/through-the-lens-rafiqul-islam-3549041</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" s="2" t="n">
+        <v>45344</v>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>Zahangir Shah</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>Remembering a language martyr</t>
+        </is>
+      </c>
+      <c r="E49" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/news/bangladesh/news/remembering-language-martyr-3549826</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" s="2" t="n">
+        <v>45690</v>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>Ahmad Istiak</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>Language Movement in Faridpur</t>
+        </is>
+      </c>
+      <c r="E50" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/news/bangladesh/news/language-movement-faridpur-3813921</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" s="2" t="n">
+        <v>45692</v>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>Ahmad Istiak</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>Language Movement in Pabna</t>
+        </is>
+      </c>
+      <c r="E51" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/news/bangladesh/news/language-movement-pabna-3815631</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" s="2" t="n">
+        <v>45693</v>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>Ahmad Istiak</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>Language Movement in Tangail</t>
+        </is>
+      </c>
+      <c r="E52" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/news/bangladesh/news/language-movement-tangail-3816451</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" s="2" t="n">
+        <v>45694</v>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>Ahmad Istiak</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>Language Movement in Rangpur</t>
+        </is>
+      </c>
+      <c r="E53" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/news/bangladesh/news/language-movement-rangpur-3817206</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" s="2" t="n">
+        <v>45696</v>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>Ahmad Istiak</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>Dr Muhammad Shahidullah’s role in Language Movement</t>
+        </is>
+      </c>
+      <c r="E54" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/news/bangladesh/news/dr-muhammad-shahidullahs-role-language-movement-3818706</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" s="2" t="n">
+        <v>45698</v>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>Ahmad Istiak</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>Mymensingh resists Urdu as state language</t>
+        </is>
+      </c>
+      <c r="E55" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/news/bangladesh/news/mymensingh-resists-urdu-state-language-3820301</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" s="2" t="n">
+        <v>45709</v>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>Mintu Deshwara</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>A forgotten hero of the Language Movement</t>
+        </is>
+      </c>
+      <c r="E56" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/news/bangladesh/news/forgotten-hero-the-language-movement-3829821</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" s="2" t="n">
+        <v>45709</v>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>Md Aminul Islam</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>Abdul Aziz: A silent pillar of the Language Movement</t>
+        </is>
+      </c>
+      <c r="E57" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/news/bangladesh/news/abdul-aziz-silent-pillar-the-language-movement-3829951</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" s="2" t="n">
+        <v>45709</v>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>Azfar Hussain</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>Language, land, labour, and liberation: Reclaiming the radical roots of Ekushey</t>
+        </is>
+      </c>
+      <c r="E58" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/supplements/amar-ekushey-2025/news/language-land-labour-and-liberation-reclaiming-the-radical-roots-ekushey-3829651</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" s="2" t="n">
+        <v>45709</v>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>Lamia Karim</t>
+        </is>
+      </c>
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t>Legacy of Ekushey February: My mother’s story of 1952</t>
+        </is>
+      </c>
+      <c r="E59" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/opinion/views/news/legacy-ekushey-february-my-mothers-story-1952-3829421</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" s="2" t="n">
+        <v>45709</v>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>Faridul Alam</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>The impact of the language movement on our national psyche</t>
+        </is>
+      </c>
+      <c r="E60" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/supplements/amar-ekushey-2025/news/the-impact-the-language-movement-our-national-psyche-3829631</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" s="2" t="n">
+        <v>45709</v>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>The Daily Star</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t>Upholding the legacy of Ekushey</t>
+        </is>
+      </c>
+      <c r="E61" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/opinion/editorial/news/upholding-the-legacy-ekushey-3829381</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" s="2" t="n">
+        <v>46074</v>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>Ahmad Istiak</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>Amar Ekushey: Fading memories of language heroes</t>
+        </is>
+      </c>
+      <c r="E62" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thedailystar.net/news/bangladesh/news/amar-ekushey-fading-memories-language-heroes-4111031</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E5"/>
+  <autoFilter ref="A1:E62"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E62" r:id="rId61"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -25168,7 +27280,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F52"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -25597,7 +27709,7 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>likely duplicate of https://www.thedailystar.net/reflections-on-the-liberation-war-17327 (same title and author)</t>
+          <t>likely duplicate of https://www.thedailystar.net/reflections-on-the-liberation-war-17327 (same title, author and text)</t>
         </is>
       </c>
     </row>
@@ -25627,27 +27739,27 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>likely duplicate of https://www.thedailystar.net/spirit-of-liberation-war-17307 (same title and author)</t>
+          <t>likely duplicate of https://www.thedailystar.net/spirit-of-liberation-war-17307 (same title, author and text)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>41622</v>
+        <v>42054</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Anthony Mascarenhas</t>
+          <t>EAM Asaduzzaman, Nilphamari</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>Genocide</t>
+          <t>Women Language Movement heroes of Nilphamari</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/genocide-2351</t>
+          <t>https://www.thedailystar.net/women-language-movement-heroes-of-nilphamari-65544</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -25657,27 +27769,27 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>likely duplicate of https://www.thedailystar.net/slow-reads/focus/news/genocide-1505440 (same title and author)</t>
+          <t>likely duplicate of https://www.thedailystar.net/country/women-language-movement-heroes-nilphamari-2785 (same title, author and text)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>43085</v>
+        <v>41622</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Kaberi Gayen</t>
+          <t>Anthony Mascarenhas</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>THE WAR OF FOOTAGE</t>
+          <t>Genocide</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/supplements/victory-day-special-2017/the-war-footage-1505443</t>
+          <t>https://www.thedailystar.net/genocide-2351</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -25687,27 +27799,27 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>likely duplicate of https://www.thedailystar.net/star-weekend/spotlight/televising-1971-the-war-footage-1380265 (same title and author)</t>
+          <t>likely duplicate of https://www.thedailystar.net/slow-reads/focus/news/genocide-1505440 (same title, author and text)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>43802</v>
+        <v>43085</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>The Daily Star</t>
+          <t>Kaberi Gayen</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>On this day in 1971</t>
+          <t>THE WAR OF FOOTAGE</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/frontpage/news/day-1971-1834984</t>
+          <t>https://www.thedailystar.net/supplements/victory-day-special-2017/the-war-footage-1505443</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -25717,27 +27829,27 @@
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>likely duplicate of https://www.thedailystar.net/frontpage/news/day-1971-1834492 (same title and author)</t>
+          <t>likely duplicate of https://www.thedailystar.net/star-weekend/spotlight/televising-1971-the-war-footage-1380265 (same title, author and text)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>43803</v>
+        <v>44264</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>The Daily Star</t>
+          <t>M Rafiqul Islam</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>On this day in 1971</t>
+          <t>The Historic Seventh March Speech of Bangabandhu: Its Influence on International Legal Discourse and Reform</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/frontpage/news/day-1971-1835425</t>
+          <t>https://www.thedailystar.net/law-our-rights/news/the-historic-seventh-march-speech-bangabandhu-its-influence-international-legal-discourse-and-reform-2057325</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -25747,27 +27859,27 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>likely duplicate of https://www.thedailystar.net/frontpage/news/day-1971-1834492 (same title and author)</t>
+          <t>likely duplicate of https://www.thedailystar.net/law-our-rights/news/the-historic-seventh-march-speech-bangabandhu-its-influence-international-legal-discourse-and-reform-2056313 (same title, author and text)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>43804</v>
+        <v>42818</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>The Daily Star</t>
+          <t>Nayanika Mookherjee</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>On this day in 1971</t>
+          <t>HISTORY AND THE BIRANGONA</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/backpage/news/day-1971-1835920</t>
+          <t>https://www.thedailystar.net/star-weekend/long-form/history-and-the-birangona-1380280</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -25777,27 +27889,27 @@
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>likely duplicate of https://www.thedailystar.net/frontpage/news/day-1971-1834492 (same title and author)</t>
+          <t>likely duplicate of https://www.thedailystar.net/in-focus/news/history-and-the-birangona-2114681 (same title, author and text)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>43805</v>
+        <v>44544</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>The Daily Star</t>
+          <t>Serajul Islam Choudhury</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>On this day in 1971</t>
+          <t>The commitment of the martyred intellectuals</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/backpage/news/day-1971-1836391</t>
+          <t>https://www.thedailystar.net/views/opinion/news/the-commitment-the-martyred-intellectuals-2916866</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -25807,934 +27919,34 @@
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>likely duplicate of https://www.thedailystar.net/frontpage/news/day-1971-1834492 (same title and author)</t>
+          <t>likely duplicate of https://www.thedailystar.net/the-commitment-of-the-martyred-intellectuals-2432 (same title, author and text)</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="n">
-        <v>43806</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>The Daily Star</t>
-        </is>
-      </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>On this day in 1971</t>
+          <t>Operation Searchlight on March 25 1971: The night hell opened over Dhaka</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/frontpage/news/day-1971-1836871</t>
+          <t>https://www.thedailystar.net/slow-reads/slow-reads-special/operation-searchlight/news/operation-searchlight-the-night-hell-opened-over-dhaka-4135406</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>(not listed - duplicate)</t>
+          <t>(not listed - could not be fetched)</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>likely duplicate of https://www.thedailystar.net/frontpage/news/day-1971-1834492 (same title and author)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="n">
-        <v>43807</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>The Daily Star</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>On this day in 1971</t>
-        </is>
-      </c>
-      <c r="D23" s="4" t="inlineStr">
-        <is>
-          <t>https://www.thedailystar.net/frontpage/news/day-1971-1837258</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>(not listed - duplicate)</t>
-        </is>
-      </c>
-      <c r="F23" s="3" t="inlineStr">
-        <is>
-          <t>likely duplicate of https://www.thedailystar.net/frontpage/news/day-1971-1834492 (same title and author)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="n">
-        <v>43808</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>The Daily Star</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>On this day in 1971</t>
-        </is>
-      </c>
-      <c r="D24" s="4" t="inlineStr">
-        <is>
-          <t>https://www.thedailystar.net/frontpage/news/day-1971-1837690</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>(not listed - duplicate)</t>
-        </is>
-      </c>
-      <c r="F24" s="3" t="inlineStr">
-        <is>
-          <t>likely duplicate of https://www.thedailystar.net/frontpage/news/day-1971-1834492 (same title and author)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="n">
-        <v>43809</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>The Daily Star</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>On this day in 1971</t>
-        </is>
-      </c>
-      <c r="D25" s="4" t="inlineStr">
-        <is>
-          <t>https://www.thedailystar.net/frontpage/news/day-1971-1838104</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>(not listed - duplicate)</t>
-        </is>
-      </c>
-      <c r="F25" s="3" t="inlineStr">
-        <is>
-          <t>likely duplicate of https://www.thedailystar.net/frontpage/news/day-1971-1834492 (same title and author)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="n">
-        <v>43810</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>The Daily Star</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>On this day in 1971</t>
-        </is>
-      </c>
-      <c r="D26" s="4" t="inlineStr">
-        <is>
-          <t>https://www.thedailystar.net/backpage/news/day-1971-1838581</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>(not listed - duplicate)</t>
-        </is>
-      </c>
-      <c r="F26" s="3" t="inlineStr">
-        <is>
-          <t>likely duplicate of https://www.thedailystar.net/frontpage/news/day-1971-1834492 (same title and author)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="n">
-        <v>43811</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>The Daily Star</t>
-        </is>
-      </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>On this day in 1971</t>
-        </is>
-      </c>
-      <c r="D27" s="4" t="inlineStr">
-        <is>
-          <t>https://www.thedailystar.net/frontpage/news/day-1971-1839046</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>(not listed - duplicate)</t>
-        </is>
-      </c>
-      <c r="F27" s="3" t="inlineStr">
-        <is>
-          <t>likely duplicate of https://www.thedailystar.net/frontpage/news/day-1971-1834492 (same title and author)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="n">
-        <v>43812</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>The Daily Star</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>On this day in 1971</t>
-        </is>
-      </c>
-      <c r="D28" s="4" t="inlineStr">
-        <is>
-          <t>https://www.thedailystar.net/backpage/news/day-1971-1839553</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>(not listed - duplicate)</t>
-        </is>
-      </c>
-      <c r="F28" s="3" t="inlineStr">
-        <is>
-          <t>likely duplicate of https://www.thedailystar.net/frontpage/news/day-1971-1834492 (same title and author)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="n">
-        <v>43813</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>The Daily Star</t>
-        </is>
-      </c>
-      <c r="C29" s="3" t="inlineStr">
-        <is>
-          <t>On this day in 1971</t>
-        </is>
-      </c>
-      <c r="D29" s="4" t="inlineStr">
-        <is>
-          <t>https://www.thedailystar.net/backpage/news/day-1971-1839985</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>(not listed - duplicate)</t>
-        </is>
-      </c>
-      <c r="F29" s="3" t="inlineStr">
-        <is>
-          <t>likely duplicate of https://www.thedailystar.net/frontpage/news/day-1971-1834492 (same title and author)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="n">
-        <v>43814</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>The Daily Star</t>
-        </is>
-      </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>Martyred Intellectuals Day</t>
-        </is>
-      </c>
-      <c r="D30" s="4" t="inlineStr">
-        <is>
-          <t>https://www.thedailystar.net/editorial/news/martyred-intellectuals-day-1840315</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>(not listed - duplicate)</t>
-        </is>
-      </c>
-      <c r="F30" s="3" t="inlineStr">
-        <is>
-          <t>likely duplicate of https://www.thedailystar.net/editorial/martyred-intellectuals-day-1504534 (same title and author)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="n">
-        <v>43814</v>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>The Daily Star</t>
-        </is>
-      </c>
-      <c r="C31" s="3" t="inlineStr">
-        <is>
-          <t>On this day in 1971</t>
-        </is>
-      </c>
-      <c r="D31" s="4" t="inlineStr">
-        <is>
-          <t>https://www.thedailystar.net/frontpage/news/day-1971-1840465</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>(not listed - duplicate)</t>
-        </is>
-      </c>
-      <c r="F31" s="3" t="inlineStr">
-        <is>
-          <t>likely duplicate of https://www.thedailystar.net/frontpage/news/day-1971-1834492 (same title and author)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="n">
-        <v>43815</v>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>The Daily Star</t>
-        </is>
-      </c>
-      <c r="C32" s="3" t="inlineStr">
-        <is>
-          <t>On this day in 1971</t>
-        </is>
-      </c>
-      <c r="D32" s="4" t="inlineStr">
-        <is>
-          <t>https://www.thedailystar.net/frontpage/news/day-1971-1840846</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>(not listed - duplicate)</t>
-        </is>
-      </c>
-      <c r="F32" s="3" t="inlineStr">
-        <is>
-          <t>likely duplicate of https://www.thedailystar.net/frontpage/news/day-1971-1834492 (same title and author)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="n">
-        <v>43816</v>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>The Daily Star</t>
-        </is>
-      </c>
-      <c r="C33" s="3" t="inlineStr">
-        <is>
-          <t>On this day in 1971</t>
-        </is>
-      </c>
-      <c r="D33" s="4" t="inlineStr">
-        <is>
-          <t>https://www.thedailystar.net/backpage/news/day-1971-1841272</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>(not listed - duplicate)</t>
-        </is>
-      </c>
-      <c r="F33" s="3" t="inlineStr">
-        <is>
-          <t>likely duplicate of https://www.thedailystar.net/frontpage/news/day-1971-1834492 (same title and author)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="n">
-        <v>43817</v>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>The Daily Star</t>
-        </is>
-      </c>
-      <c r="C34" s="3" t="inlineStr">
-        <is>
-          <t>On this day in 1971</t>
-        </is>
-      </c>
-      <c r="D34" s="4" t="inlineStr">
-        <is>
-          <t>https://www.thedailystar.net/backpage/news/day-1971-1841626</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>(not listed - duplicate)</t>
-        </is>
-      </c>
-      <c r="F34" s="3" t="inlineStr">
-        <is>
-          <t>likely duplicate of https://www.thedailystar.net/frontpage/news/day-1971-1834492 (same title and author)</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="n">
-        <v>43818</v>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>The Daily Star</t>
-        </is>
-      </c>
-      <c r="C35" s="3" t="inlineStr">
-        <is>
-          <t>On this day in 1971</t>
-        </is>
-      </c>
-      <c r="D35" s="4" t="inlineStr">
-        <is>
-          <t>https://www.thedailystar.net/backpage/news/day-1971-1842187</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>(not listed - duplicate)</t>
-        </is>
-      </c>
-      <c r="F35" s="3" t="inlineStr">
-        <is>
-          <t>likely duplicate of https://www.thedailystar.net/frontpage/news/day-1971-1834492 (same title and author)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="n">
-        <v>43819</v>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>The Daily Star</t>
-        </is>
-      </c>
-      <c r="C36" s="3" t="inlineStr">
-        <is>
-          <t>On this day in 1971</t>
-        </is>
-      </c>
-      <c r="D36" s="4" t="inlineStr">
-        <is>
-          <t>https://www.thedailystar.net/backpage/news/day-1971-1842628</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>(not listed - duplicate)</t>
-        </is>
-      </c>
-      <c r="F36" s="3" t="inlineStr">
-        <is>
-          <t>likely duplicate of https://www.thedailystar.net/frontpage/news/day-1971-1834492 (same title and author)</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="n">
-        <v>43820</v>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>The Daily Star</t>
-        </is>
-      </c>
-      <c r="C37" s="3" t="inlineStr">
-        <is>
-          <t>On this day in 1971</t>
-        </is>
-      </c>
-      <c r="D37" s="4" t="inlineStr">
-        <is>
-          <t>https://www.thedailystar.net/frontpage/news/day-1971-1843123</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>(not listed - duplicate)</t>
-        </is>
-      </c>
-      <c r="F37" s="3" t="inlineStr">
-        <is>
-          <t>likely duplicate of https://www.thedailystar.net/frontpage/news/day-1971-1834492 (same title and author)</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="n">
-        <v>43822</v>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>The Daily Star</t>
-        </is>
-      </c>
-      <c r="C38" s="3" t="inlineStr">
-        <is>
-          <t>On this day in 1971</t>
-        </is>
-      </c>
-      <c r="D38" s="4" t="inlineStr">
-        <is>
-          <t>https://www.thedailystar.net/backpage/news/day-1971-1843864</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>(not listed - duplicate)</t>
-        </is>
-      </c>
-      <c r="F38" s="3" t="inlineStr">
-        <is>
-          <t>likely duplicate of https://www.thedailystar.net/frontpage/news/day-1971-1834492 (same title and author)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="n">
-        <v>43823</v>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>The Daily Star</t>
-        </is>
-      </c>
-      <c r="C39" s="3" t="inlineStr">
-        <is>
-          <t>On this day in 1971</t>
-        </is>
-      </c>
-      <c r="D39" s="4" t="inlineStr">
-        <is>
-          <t>https://www.thedailystar.net/backpage/news/day-1971-1844326</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>(not listed - duplicate)</t>
-        </is>
-      </c>
-      <c r="F39" s="3" t="inlineStr">
-        <is>
-          <t>likely duplicate of https://www.thedailystar.net/frontpage/news/day-1971-1834492 (same title and author)</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="n">
-        <v>43824</v>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>The Daily Star</t>
-        </is>
-      </c>
-      <c r="C40" s="3" t="inlineStr">
-        <is>
-          <t>On this day in 1971</t>
-        </is>
-      </c>
-      <c r="D40" s="4" t="inlineStr">
-        <is>
-          <t>https://www.thedailystar.net/backpage/news/day-1971-1844836</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>(not listed - duplicate)</t>
-        </is>
-      </c>
-      <c r="F40" s="3" t="inlineStr">
-        <is>
-          <t>likely duplicate of https://www.thedailystar.net/frontpage/news/day-1971-1834492 (same title and author)</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="n">
-        <v>43825</v>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>The Daily Star</t>
-        </is>
-      </c>
-      <c r="C41" s="3" t="inlineStr">
-        <is>
-          <t>On this day in 1971</t>
-        </is>
-      </c>
-      <c r="D41" s="4" t="inlineStr">
-        <is>
-          <t>https://www.thedailystar.net/frontpage/news/day-1971-1845265</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>(not listed - duplicate)</t>
-        </is>
-      </c>
-      <c r="F41" s="3" t="inlineStr">
-        <is>
-          <t>likely duplicate of https://www.thedailystar.net/frontpage/news/day-1971-1834492 (same title and author)</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="n">
-        <v>43826</v>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>The Daily Star</t>
-        </is>
-      </c>
-      <c r="C42" s="3" t="inlineStr">
-        <is>
-          <t>On this day in 1971</t>
-        </is>
-      </c>
-      <c r="D42" s="4" t="inlineStr">
-        <is>
-          <t>https://www.thedailystar.net/backpage/news/day-1971-1845622</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>(not listed - duplicate)</t>
-        </is>
-      </c>
-      <c r="F42" s="3" t="inlineStr">
-        <is>
-          <t>likely duplicate of https://www.thedailystar.net/frontpage/news/day-1971-1834492 (same title and author)</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="n">
-        <v>43827</v>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>The Daily Star</t>
-        </is>
-      </c>
-      <c r="C43" s="3" t="inlineStr">
-        <is>
-          <t>On this day in 1971</t>
-        </is>
-      </c>
-      <c r="D43" s="4" t="inlineStr">
-        <is>
-          <t>https://www.thedailystar.net/backpage/news/day-1971-1846141</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>(not listed - duplicate)</t>
-        </is>
-      </c>
-      <c r="F43" s="3" t="inlineStr">
-        <is>
-          <t>likely duplicate of https://www.thedailystar.net/frontpage/news/day-1971-1834492 (same title and author)</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="n">
-        <v>43828</v>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>The Daily Star</t>
-        </is>
-      </c>
-      <c r="C44" s="3" t="inlineStr">
-        <is>
-          <t>On this day in 1971</t>
-        </is>
-      </c>
-      <c r="D44" s="4" t="inlineStr">
-        <is>
-          <t>https://www.thedailystar.net/backpage/news/day-1971-1846756</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>(not listed - duplicate)</t>
-        </is>
-      </c>
-      <c r="F44" s="3" t="inlineStr">
-        <is>
-          <t>likely duplicate of https://www.thedailystar.net/frontpage/news/day-1971-1834492 (same title and author)</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="n">
-        <v>43829</v>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>The Daily Star</t>
-        </is>
-      </c>
-      <c r="C45" s="3" t="inlineStr">
-        <is>
-          <t>On this day in 1971</t>
-        </is>
-      </c>
-      <c r="D45" s="4" t="inlineStr">
-        <is>
-          <t>https://www.thedailystar.net/backpage/news/day-1971-1847032</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>(not listed - duplicate)</t>
-        </is>
-      </c>
-      <c r="F45" s="3" t="inlineStr">
-        <is>
-          <t>likely duplicate of https://www.thedailystar.net/frontpage/news/day-1971-1834492 (same title and author)</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="n">
-        <v>43830</v>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>The Daily Star</t>
-        </is>
-      </c>
-      <c r="C46" s="3" t="inlineStr">
-        <is>
-          <t>On this day in 1971</t>
-        </is>
-      </c>
-      <c r="D46" s="4" t="inlineStr">
-        <is>
-          <t>https://www.thedailystar.net/backpage/news/day-1971-1847383</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>(not listed - duplicate)</t>
-        </is>
-      </c>
-      <c r="F46" s="3" t="inlineStr">
-        <is>
-          <t>likely duplicate of https://www.thedailystar.net/frontpage/news/day-1971-1834492 (same title and author)</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="n">
-        <v>44264</v>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>M Rafiqul Islam</t>
-        </is>
-      </c>
-      <c r="C47" s="3" t="inlineStr">
-        <is>
-          <t>The Historic Seventh March Speech of Bangabandhu: Its Influence on International Legal Discourse and Reform</t>
-        </is>
-      </c>
-      <c r="D47" s="4" t="inlineStr">
-        <is>
-          <t>https://www.thedailystar.net/law-our-rights/news/the-historic-seventh-march-speech-bangabandhu-its-influence-international-legal-discourse-and-reform-2057325</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>(not listed - duplicate)</t>
-        </is>
-      </c>
-      <c r="F47" s="3" t="inlineStr">
-        <is>
-          <t>likely duplicate of https://www.thedailystar.net/law-our-rights/news/the-historic-seventh-march-speech-bangabandhu-its-influence-international-legal-discourse-and-reform-2056313 (same title and author)</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="n">
-        <v>44323</v>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Shamsuddoza Sajen</t>
-        </is>
-      </c>
-      <c r="C48" s="3" t="inlineStr">
-        <is>
-          <t>Road to Freedom: This Day in Bangladesh Liberation War History</t>
-        </is>
-      </c>
-      <c r="D48" s="4" t="inlineStr">
-        <is>
-          <t>https://www.thedailystar.net/backpage/news/road-freedom-day-bangladesh-liberation-war-history-2089641</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>(not listed - duplicate)</t>
-        </is>
-      </c>
-      <c r="F48" s="3" t="inlineStr">
-        <is>
-          <t>likely duplicate of https://www.thedailystar.net/backpage/news/road-freedom-day-bangladesh-liberation-war-history-2061241 (same title and author)</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="n">
-        <v>42818</v>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Nayanika Mookherjee</t>
-        </is>
-      </c>
-      <c r="C49" s="3" t="inlineStr">
-        <is>
-          <t>HISTORY AND THE BIRANGONA</t>
-        </is>
-      </c>
-      <c r="D49" s="4" t="inlineStr">
-        <is>
-          <t>https://www.thedailystar.net/star-weekend/long-form/history-and-the-birangona-1380280</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>(not listed - duplicate)</t>
-        </is>
-      </c>
-      <c r="F49" s="3" t="inlineStr">
-        <is>
-          <t>likely duplicate of https://www.thedailystar.net/in-focus/news/history-and-the-birangona-2114681 (same title and author)</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="n">
-        <v>44531</v>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Shamsuddoza Sajen</t>
-        </is>
-      </c>
-      <c r="C50" s="3" t="inlineStr">
-        <is>
-          <t>Road to Freedom: This Day in Bangladesh Liberation War History</t>
-        </is>
-      </c>
-      <c r="D50" s="4" t="inlineStr">
-        <is>
-          <t>https://www.thedailystar.net/news/bangladesh/news/road-freedom-day-bangladesh-liberation-war-history-2906801</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>(not listed - duplicate)</t>
-        </is>
-      </c>
-      <c r="F50" s="3" t="inlineStr">
-        <is>
-          <t>likely duplicate of https://www.thedailystar.net/backpage/news/road-freedom-day-bangladesh-liberation-war-history-2061241 (same title and author)</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="n">
-        <v>44544</v>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Serajul Islam Choudhury</t>
-        </is>
-      </c>
-      <c r="C51" s="3" t="inlineStr">
-        <is>
-          <t>The commitment of the martyred intellectuals</t>
-        </is>
-      </c>
-      <c r="D51" s="4" t="inlineStr">
-        <is>
-          <t>https://www.thedailystar.net/views/opinion/news/the-commitment-the-martyred-intellectuals-2916866</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>(not listed - duplicate)</t>
-        </is>
-      </c>
-      <c r="F51" s="3" t="inlineStr">
-        <is>
-          <t>likely duplicate of https://www.thedailystar.net/the-commitment-of-the-martyred-intellectuals-2432 (same title and author)</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="C52" s="3" t="inlineStr">
-        <is>
-          <t>Operation Searchlight on March 25 1971: The night hell opened over Dhaka</t>
-        </is>
-      </c>
-      <c r="D52" s="4" t="inlineStr">
-        <is>
-          <t>https://www.thedailystar.net/slow-reads/slow-reads-special/operation-searchlight/news/operation-searchlight-the-night-hell-opened-over-dhaka-4135406</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>(not listed - could not be fetched)</t>
-        </is>
-      </c>
-      <c r="F52" s="3" t="inlineStr">
-        <is>
           <t>not extracted: Redirects to the interactive microsite operationsearchlight.thedailystar.net, which this environment cannot reach; title from search results; date and author not extracted</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F52"/>
+  <autoFilter ref="A1:F22"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId2"/>
@@ -26757,36 +27969,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D20" r:id="rId19"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D21" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D22" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D23" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D24" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D25" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D26" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D27" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D28" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D29" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D30" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D31" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D32" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D33" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D34" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D35" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D36" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D37" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D38" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D39" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D40" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D41" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D42" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D43" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D44" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D45" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D46" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D47" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D48" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D49" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D50" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D51" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D52" r:id="rId51"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -26842,7 +28024,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>738</v>
+        <v>769</v>
       </c>
     </row>
     <row r="4">
@@ -26862,7 +28044,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4</v>
+        <v>61</v>
       </c>
     </row>
     <row r="6">
@@ -26892,7 +28074,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>51</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9">
@@ -26902,7 +28084,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>38</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10">
@@ -26912,7 +28094,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>139</v>
+        <v>147</v>
       </c>
     </row>
     <row r="11">
@@ -26922,7 +28104,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1225</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="12">
@@ -27158,7 +28340,7 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F23" t="n">
         <v>1</v>
@@ -27181,7 +28363,7 @@
         <v>1</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F24" t="n">
         <v>1</v>
@@ -27204,7 +28386,7 @@
         <v>1</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -27227,7 +28409,7 @@
         <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
@@ -27244,13 +28426,13 @@
         <v>3</v>
       </c>
       <c r="C27" t="n">
-        <v>39</v>
+        <v>68</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
@@ -27273,7 +28455,7 @@
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F28" t="n">
         <v>3</v>
@@ -27290,7 +28472,7 @@
         <v>12</v>
       </c>
       <c r="C29" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D29" t="n">
         <v>1</v>
@@ -27319,7 +28501,7 @@
         <v>5</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F30" t="n">
         <v>3</v>
@@ -27342,7 +28524,7 @@
         <v>1</v>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
@@ -27365,7 +28547,7 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
@@ -27388,7 +28570,7 @@
         <v>1</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F33" t="n">
         <v>1</v>
@@ -27411,7 +28593,7 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F34" t="n">
         <v>1</v>
@@ -27465,7 +28647,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>07-Mar-2014 to 20-Feb-2021</t>
+          <t>07-Mar-2014 to 21-Feb-2026</t>
         </is>
       </c>
     </row>
@@ -27535,7 +28717,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>2545</v>
+        <v>2838</v>
       </c>
       <c r="C45" t="n">
         <v>2840</v>
@@ -27549,7 +28731,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Other-section tabs are still being completed: some candidates are not yet read.</t>
+          <t>11 candidate pages could not be fetched (HTTP 403/404 or redirects to other sites); they are listed in REPORT.md.</t>
         </is>
       </c>
     </row>
